--- a/file/players_updated.xlsx
+++ b/file/players_updated.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckkil\Documents\GitHub\cs-tools\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckkil\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AA5E9E-7EA8-4A91-8C67-B8C355EBBCEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0125B3-9997-44B0-81AE-17D15CC8A9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2842" uniqueCount="1079">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2932" uniqueCount="1087">
   <si>
     <t>PlayerName</t>
   </si>
@@ -3257,6 +3257,30 @@
   </si>
   <si>
     <t>Czechia</t>
+  </si>
+  <si>
+    <t>Bulgaria</t>
+  </si>
+  <si>
+    <t>Thailand</t>
+  </si>
+  <si>
+    <t>Serbia</t>
+  </si>
+  <si>
+    <t>Montenegro</t>
+  </si>
+  <si>
+    <t>Hungary</t>
+  </si>
+  <si>
+    <t>Uzbekistan</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
+    <t>Georgia</t>
   </si>
 </sst>
 </file>
@@ -15007,6 +15031,9 @@
       <c r="O227">
         <v>0</v>
       </c>
+      <c r="P227" t="s">
+        <v>1071</v>
+      </c>
     </row>
     <row r="228" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
@@ -15054,6 +15081,9 @@
       <c r="O228">
         <v>0</v>
       </c>
+      <c r="P228" t="s">
+        <v>1046</v>
+      </c>
     </row>
     <row r="229" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
@@ -15101,6 +15131,9 @@
       <c r="O229">
         <v>0</v>
       </c>
+      <c r="P229" t="s">
+        <v>1079</v>
+      </c>
     </row>
     <row r="230" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
@@ -15148,6 +15181,9 @@
       <c r="O230">
         <v>0</v>
       </c>
+      <c r="P230" t="s">
+        <v>1080</v>
+      </c>
     </row>
     <row r="231" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
@@ -15195,6 +15231,9 @@
       <c r="O231">
         <v>0</v>
       </c>
+      <c r="P231" t="s">
+        <v>1043</v>
+      </c>
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
@@ -15242,6 +15281,9 @@
       <c r="O232">
         <v>0</v>
       </c>
+      <c r="P232" t="s">
+        <v>1081</v>
+      </c>
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
@@ -15289,6 +15331,9 @@
       <c r="O233">
         <v>0</v>
       </c>
+      <c r="P233" t="s">
+        <v>1081</v>
+      </c>
     </row>
     <row r="234" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
@@ -15336,6 +15381,9 @@
       <c r="O234">
         <v>0</v>
       </c>
+      <c r="P234" t="s">
+        <v>1082</v>
+      </c>
     </row>
     <row r="235" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
@@ -15383,6 +15431,9 @@
       <c r="O235">
         <v>0</v>
       </c>
+      <c r="P235" t="s">
+        <v>1082</v>
+      </c>
     </row>
     <row r="236" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
@@ -15430,6 +15481,9 @@
       <c r="O236">
         <v>0</v>
       </c>
+      <c r="P236" t="s">
+        <v>1061</v>
+      </c>
     </row>
     <row r="237" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
@@ -15477,6 +15531,9 @@
       <c r="O237">
         <v>0</v>
       </c>
+      <c r="P237" t="s">
+        <v>1075</v>
+      </c>
     </row>
     <row r="238" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
@@ -15524,6 +15581,9 @@
       <c r="O238">
         <v>0</v>
       </c>
+      <c r="P238" t="s">
+        <v>1075</v>
+      </c>
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
@@ -15571,6 +15631,9 @@
       <c r="O239">
         <v>0</v>
       </c>
+      <c r="P239" t="s">
+        <v>1075</v>
+      </c>
     </row>
     <row r="240" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
@@ -15618,8 +15681,11 @@
       <c r="O240">
         <v>0</v>
       </c>
-    </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P240" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>285</v>
       </c>
@@ -15665,8 +15731,11 @@
       <c r="O241">
         <v>0</v>
       </c>
-    </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P241" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>286</v>
       </c>
@@ -15712,8 +15781,11 @@
       <c r="O242">
         <v>0</v>
       </c>
-    </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P242" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>287</v>
       </c>
@@ -15759,8 +15831,11 @@
       <c r="O243">
         <v>0</v>
       </c>
-    </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P243" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="244" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>288</v>
       </c>
@@ -15806,8 +15881,11 @@
       <c r="O244">
         <v>0</v>
       </c>
-    </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P244" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="245" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>289</v>
       </c>
@@ -15853,8 +15931,11 @@
       <c r="O245">
         <v>0</v>
       </c>
-    </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P245" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>290</v>
       </c>
@@ -15900,8 +15981,11 @@
       <c r="O246">
         <v>0</v>
       </c>
-    </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P246" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>291</v>
       </c>
@@ -15947,8 +16031,11 @@
       <c r="O247">
         <v>0</v>
       </c>
-    </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P247" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>292</v>
       </c>
@@ -15994,8 +16081,11 @@
       <c r="O248">
         <v>0</v>
       </c>
-    </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P248" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>293</v>
       </c>
@@ -16041,8 +16131,11 @@
       <c r="O249">
         <v>0</v>
       </c>
-    </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P249" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>294</v>
       </c>
@@ -16088,8 +16181,11 @@
       <c r="O250">
         <v>0</v>
       </c>
-    </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P250" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="251" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>295</v>
       </c>
@@ -16135,8 +16231,11 @@
       <c r="O251">
         <v>0</v>
       </c>
-    </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P251" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>296</v>
       </c>
@@ -16182,8 +16281,11 @@
       <c r="O252">
         <v>0</v>
       </c>
-    </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P252" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>297</v>
       </c>
@@ -16229,8 +16331,11 @@
       <c r="O253">
         <v>0</v>
       </c>
-    </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P253" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>298</v>
       </c>
@@ -16276,8 +16381,11 @@
       <c r="O254">
         <v>0</v>
       </c>
-    </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P254" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>299</v>
       </c>
@@ -16323,8 +16431,11 @@
       <c r="O255">
         <v>0</v>
       </c>
-    </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P255" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>300</v>
       </c>
@@ -16370,8 +16481,11 @@
       <c r="O256">
         <v>0</v>
       </c>
-    </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P256" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>301</v>
       </c>
@@ -16417,8 +16531,11 @@
       <c r="O257">
         <v>0</v>
       </c>
-    </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P257" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="258" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>302</v>
       </c>
@@ -16464,8 +16581,11 @@
       <c r="O258">
         <v>0</v>
       </c>
-    </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P258" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>303</v>
       </c>
@@ -16511,8 +16631,11 @@
       <c r="O259">
         <v>0</v>
       </c>
-    </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P259" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>304</v>
       </c>
@@ -16558,8 +16681,11 @@
       <c r="O260">
         <v>0</v>
       </c>
-    </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P260" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="261" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>305</v>
       </c>
@@ -16605,8 +16731,11 @@
       <c r="O261">
         <v>0</v>
       </c>
-    </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P261" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="262" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>306</v>
       </c>
@@ -16652,8 +16781,11 @@
       <c r="O262">
         <v>0</v>
       </c>
-    </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P262" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>307</v>
       </c>
@@ -16699,8 +16831,11 @@
       <c r="O263">
         <v>0</v>
       </c>
-    </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P263" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="264" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>308</v>
       </c>
@@ -16746,8 +16881,11 @@
       <c r="O264">
         <v>0</v>
       </c>
-    </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P264" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="265" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>309</v>
       </c>
@@ -16793,8 +16931,11 @@
       <c r="O265">
         <v>0</v>
       </c>
-    </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P265" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>310</v>
       </c>
@@ -16840,8 +16981,11 @@
       <c r="O266">
         <v>0</v>
       </c>
-    </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P266" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>311</v>
       </c>
@@ -16887,8 +17031,11 @@
       <c r="O267">
         <v>0</v>
       </c>
-    </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P267" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>312</v>
       </c>
@@ -16934,8 +17081,11 @@
       <c r="O268">
         <v>0</v>
       </c>
-    </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P268" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>313</v>
       </c>
@@ -16981,8 +17131,11 @@
       <c r="O269">
         <v>0</v>
       </c>
-    </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P269" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>314</v>
       </c>
@@ -17028,8 +17181,11 @@
       <c r="O270">
         <v>0</v>
       </c>
-    </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P270" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="271" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>315</v>
       </c>
@@ -17075,8 +17231,11 @@
       <c r="O271">
         <v>0</v>
       </c>
-    </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P271" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>316</v>
       </c>
@@ -17122,8 +17281,11 @@
       <c r="O272">
         <v>0</v>
       </c>
-    </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P272" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>317</v>
       </c>
@@ -17169,8 +17331,11 @@
       <c r="O273">
         <v>0</v>
       </c>
-    </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P273" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="274" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>318</v>
       </c>
@@ -17216,8 +17381,11 @@
       <c r="O274">
         <v>0</v>
       </c>
-    </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P274" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>319</v>
       </c>
@@ -17263,8 +17431,11 @@
       <c r="O275">
         <v>0</v>
       </c>
-    </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P275" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>320</v>
       </c>
@@ -17310,8 +17481,11 @@
       <c r="O276">
         <v>0</v>
       </c>
-    </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P276" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>321</v>
       </c>
@@ -17357,8 +17531,11 @@
       <c r="O277">
         <v>0</v>
       </c>
-    </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P277" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="278" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>322</v>
       </c>
@@ -17404,8 +17581,11 @@
       <c r="O278">
         <v>0</v>
       </c>
-    </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P278" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>323</v>
       </c>
@@ -17451,8 +17631,11 @@
       <c r="O279">
         <v>0</v>
       </c>
-    </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P279" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>324</v>
       </c>
@@ -17498,8 +17681,11 @@
       <c r="O280">
         <v>0</v>
       </c>
-    </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P280" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>325</v>
       </c>
@@ -17545,8 +17731,11 @@
       <c r="O281">
         <v>0</v>
       </c>
-    </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P281" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="282" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>326</v>
       </c>
@@ -17592,8 +17781,11 @@
       <c r="O282">
         <v>0</v>
       </c>
-    </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P282" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>327</v>
       </c>
@@ -17639,8 +17831,11 @@
       <c r="O283">
         <v>0</v>
       </c>
-    </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P283" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="284" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>328</v>
       </c>
@@ -17686,8 +17881,11 @@
       <c r="O284">
         <v>0</v>
       </c>
-    </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P284" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>329</v>
       </c>
@@ -17733,8 +17931,11 @@
       <c r="O285">
         <v>0</v>
       </c>
-    </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P285" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="286" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>330</v>
       </c>
@@ -17780,8 +17981,11 @@
       <c r="O286">
         <v>0</v>
       </c>
-    </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P286" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>331</v>
       </c>
@@ -17827,8 +18031,11 @@
       <c r="O287">
         <v>0</v>
       </c>
-    </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P287" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>332</v>
       </c>
@@ -17874,8 +18081,11 @@
       <c r="O288">
         <v>0</v>
       </c>
-    </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P288" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>333</v>
       </c>
@@ -17921,8 +18131,11 @@
       <c r="O289">
         <v>0</v>
       </c>
-    </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P289" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>334</v>
       </c>
@@ -17968,8 +18181,11 @@
       <c r="O290">
         <v>0</v>
       </c>
-    </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P290" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>335</v>
       </c>
@@ -18015,8 +18231,11 @@
       <c r="O291">
         <v>0</v>
       </c>
-    </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P291" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>336</v>
       </c>
@@ -18062,8 +18281,11 @@
       <c r="O292">
         <v>0</v>
       </c>
-    </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P292" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="293" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>337</v>
       </c>
@@ -18109,8 +18331,11 @@
       <c r="O293">
         <v>0</v>
       </c>
-    </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P293" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>338</v>
       </c>
@@ -18156,8 +18381,11 @@
       <c r="O294">
         <v>0</v>
       </c>
-    </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P294" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>339</v>
       </c>
@@ -18203,8 +18431,11 @@
       <c r="O295">
         <v>0</v>
       </c>
-    </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P295" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>340</v>
       </c>
@@ -18250,8 +18481,11 @@
       <c r="O296">
         <v>0</v>
       </c>
-    </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P296" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>341</v>
       </c>
@@ -18297,8 +18531,11 @@
       <c r="O297">
         <v>0</v>
       </c>
-    </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P297" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>342</v>
       </c>
@@ -18344,8 +18581,11 @@
       <c r="O298">
         <v>0</v>
       </c>
-    </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P298" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="299" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>343</v>
       </c>
@@ -18391,8 +18631,11 @@
       <c r="O299">
         <v>0</v>
       </c>
-    </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P299" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>344</v>
       </c>
@@ -18438,8 +18681,11 @@
       <c r="O300">
         <v>0</v>
       </c>
-    </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P300" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="301" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>345</v>
       </c>
@@ -18485,8 +18731,11 @@
       <c r="O301">
         <v>0</v>
       </c>
-    </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P301" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="302" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>346</v>
       </c>
@@ -18532,8 +18781,11 @@
       <c r="O302">
         <v>0</v>
       </c>
-    </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P302" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="303" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>347</v>
       </c>
@@ -18579,8 +18831,11 @@
       <c r="O303">
         <v>0</v>
       </c>
-    </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P303" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="304" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>348</v>
       </c>
@@ -18626,8 +18881,11 @@
       <c r="O304">
         <v>0</v>
       </c>
-    </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P304" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="305" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>349</v>
       </c>
@@ -18673,8 +18931,11 @@
       <c r="O305">
         <v>0</v>
       </c>
-    </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P305" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="306" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>350</v>
       </c>
@@ -18720,8 +18981,11 @@
       <c r="O306">
         <v>0</v>
       </c>
-    </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P306" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="307" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>351</v>
       </c>
@@ -18767,8 +19031,11 @@
       <c r="O307">
         <v>0</v>
       </c>
-    </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P307" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="308" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>352</v>
       </c>
@@ -18814,8 +19081,11 @@
       <c r="O308">
         <v>0</v>
       </c>
-    </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P308" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="309" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>353</v>
       </c>
@@ -18861,8 +19131,11 @@
       <c r="O309">
         <v>0</v>
       </c>
-    </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P309" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="310" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>354</v>
       </c>
@@ -18908,8 +19181,11 @@
       <c r="O310">
         <v>0</v>
       </c>
-    </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P310" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="311" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>355</v>
       </c>
@@ -18955,8 +19231,11 @@
       <c r="O311">
         <v>0</v>
       </c>
-    </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P311" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="312" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>356</v>
       </c>
@@ -19002,8 +19281,11 @@
       <c r="O312">
         <v>0</v>
       </c>
-    </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P312" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="313" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>357</v>
       </c>
@@ -19049,8 +19331,11 @@
       <c r="O313">
         <v>0</v>
       </c>
-    </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P313" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="314" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>222</v>
       </c>
@@ -19096,8 +19381,11 @@
       <c r="O314">
         <v>0</v>
       </c>
-    </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P314" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="315" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>358</v>
       </c>
@@ -19143,8 +19431,11 @@
       <c r="O315">
         <v>0</v>
       </c>
-    </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P315" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="316" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>359</v>
       </c>
@@ -19190,8 +19481,11 @@
       <c r="O316">
         <v>0</v>
       </c>
-    </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P316" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="317" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>360</v>
       </c>
@@ -19238,7 +19532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>361</v>
       </c>
@@ -19285,7 +19579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>362</v>
       </c>
@@ -19332,7 +19626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>363</v>
       </c>

--- a/file/players_updated.xlsx
+++ b/file/players_updated.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckkil\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.abraga\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0125B3-9997-44B0-81AE-17D15CC8A9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B85BCC1C-4AB9-406C-9BB4-7D52A817D38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2932" uniqueCount="1087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3179" uniqueCount="1095">
   <si>
     <t>PlayerName</t>
   </si>
@@ -3281,6 +3281,30 @@
   </si>
   <si>
     <t>Georgia</t>
+  </si>
+  <si>
+    <t>Guatemala</t>
+  </si>
+  <si>
+    <t>Luxembourg</t>
+  </si>
+  <si>
+    <t>United Arab Emirates</t>
+  </si>
+  <si>
+    <t>Iraq</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>South Korea</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>Singapore</t>
   </si>
 </sst>
 </file>
@@ -3676,16 +3700,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P867"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.125" customWidth="1"/>
-    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="6" max="6" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.75" customWidth="1"/>
+    <col min="8" max="8" width="3.75" customWidth="1"/>
+    <col min="9" max="9" width="3.25" customWidth="1"/>
+    <col min="10" max="10" width="4.83203125" customWidth="1"/>
+    <col min="11" max="11" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.9140625" customWidth="1"/>
+    <col min="15" max="15" width="11.5" customWidth="1"/>
     <col min="16" max="16" width="20.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3735,7 +3764,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>79</v>
       </c>
@@ -3785,7 +3814,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>80</v>
       </c>
@@ -3835,7 +3864,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,7 +3914,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>82</v>
       </c>
@@ -3935,7 +3964,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>83</v>
       </c>
@@ -3985,7 +4014,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>84</v>
       </c>
@@ -4035,7 +4064,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>85</v>
       </c>
@@ -4085,7 +4114,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>72</v>
       </c>
@@ -4135,7 +4164,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>73</v>
       </c>
@@ -4185,7 +4214,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>74</v>
       </c>
@@ -4235,7 +4264,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>59</v>
       </c>
@@ -4285,7 +4314,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>61</v>
       </c>
@@ -4335,7 +4364,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>62</v>
       </c>
@@ -4385,7 +4414,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>63</v>
       </c>
@@ -4435,7 +4464,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>64</v>
       </c>
@@ -4485,7 +4514,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>86</v>
       </c>
@@ -4535,7 +4564,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>87</v>
       </c>
@@ -4585,7 +4614,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>88</v>
       </c>
@@ -4635,7 +4664,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>89</v>
       </c>
@@ -4685,7 +4714,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>90</v>
       </c>
@@ -4735,7 +4764,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>91</v>
       </c>
@@ -4785,7 +4814,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>92</v>
       </c>
@@ -4835,7 +4864,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>93</v>
       </c>
@@ -4885,7 +4914,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>94</v>
       </c>
@@ -4935,7 +4964,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>95</v>
       </c>
@@ -4985,7 +5014,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>21</v>
       </c>
@@ -5035,7 +5064,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>23</v>
       </c>
@@ -5085,7 +5114,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>24</v>
       </c>
@@ -5135,7 +5164,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>25</v>
       </c>
@@ -5185,7 +5214,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>26</v>
       </c>
@@ -5235,7 +5264,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>33</v>
       </c>
@@ -5285,7 +5314,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>35</v>
       </c>
@@ -5335,7 +5364,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>36</v>
       </c>
@@ -5385,7 +5414,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>37</v>
       </c>
@@ -5435,7 +5464,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>38</v>
       </c>
@@ -5485,7 +5514,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>96</v>
       </c>
@@ -5535,7 +5564,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>97</v>
       </c>
@@ -5585,7 +5614,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>98</v>
       </c>
@@ -5635,7 +5664,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>99</v>
       </c>
@@ -5685,7 +5714,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>100</v>
       </c>
@@ -5735,7 +5764,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>101</v>
       </c>
@@ -5785,7 +5814,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>102</v>
       </c>
@@ -5835,7 +5864,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>103</v>
       </c>
@@ -5885,7 +5914,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>104</v>
       </c>
@@ -5935,7 +5964,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>105</v>
       </c>
@@ -5985,7 +6014,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>106</v>
       </c>
@@ -6035,7 +6064,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>107</v>
       </c>
@@ -6085,7 +6114,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>108</v>
       </c>
@@ -6135,7 +6164,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>109</v>
       </c>
@@ -6185,7 +6214,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>110</v>
       </c>
@@ -6235,7 +6264,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>111</v>
       </c>
@@ -6285,7 +6314,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>112</v>
       </c>
@@ -6335,7 +6364,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>113</v>
       </c>
@@ -6385,7 +6414,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>114</v>
       </c>
@@ -6435,7 +6464,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>115</v>
       </c>
@@ -6485,7 +6514,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>116</v>
       </c>
@@ -6535,7 +6564,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>117</v>
       </c>
@@ -6585,7 +6614,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>118</v>
       </c>
@@ -6635,7 +6664,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>119</v>
       </c>
@@ -6685,7 +6714,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>120</v>
       </c>
@@ -6735,7 +6764,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>53</v>
       </c>
@@ -6785,7 +6814,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6835,7 +6864,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>56</v>
       </c>
@@ -6885,7 +6914,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6935,7 +6964,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>58</v>
       </c>
@@ -6985,7 +7014,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>121</v>
       </c>
@@ -7035,7 +7064,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>122</v>
       </c>
@@ -7085,7 +7114,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>123</v>
       </c>
@@ -7135,7 +7164,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>124</v>
       </c>
@@ -7185,7 +7214,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>125</v>
       </c>
@@ -7235,7 +7264,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>126</v>
       </c>
@@ -7285,7 +7314,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>127</v>
       </c>
@@ -7335,7 +7364,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>128</v>
       </c>
@@ -7385,7 +7414,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>129</v>
       </c>
@@ -7435,7 +7464,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>130</v>
       </c>
@@ -7485,7 +7514,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>131</v>
       </c>
@@ -7535,7 +7564,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>132</v>
       </c>
@@ -7585,7 +7614,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>133</v>
       </c>
@@ -7635,7 +7664,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>134</v>
       </c>
@@ -7685,7 +7714,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>135</v>
       </c>
@@ -7735,7 +7764,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>136</v>
       </c>
@@ -7785,7 +7814,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>137</v>
       </c>
@@ -7835,7 +7864,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>138</v>
       </c>
@@ -7885,7 +7914,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>139</v>
       </c>
@@ -7935,7 +7964,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>140</v>
       </c>
@@ -7985,7 +8014,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>141</v>
       </c>
@@ -8035,7 +8064,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>142</v>
       </c>
@@ -8085,7 +8114,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>143</v>
       </c>
@@ -8135,7 +8164,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>144</v>
       </c>
@@ -8185,7 +8214,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>145</v>
       </c>
@@ -8235,7 +8264,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>146</v>
       </c>
@@ -8285,7 +8314,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>147</v>
       </c>
@@ -8335,7 +8364,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>148</v>
       </c>
@@ -8385,7 +8414,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>149</v>
       </c>
@@ -8435,7 +8464,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>150</v>
       </c>
@@ -8485,7 +8514,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>151</v>
       </c>
@@ -8535,7 +8564,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>152</v>
       </c>
@@ -8585,7 +8614,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>153</v>
       </c>
@@ -8635,7 +8664,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>154</v>
       </c>
@@ -8685,7 +8714,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>155</v>
       </c>
@@ -8735,7 +8764,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>156</v>
       </c>
@@ -8785,7 +8814,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>157</v>
       </c>
@@ -8835,7 +8864,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>158</v>
       </c>
@@ -8885,7 +8914,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>159</v>
       </c>
@@ -8935,7 +8964,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>160</v>
       </c>
@@ -8985,7 +9014,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>161</v>
       </c>
@@ -9035,7 +9064,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>162</v>
       </c>
@@ -9085,7 +9114,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>163</v>
       </c>
@@ -9135,7 +9164,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>164</v>
       </c>
@@ -9185,7 +9214,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>165</v>
       </c>
@@ -9235,7 +9264,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>166</v>
       </c>
@@ -9285,7 +9314,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>167</v>
       </c>
@@ -9335,7 +9364,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>168</v>
       </c>
@@ -9385,7 +9414,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>169</v>
       </c>
@@ -9435,7 +9464,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>170</v>
       </c>
@@ -9485,7 +9514,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>4</v>
       </c>
@@ -9535,7 +9564,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>6</v>
       </c>
@@ -9585,7 +9614,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>7</v>
       </c>
@@ -9635,7 +9664,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>8</v>
       </c>
@@ -9685,7 +9714,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>9</v>
       </c>
@@ -9735,7 +9764,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>171</v>
       </c>
@@ -9785,7 +9814,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>172</v>
       </c>
@@ -9835,7 +9864,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>173</v>
       </c>
@@ -9885,7 +9914,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>174</v>
       </c>
@@ -9935,7 +9964,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>175</v>
       </c>
@@ -9985,7 +10014,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>176</v>
       </c>
@@ -10035,7 +10064,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>177</v>
       </c>
@@ -10085,7 +10114,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>178</v>
       </c>
@@ -10135,7 +10164,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>179</v>
       </c>
@@ -10185,7 +10214,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>180</v>
       </c>
@@ -10235,7 +10264,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>181</v>
       </c>
@@ -10285,7 +10314,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>182</v>
       </c>
@@ -10335,7 +10364,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>183</v>
       </c>
@@ -10385,7 +10414,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>184</v>
       </c>
@@ -10435,7 +10464,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>185</v>
       </c>
@@ -10485,7 +10514,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>186</v>
       </c>
@@ -10535,7 +10564,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>187</v>
       </c>
@@ -10585,7 +10614,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>188</v>
       </c>
@@ -10635,7 +10664,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>189</v>
       </c>
@@ -10685,7 +10714,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>190</v>
       </c>
@@ -10735,7 +10764,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>191</v>
       </c>
@@ -10785,7 +10814,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>192</v>
       </c>
@@ -10835,7 +10864,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>193</v>
       </c>
@@ -10885,7 +10914,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>194</v>
       </c>
@@ -10935,7 +10964,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>195</v>
       </c>
@@ -10985,7 +11014,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>196</v>
       </c>
@@ -11035,7 +11064,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>197</v>
       </c>
@@ -11085,7 +11114,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>198</v>
       </c>
@@ -11135,7 +11164,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>199</v>
       </c>
@@ -11185,7 +11214,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>200</v>
       </c>
@@ -11235,7 +11264,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>201</v>
       </c>
@@ -11285,7 +11314,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>202</v>
       </c>
@@ -11335,7 +11364,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>203</v>
       </c>
@@ -11385,7 +11414,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>204</v>
       </c>
@@ -11435,7 +11464,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>205</v>
       </c>
@@ -11485,7 +11514,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>206</v>
       </c>
@@ -11535,7 +11564,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>207</v>
       </c>
@@ -11585,7 +11614,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>208</v>
       </c>
@@ -11635,7 +11664,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>209</v>
       </c>
@@ -11685,7 +11714,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>210</v>
       </c>
@@ -11735,7 +11764,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>211</v>
       </c>
@@ -11785,7 +11814,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
         <v>212</v>
       </c>
@@ -11835,7 +11864,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>213</v>
       </c>
@@ -11885,7 +11914,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
         <v>214</v>
       </c>
@@ -11935,7 +11964,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>215</v>
       </c>
@@ -11985,7 +12014,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>216</v>
       </c>
@@ -12035,7 +12064,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
         <v>217</v>
       </c>
@@ -12085,7 +12114,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
         <v>218</v>
       </c>
@@ -12135,7 +12164,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>219</v>
       </c>
@@ -12185,7 +12214,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
         <v>220</v>
       </c>
@@ -12235,7 +12264,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
         <v>221</v>
       </c>
@@ -12285,7 +12314,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
         <v>222</v>
       </c>
@@ -12335,7 +12364,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
         <v>223</v>
       </c>
@@ -12385,7 +12414,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>224</v>
       </c>
@@ -12435,7 +12464,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>225</v>
       </c>
@@ -12485,7 +12514,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
         <v>47</v>
       </c>
@@ -12535,7 +12564,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
         <v>49</v>
       </c>
@@ -12585,7 +12614,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>50</v>
       </c>
@@ -12635,7 +12664,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
         <v>51</v>
       </c>
@@ -12685,7 +12714,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>52</v>
       </c>
@@ -12735,7 +12764,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>226</v>
       </c>
@@ -12785,7 +12814,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
         <v>227</v>
       </c>
@@ -12835,7 +12864,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
         <v>228</v>
       </c>
@@ -12885,7 +12914,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>229</v>
       </c>
@@ -12935,7 +12964,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
         <v>230</v>
       </c>
@@ -12985,7 +13014,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
         <v>231</v>
       </c>
@@ -13035,7 +13064,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
         <v>232</v>
       </c>
@@ -13085,7 +13114,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
         <v>233</v>
       </c>
@@ -13135,7 +13164,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
         <v>234</v>
       </c>
@@ -13185,7 +13214,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
         <v>235</v>
       </c>
@@ -13235,7 +13264,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
         <v>236</v>
       </c>
@@ -13285,7 +13314,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
         <v>237</v>
       </c>
@@ -13335,7 +13364,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
         <v>238</v>
       </c>
@@ -13385,7 +13414,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
         <v>239</v>
       </c>
@@ -13435,7 +13464,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
         <v>240</v>
       </c>
@@ -13485,7 +13514,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
         <v>241</v>
       </c>
@@ -13535,7 +13564,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
         <v>242</v>
       </c>
@@ -13585,7 +13614,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
         <v>243</v>
       </c>
@@ -13635,7 +13664,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
         <v>244</v>
       </c>
@@ -13685,7 +13714,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
         <v>245</v>
       </c>
@@ -13735,7 +13764,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
         <v>246</v>
       </c>
@@ -13785,7 +13814,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
         <v>247</v>
       </c>
@@ -13835,7 +13864,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
         <v>248</v>
       </c>
@@ -13885,7 +13914,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
         <v>249</v>
       </c>
@@ -13935,7 +13964,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
         <v>250</v>
       </c>
@@ -13985,7 +14014,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
         <v>251</v>
       </c>
@@ -14035,7 +14064,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
         <v>252</v>
       </c>
@@ -14085,7 +14114,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
         <v>253</v>
       </c>
@@ -14135,7 +14164,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
         <v>254</v>
       </c>
@@ -14185,7 +14214,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A211" s="1" t="s">
         <v>255</v>
       </c>
@@ -14235,7 +14264,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>256</v>
       </c>
@@ -14285,7 +14314,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
         <v>257</v>
       </c>
@@ -14335,7 +14364,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
         <v>258</v>
       </c>
@@ -14385,7 +14414,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
         <v>259</v>
       </c>
@@ -14435,7 +14464,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
         <v>260</v>
       </c>
@@ -14485,7 +14514,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
         <v>261</v>
       </c>
@@ -14535,7 +14564,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
         <v>262</v>
       </c>
@@ -14585,7 +14614,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
         <v>263</v>
       </c>
@@ -14635,7 +14664,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
         <v>264</v>
       </c>
@@ -14685,7 +14714,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
         <v>265</v>
       </c>
@@ -14735,7 +14764,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
         <v>266</v>
       </c>
@@ -14785,7 +14814,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
         <v>267</v>
       </c>
@@ -14835,7 +14864,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
         <v>268</v>
       </c>
@@ -14885,7 +14914,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
         <v>269</v>
       </c>
@@ -14935,7 +14964,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
         <v>270</v>
       </c>
@@ -14985,7 +15014,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
         <v>271</v>
       </c>
@@ -15035,7 +15064,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
         <v>272</v>
       </c>
@@ -15085,7 +15114,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
         <v>273</v>
       </c>
@@ -15135,7 +15164,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
         <v>274</v>
       </c>
@@ -15185,7 +15214,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
         <v>275</v>
       </c>
@@ -15235,7 +15264,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
         <v>276</v>
       </c>
@@ -15285,7 +15314,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>277</v>
       </c>
@@ -15335,7 +15364,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>278</v>
       </c>
@@ -15385,7 +15414,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
         <v>279</v>
       </c>
@@ -15435,7 +15464,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
         <v>280</v>
       </c>
@@ -15485,7 +15514,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A237" s="1" t="s">
         <v>281</v>
       </c>
@@ -15535,7 +15564,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A238" s="1" t="s">
         <v>282</v>
       </c>
@@ -15585,7 +15614,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A239" s="1" t="s">
         <v>283</v>
       </c>
@@ -15635,7 +15664,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A240" s="1" t="s">
         <v>284</v>
       </c>
@@ -15685,7 +15714,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A241" s="1" t="s">
         <v>285</v>
       </c>
@@ -15735,7 +15764,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A242" s="1" t="s">
         <v>286</v>
       </c>
@@ -15785,7 +15814,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A243" s="1" t="s">
         <v>287</v>
       </c>
@@ -15835,7 +15864,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A244" s="1" t="s">
         <v>288</v>
       </c>
@@ -15885,7 +15914,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A245" s="1" t="s">
         <v>289</v>
       </c>
@@ -15935,7 +15964,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A246" s="1" t="s">
         <v>290</v>
       </c>
@@ -15985,7 +16014,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A247" s="1" t="s">
         <v>291</v>
       </c>
@@ -16035,7 +16064,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A248" s="1" t="s">
         <v>292</v>
       </c>
@@ -16085,7 +16114,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A249" s="1" t="s">
         <v>293</v>
       </c>
@@ -16135,7 +16164,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A250" s="1" t="s">
         <v>294</v>
       </c>
@@ -16185,7 +16214,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A251" s="1" t="s">
         <v>295</v>
       </c>
@@ -16235,7 +16264,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A252" s="1" t="s">
         <v>296</v>
       </c>
@@ -16285,7 +16314,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A253" s="1" t="s">
         <v>297</v>
       </c>
@@ -16335,7 +16364,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A254" s="1" t="s">
         <v>298</v>
       </c>
@@ -16385,7 +16414,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A255" s="1" t="s">
         <v>299</v>
       </c>
@@ -16435,7 +16464,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A256" s="1" t="s">
         <v>300</v>
       </c>
@@ -16485,7 +16514,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A257" s="1" t="s">
         <v>301</v>
       </c>
@@ -16535,7 +16564,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A258" s="1" t="s">
         <v>302</v>
       </c>
@@ -16585,7 +16614,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A259" s="1" t="s">
         <v>303</v>
       </c>
@@ -16635,7 +16664,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A260" s="1" t="s">
         <v>304</v>
       </c>
@@ -16685,7 +16714,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A261" s="1" t="s">
         <v>305</v>
       </c>
@@ -16735,7 +16764,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A262" s="1" t="s">
         <v>306</v>
       </c>
@@ -16785,7 +16814,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A263" s="1" t="s">
         <v>307</v>
       </c>
@@ -16835,7 +16864,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A264" s="1" t="s">
         <v>308</v>
       </c>
@@ -16885,7 +16914,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A265" s="1" t="s">
         <v>309</v>
       </c>
@@ -16935,7 +16964,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A266" s="1" t="s">
         <v>310</v>
       </c>
@@ -16985,7 +17014,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A267" s="1" t="s">
         <v>311</v>
       </c>
@@ -17035,7 +17064,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A268" s="1" t="s">
         <v>312</v>
       </c>
@@ -17085,7 +17114,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A269" s="1" t="s">
         <v>313</v>
       </c>
@@ -17135,7 +17164,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A270" s="1" t="s">
         <v>314</v>
       </c>
@@ -17185,7 +17214,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A271" s="1" t="s">
         <v>315</v>
       </c>
@@ -17235,7 +17264,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A272" s="1" t="s">
         <v>316</v>
       </c>
@@ -17285,7 +17314,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A273" s="1" t="s">
         <v>317</v>
       </c>
@@ -17335,7 +17364,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A274" s="1" t="s">
         <v>318</v>
       </c>
@@ -17385,7 +17414,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A275" s="1" t="s">
         <v>319</v>
       </c>
@@ -17435,7 +17464,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A276" s="1" t="s">
         <v>320</v>
       </c>
@@ -17485,7 +17514,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A277" s="1" t="s">
         <v>321</v>
       </c>
@@ -17535,7 +17564,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A278" s="1" t="s">
         <v>322</v>
       </c>
@@ -17585,7 +17614,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A279" s="1" t="s">
         <v>323</v>
       </c>
@@ -17635,7 +17664,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A280" s="1" t="s">
         <v>324</v>
       </c>
@@ -17685,7 +17714,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A281" s="1" t="s">
         <v>325</v>
       </c>
@@ -17735,7 +17764,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A282" s="1" t="s">
         <v>326</v>
       </c>
@@ -17785,7 +17814,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A283" s="1" t="s">
         <v>327</v>
       </c>
@@ -17835,7 +17864,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A284" s="1" t="s">
         <v>328</v>
       </c>
@@ -17885,7 +17914,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A285" s="1" t="s">
         <v>329</v>
       </c>
@@ -17935,7 +17964,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="286" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A286" s="1" t="s">
         <v>330</v>
       </c>
@@ -17985,7 +18014,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A287" s="1" t="s">
         <v>331</v>
       </c>
@@ -18035,7 +18064,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A288" s="1" t="s">
         <v>332</v>
       </c>
@@ -18085,7 +18114,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A289" s="1" t="s">
         <v>333</v>
       </c>
@@ -18135,7 +18164,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A290" s="1" t="s">
         <v>334</v>
       </c>
@@ -18185,7 +18214,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A291" s="1" t="s">
         <v>335</v>
       </c>
@@ -18235,7 +18264,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A292" s="1" t="s">
         <v>336</v>
       </c>
@@ -18285,7 +18314,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="293" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A293" s="1" t="s">
         <v>337</v>
       </c>
@@ -18335,7 +18364,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A294" s="1" t="s">
         <v>338</v>
       </c>
@@ -18385,7 +18414,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A295" s="1" t="s">
         <v>339</v>
       </c>
@@ -18435,7 +18464,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A296" s="1" t="s">
         <v>340</v>
       </c>
@@ -18485,7 +18514,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A297" s="1" t="s">
         <v>341</v>
       </c>
@@ -18535,7 +18564,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A298" s="1" t="s">
         <v>342</v>
       </c>
@@ -18585,7 +18614,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="299" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A299" s="1" t="s">
         <v>343</v>
       </c>
@@ -18635,7 +18664,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A300" s="1" t="s">
         <v>344</v>
       </c>
@@ -18685,7 +18714,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A301" s="1" t="s">
         <v>345</v>
       </c>
@@ -18735,7 +18764,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="302" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A302" s="1" t="s">
         <v>346</v>
       </c>
@@ -18785,7 +18814,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="303" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A303" s="1" t="s">
         <v>347</v>
       </c>
@@ -18835,7 +18864,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="304" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A304" s="1" t="s">
         <v>348</v>
       </c>
@@ -18885,7 +18914,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="305" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A305" s="1" t="s">
         <v>349</v>
       </c>
@@ -18935,7 +18964,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="306" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A306" s="1" t="s">
         <v>350</v>
       </c>
@@ -18985,7 +19014,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A307" s="1" t="s">
         <v>351</v>
       </c>
@@ -19035,7 +19064,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="308" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A308" s="1" t="s">
         <v>352</v>
       </c>
@@ -19085,7 +19114,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="309" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A309" s="1" t="s">
         <v>353</v>
       </c>
@@ -19135,7 +19164,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="310" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A310" s="1" t="s">
         <v>354</v>
       </c>
@@ -19185,7 +19214,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="311" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A311" s="1" t="s">
         <v>355</v>
       </c>
@@ -19235,7 +19264,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="312" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A312" s="1" t="s">
         <v>356</v>
       </c>
@@ -19285,7 +19314,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="313" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A313" s="1" t="s">
         <v>357</v>
       </c>
@@ -19335,7 +19364,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A314" s="1" t="s">
         <v>222</v>
       </c>
@@ -19385,7 +19414,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="315" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A315" s="1" t="s">
         <v>358</v>
       </c>
@@ -19435,7 +19464,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="316" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A316" s="1" t="s">
         <v>359</v>
       </c>
@@ -19485,7 +19514,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="317" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A317" s="1" t="s">
         <v>360</v>
       </c>
@@ -19531,8 +19560,11 @@
       <c r="O317">
         <v>0</v>
       </c>
-    </row>
-    <row r="318" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P317" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="318" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A318" s="1" t="s">
         <v>361</v>
       </c>
@@ -19578,8 +19610,11 @@
       <c r="O318">
         <v>0</v>
       </c>
-    </row>
-    <row r="319" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P318" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="319" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A319" s="1" t="s">
         <v>362</v>
       </c>
@@ -19625,8 +19660,11 @@
       <c r="O319">
         <v>0</v>
       </c>
-    </row>
-    <row r="320" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P319" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="320" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A320" s="1" t="s">
         <v>363</v>
       </c>
@@ -19672,8 +19710,11 @@
       <c r="O320">
         <v>0</v>
       </c>
-    </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P320" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="321" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A321" s="1" t="s">
         <v>364</v>
       </c>
@@ -19719,8 +19760,11 @@
       <c r="O321">
         <v>0</v>
       </c>
-    </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P321" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="322" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A322" s="1" t="s">
         <v>15</v>
       </c>
@@ -19766,8 +19810,11 @@
       <c r="O322">
         <v>0</v>
       </c>
-    </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P322" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="323" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A323" s="1" t="s">
         <v>17</v>
       </c>
@@ -19813,8 +19860,11 @@
       <c r="O323">
         <v>0</v>
       </c>
-    </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P323" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="324" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A324" s="1" t="s">
         <v>18</v>
       </c>
@@ -19860,8 +19910,11 @@
       <c r="O324">
         <v>0</v>
       </c>
-    </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P324" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="325" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A325" s="1" t="s">
         <v>19</v>
       </c>
@@ -19907,8 +19960,11 @@
       <c r="O325">
         <v>0</v>
       </c>
-    </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P325" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="326" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A326" s="1" t="s">
         <v>20</v>
       </c>
@@ -19954,8 +20010,11 @@
       <c r="O326">
         <v>0</v>
       </c>
-    </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P326" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="327" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A327" s="1" t="s">
         <v>365</v>
       </c>
@@ -20001,8 +20060,11 @@
       <c r="O327">
         <v>0</v>
       </c>
-    </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P327" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="328" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A328" s="1" t="s">
         <v>366</v>
       </c>
@@ -20048,8 +20110,11 @@
       <c r="O328">
         <v>0</v>
       </c>
-    </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P328" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="329" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A329" s="1" t="s">
         <v>367</v>
       </c>
@@ -20095,8 +20160,11 @@
       <c r="O329">
         <v>0</v>
       </c>
-    </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P329" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="330" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A330" s="1" t="s">
         <v>368</v>
       </c>
@@ -20142,8 +20210,11 @@
       <c r="O330">
         <v>0</v>
       </c>
-    </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P330" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="331" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A331" s="1" t="s">
         <v>369</v>
       </c>
@@ -20189,8 +20260,11 @@
       <c r="O331">
         <v>0</v>
       </c>
-    </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P331" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="332" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A332" s="1" t="s">
         <v>370</v>
       </c>
@@ -20236,8 +20310,11 @@
       <c r="O332">
         <v>0</v>
       </c>
-    </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P332" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="333" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A333" s="1" t="s">
         <v>371</v>
       </c>
@@ -20283,8 +20360,11 @@
       <c r="O333">
         <v>0</v>
       </c>
-    </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P333" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="334" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A334" s="1" t="s">
         <v>372</v>
       </c>
@@ -20330,8 +20410,11 @@
       <c r="O334">
         <v>0</v>
       </c>
-    </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P334" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="335" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A335" s="1" t="s">
         <v>373</v>
       </c>
@@ -20377,8 +20460,11 @@
       <c r="O335">
         <v>0</v>
       </c>
-    </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P335" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="336" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A336" s="1" t="s">
         <v>374</v>
       </c>
@@ -20424,8 +20510,11 @@
       <c r="O336">
         <v>0</v>
       </c>
-    </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P336" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="337" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A337" s="1" t="s">
         <v>375</v>
       </c>
@@ -20471,8 +20560,11 @@
       <c r="O337">
         <v>0</v>
       </c>
-    </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P337" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="338" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A338" s="1" t="s">
         <v>376</v>
       </c>
@@ -20518,8 +20610,11 @@
       <c r="O338">
         <v>0</v>
       </c>
-    </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P338" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="339" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A339" s="1" t="s">
         <v>377</v>
       </c>
@@ -20565,8 +20660,11 @@
       <c r="O339">
         <v>0</v>
       </c>
-    </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P339" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="340" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A340" s="1" t="s">
         <v>378</v>
       </c>
@@ -20612,8 +20710,11 @@
       <c r="O340">
         <v>0</v>
       </c>
-    </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P340" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="341" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A341" s="1" t="s">
         <v>379</v>
       </c>
@@ -20659,8 +20760,11 @@
       <c r="O341">
         <v>0</v>
       </c>
-    </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P341" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="342" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A342" s="1" t="s">
         <v>380</v>
       </c>
@@ -20706,8 +20810,11 @@
       <c r="O342">
         <v>0</v>
       </c>
-    </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P342" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="343" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A343" s="1" t="s">
         <v>381</v>
       </c>
@@ -20753,8 +20860,11 @@
       <c r="O343">
         <v>0</v>
       </c>
-    </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P343" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="344" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A344" s="1" t="s">
         <v>382</v>
       </c>
@@ -20800,8 +20910,11 @@
       <c r="O344">
         <v>0</v>
       </c>
-    </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P344" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="345" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A345" s="1" t="s">
         <v>383</v>
       </c>
@@ -20847,8 +20960,11 @@
       <c r="O345">
         <v>0</v>
       </c>
-    </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P345" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="346" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A346" s="1" t="s">
         <v>384</v>
       </c>
@@ -20894,8 +21010,11 @@
       <c r="O346">
         <v>0</v>
       </c>
-    </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P346" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="347" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A347" s="1" t="s">
         <v>385</v>
       </c>
@@ -20941,8 +21060,11 @@
       <c r="O347">
         <v>0</v>
       </c>
-    </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P347" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="348" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A348" s="1" t="s">
         <v>386</v>
       </c>
@@ -20988,8 +21110,11 @@
       <c r="O348">
         <v>0</v>
       </c>
-    </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P348" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="349" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A349" s="1" t="s">
         <v>387</v>
       </c>
@@ -21035,8 +21160,11 @@
       <c r="O349">
         <v>0</v>
       </c>
-    </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P349" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="350" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A350" s="1" t="s">
         <v>388</v>
       </c>
@@ -21082,8 +21210,11 @@
       <c r="O350">
         <v>0</v>
       </c>
-    </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P350" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="351" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A351" s="1" t="s">
         <v>389</v>
       </c>
@@ -21129,8 +21260,11 @@
       <c r="O351">
         <v>0</v>
       </c>
-    </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P351" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="352" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A352" s="1" t="s">
         <v>390</v>
       </c>
@@ -21176,8 +21310,11 @@
       <c r="O352">
         <v>0</v>
       </c>
-    </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P352" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="353" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A353" s="1" t="s">
         <v>391</v>
       </c>
@@ -21223,8 +21360,11 @@
       <c r="O353">
         <v>0</v>
       </c>
-    </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P353" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="354" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A354" s="1" t="s">
         <v>392</v>
       </c>
@@ -21270,8 +21410,11 @@
       <c r="O354">
         <v>0</v>
       </c>
-    </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P354" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="355" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A355" s="1" t="s">
         <v>393</v>
       </c>
@@ -21317,8 +21460,11 @@
       <c r="O355">
         <v>0</v>
       </c>
-    </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P355" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="356" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A356" s="1" t="s">
         <v>394</v>
       </c>
@@ -21364,8 +21510,11 @@
       <c r="O356">
         <v>0</v>
       </c>
-    </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P356" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="357" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A357" s="1" t="s">
         <v>395</v>
       </c>
@@ -21411,8 +21560,11 @@
       <c r="O357">
         <v>0</v>
       </c>
-    </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P357" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="358" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A358" s="1" t="s">
         <v>396</v>
       </c>
@@ -21458,8 +21610,11 @@
       <c r="O358">
         <v>0</v>
       </c>
-    </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P358" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="359" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A359" s="1" t="s">
         <v>397</v>
       </c>
@@ -21505,8 +21660,11 @@
       <c r="O359">
         <v>0</v>
       </c>
-    </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P359" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="360" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A360" s="1" t="s">
         <v>398</v>
       </c>
@@ -21552,8 +21710,11 @@
       <c r="O360">
         <v>0</v>
       </c>
-    </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P360" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="361" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A361" s="1" t="s">
         <v>399</v>
       </c>
@@ -21599,8 +21760,11 @@
       <c r="O361">
         <v>0</v>
       </c>
-    </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P361" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="362" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A362" s="1" t="s">
         <v>40</v>
       </c>
@@ -21646,8 +21810,11 @@
       <c r="O362">
         <v>0</v>
       </c>
-    </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P362" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="363" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A363" s="1" t="s">
         <v>42</v>
       </c>
@@ -21693,8 +21860,11 @@
       <c r="O363">
         <v>0</v>
       </c>
-    </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P363" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="364" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
         <v>43</v>
       </c>
@@ -21740,8 +21910,11 @@
       <c r="O364">
         <v>0</v>
       </c>
-    </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P364" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="365" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
         <v>44</v>
       </c>
@@ -21787,8 +21960,11 @@
       <c r="O365">
         <v>0</v>
       </c>
-    </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P365" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="366" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A366" s="1" t="s">
         <v>45</v>
       </c>
@@ -21834,8 +22010,11 @@
       <c r="O366">
         <v>0</v>
       </c>
-    </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P366" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="367" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
         <v>400</v>
       </c>
@@ -21881,8 +22060,11 @@
       <c r="O367">
         <v>0</v>
       </c>
-    </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P367" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="368" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A368" s="1" t="s">
         <v>401</v>
       </c>
@@ -21928,8 +22110,11 @@
       <c r="O368">
         <v>0</v>
       </c>
-    </row>
-    <row r="369" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P368" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="369" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A369" s="1" t="s">
         <v>402</v>
       </c>
@@ -21975,8 +22160,11 @@
       <c r="O369">
         <v>0</v>
       </c>
-    </row>
-    <row r="370" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P369" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="370" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A370" s="1" t="s">
         <v>403</v>
       </c>
@@ -22022,8 +22210,11 @@
       <c r="O370">
         <v>0</v>
       </c>
-    </row>
-    <row r="371" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P370" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="371" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A371" s="1" t="s">
         <v>404</v>
       </c>
@@ -22069,8 +22260,11 @@
       <c r="O371">
         <v>0</v>
       </c>
-    </row>
-    <row r="372" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P371" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="372" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A372" s="1" t="s">
         <v>405</v>
       </c>
@@ -22116,8 +22310,11 @@
       <c r="O372">
         <v>0</v>
       </c>
-    </row>
-    <row r="373" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P372" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="373" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A373" s="1" t="s">
         <v>406</v>
       </c>
@@ -22163,8 +22360,11 @@
       <c r="O373">
         <v>0</v>
       </c>
-    </row>
-    <row r="374" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P373" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="374" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A374" s="1" t="s">
         <v>407</v>
       </c>
@@ -22210,8 +22410,11 @@
       <c r="O374">
         <v>0</v>
       </c>
-    </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P374" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="375" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A375" s="1" t="s">
         <v>408</v>
       </c>
@@ -22257,8 +22460,11 @@
       <c r="O375">
         <v>0</v>
       </c>
-    </row>
-    <row r="376" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P375" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="376" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A376" s="1" t="s">
         <v>409</v>
       </c>
@@ -22304,8 +22510,11 @@
       <c r="O376">
         <v>0</v>
       </c>
-    </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P376" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="377" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A377" s="1" t="s">
         <v>410</v>
       </c>
@@ -22351,8 +22560,11 @@
       <c r="O377">
         <v>0</v>
       </c>
-    </row>
-    <row r="378" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P377" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="378" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A378" s="1" t="s">
         <v>411</v>
       </c>
@@ -22398,8 +22610,11 @@
       <c r="O378">
         <v>0</v>
       </c>
-    </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P378" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="379" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A379" s="1" t="s">
         <v>412</v>
       </c>
@@ -22445,8 +22660,11 @@
       <c r="O379">
         <v>0</v>
       </c>
-    </row>
-    <row r="380" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P379" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="380" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A380" s="1" t="s">
         <v>413</v>
       </c>
@@ -22492,8 +22710,11 @@
       <c r="O380">
         <v>0</v>
       </c>
-    </row>
-    <row r="381" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P380" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="381" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A381" s="1" t="s">
         <v>414</v>
       </c>
@@ -22539,8 +22760,11 @@
       <c r="O381">
         <v>0</v>
       </c>
-    </row>
-    <row r="382" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P381" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="382" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A382" s="1" t="s">
         <v>415</v>
       </c>
@@ -22586,8 +22810,11 @@
       <c r="O382">
         <v>0</v>
       </c>
-    </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P382" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="383" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A383" s="1" t="s">
         <v>416</v>
       </c>
@@ -22633,8 +22860,11 @@
       <c r="O383">
         <v>0</v>
       </c>
-    </row>
-    <row r="384" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P383" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="384" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A384" s="1" t="s">
         <v>417</v>
       </c>
@@ -22680,8 +22910,11 @@
       <c r="O384">
         <v>0</v>
       </c>
-    </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P384" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="385" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A385" s="1" t="s">
         <v>418</v>
       </c>
@@ -22727,8 +22960,11 @@
       <c r="O385">
         <v>0</v>
       </c>
-    </row>
-    <row r="386" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P385" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="386" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A386" s="1" t="s">
         <v>419</v>
       </c>
@@ -22774,8 +23010,11 @@
       <c r="O386">
         <v>0</v>
       </c>
-    </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P386" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="387" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A387" s="1" t="s">
         <v>420</v>
       </c>
@@ -22821,8 +23060,11 @@
       <c r="O387">
         <v>0</v>
       </c>
-    </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P387" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="388" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A388" s="1" t="s">
         <v>421</v>
       </c>
@@ -22868,8 +23110,11 @@
       <c r="O388">
         <v>0</v>
       </c>
-    </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P388" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="389" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A389" s="1" t="s">
         <v>422</v>
       </c>
@@ -22915,8 +23160,11 @@
       <c r="O389">
         <v>0</v>
       </c>
-    </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P389" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="390" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A390" s="1" t="s">
         <v>423</v>
       </c>
@@ -22962,8 +23210,11 @@
       <c r="O390">
         <v>0</v>
       </c>
-    </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P390" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="391" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A391" s="1" t="s">
         <v>424</v>
       </c>
@@ -23009,8 +23260,11 @@
       <c r="O391">
         <v>0</v>
       </c>
-    </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P391" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="392" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A392" s="1" t="s">
         <v>425</v>
       </c>
@@ -23056,8 +23310,11 @@
       <c r="O392">
         <v>0</v>
       </c>
-    </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P392" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="393" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A393" s="1" t="s">
         <v>426</v>
       </c>
@@ -23103,8 +23360,11 @@
       <c r="O393">
         <v>0</v>
       </c>
-    </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P393" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="394" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A394" s="1" t="s">
         <v>427</v>
       </c>
@@ -23150,8 +23410,11 @@
       <c r="O394">
         <v>0</v>
       </c>
-    </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P394" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="395" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A395" s="1" t="s">
         <v>428</v>
       </c>
@@ -23197,8 +23460,11 @@
       <c r="O395">
         <v>0</v>
       </c>
-    </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P395" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="396" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A396" s="1" t="s">
         <v>429</v>
       </c>
@@ -23244,8 +23510,11 @@
       <c r="O396">
         <v>0</v>
       </c>
-    </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P396" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="397" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A397" s="1" t="s">
         <v>430</v>
       </c>
@@ -23291,8 +23560,11 @@
       <c r="O397">
         <v>0</v>
       </c>
-    </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P397" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="398" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A398" s="1" t="s">
         <v>431</v>
       </c>
@@ -23338,8 +23610,11 @@
       <c r="O398">
         <v>0</v>
       </c>
-    </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P398" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="399" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A399" s="1" t="s">
         <v>432</v>
       </c>
@@ -23385,8 +23660,11 @@
       <c r="O399">
         <v>0</v>
       </c>
-    </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P399" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="400" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A400" s="1" t="s">
         <v>433</v>
       </c>
@@ -23432,8 +23710,11 @@
       <c r="O400">
         <v>0</v>
       </c>
-    </row>
-    <row r="401" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P400" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="401" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A401" s="1" t="s">
         <v>434</v>
       </c>
@@ -23479,8 +23760,11 @@
       <c r="O401">
         <v>0</v>
       </c>
-    </row>
-    <row r="402" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P401" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="402" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A402" s="1" t="s">
         <v>435</v>
       </c>
@@ -23526,8 +23810,11 @@
       <c r="O402">
         <v>0</v>
       </c>
-    </row>
-    <row r="403" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P402" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="403" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A403" s="1" t="s">
         <v>436</v>
       </c>
@@ -23573,8 +23860,11 @@
       <c r="O403">
         <v>0</v>
       </c>
-    </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P403" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="404" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A404" s="1" t="s">
         <v>437</v>
       </c>
@@ -23620,8 +23910,11 @@
       <c r="O404">
         <v>0</v>
       </c>
-    </row>
-    <row r="405" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P404" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="405" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A405" s="1" t="s">
         <v>438</v>
       </c>
@@ -23667,8 +23960,11 @@
       <c r="O405">
         <v>0</v>
       </c>
-    </row>
-    <row r="406" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P405" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="406" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A406" s="1" t="s">
         <v>439</v>
       </c>
@@ -23714,8 +24010,11 @@
       <c r="O406">
         <v>0</v>
       </c>
-    </row>
-    <row r="407" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P406" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="407" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A407" s="1" t="s">
         <v>440</v>
       </c>
@@ -23761,8 +24060,11 @@
       <c r="O407">
         <v>0</v>
       </c>
-    </row>
-    <row r="408" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P407" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="408" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A408" s="1" t="s">
         <v>441</v>
       </c>
@@ -23808,8 +24110,11 @@
       <c r="O408">
         <v>0</v>
       </c>
-    </row>
-    <row r="409" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P408" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="409" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A409" s="1" t="s">
         <v>442</v>
       </c>
@@ -23855,8 +24160,11 @@
       <c r="O409">
         <v>0</v>
       </c>
-    </row>
-    <row r="410" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P409" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="410" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A410" s="1" t="s">
         <v>443</v>
       </c>
@@ -23902,8 +24210,11 @@
       <c r="O410">
         <v>0</v>
       </c>
-    </row>
-    <row r="411" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P410" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="411" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A411" s="1" t="s">
         <v>444</v>
       </c>
@@ -23949,8 +24260,11 @@
       <c r="O411">
         <v>0</v>
       </c>
-    </row>
-    <row r="412" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P411" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="412" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A412" s="1" t="s">
         <v>445</v>
       </c>
@@ -23996,8 +24310,11 @@
       <c r="O412">
         <v>0</v>
       </c>
-    </row>
-    <row r="413" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P412" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="413" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A413" s="1" t="s">
         <v>446</v>
       </c>
@@ -24043,8 +24360,11 @@
       <c r="O413">
         <v>0</v>
       </c>
-    </row>
-    <row r="414" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P413" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="414" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A414" s="1" t="s">
         <v>447</v>
       </c>
@@ -24090,8 +24410,11 @@
       <c r="O414">
         <v>0</v>
       </c>
-    </row>
-    <row r="415" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P414" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="415" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A415" s="1" t="s">
         <v>448</v>
       </c>
@@ -24137,8 +24460,11 @@
       <c r="O415">
         <v>0</v>
       </c>
-    </row>
-    <row r="416" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P415" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="416" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A416" s="1" t="s">
         <v>449</v>
       </c>
@@ -24184,8 +24510,11 @@
       <c r="O416">
         <v>0</v>
       </c>
-    </row>
-    <row r="417" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P416" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="417" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A417" s="1" t="s">
         <v>450</v>
       </c>
@@ -24231,8 +24560,11 @@
       <c r="O417">
         <v>0</v>
       </c>
-    </row>
-    <row r="418" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P417" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="418" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A418" s="1" t="s">
         <v>451</v>
       </c>
@@ -24278,8 +24610,11 @@
       <c r="O418">
         <v>0</v>
       </c>
-    </row>
-    <row r="419" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P418" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="419" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A419" s="1" t="s">
         <v>452</v>
       </c>
@@ -24325,8 +24660,11 @@
       <c r="O419">
         <v>0</v>
       </c>
-    </row>
-    <row r="420" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P419" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="420" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A420" s="1" t="s">
         <v>453</v>
       </c>
@@ -24372,8 +24710,11 @@
       <c r="O420">
         <v>0</v>
       </c>
-    </row>
-    <row r="421" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P420" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="421" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A421" s="1" t="s">
         <v>454</v>
       </c>
@@ -24419,8 +24760,11 @@
       <c r="O421">
         <v>0</v>
       </c>
-    </row>
-    <row r="422" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P421" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="422" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A422" s="1" t="s">
         <v>455</v>
       </c>
@@ -24466,8 +24810,11 @@
       <c r="O422">
         <v>0</v>
       </c>
-    </row>
-    <row r="423" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P422" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="423" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A423" s="1" t="s">
         <v>456</v>
       </c>
@@ -24513,8 +24860,11 @@
       <c r="O423">
         <v>0</v>
       </c>
-    </row>
-    <row r="424" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P423" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="424" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A424" s="1" t="s">
         <v>457</v>
       </c>
@@ -24560,8 +24910,11 @@
       <c r="O424">
         <v>0</v>
       </c>
-    </row>
-    <row r="425" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P424" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="425" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A425" s="1" t="s">
         <v>458</v>
       </c>
@@ -24607,8 +24960,11 @@
       <c r="O425">
         <v>0</v>
       </c>
-    </row>
-    <row r="426" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P425" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="426" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A426" s="1" t="s">
         <v>459</v>
       </c>
@@ -24654,8 +25010,11 @@
       <c r="O426">
         <v>0</v>
       </c>
-    </row>
-    <row r="427" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P426" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="427" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A427" s="1" t="s">
         <v>460</v>
       </c>
@@ -24701,8 +25060,11 @@
       <c r="O427">
         <v>0</v>
       </c>
-    </row>
-    <row r="428" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P427" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="428" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A428" s="1" t="s">
         <v>461</v>
       </c>
@@ -24748,8 +25110,11 @@
       <c r="O428">
         <v>0</v>
       </c>
-    </row>
-    <row r="429" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P428" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="429" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A429" s="1" t="s">
         <v>462</v>
       </c>
@@ -24795,8 +25160,11 @@
       <c r="O429">
         <v>0</v>
       </c>
-    </row>
-    <row r="430" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P429" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="430" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A430" s="1" t="s">
         <v>463</v>
       </c>
@@ -24842,8 +25210,11 @@
       <c r="O430">
         <v>0</v>
       </c>
-    </row>
-    <row r="431" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P430" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="431" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A431" s="1" t="s">
         <v>464</v>
       </c>
@@ -24889,8 +25260,11 @@
       <c r="O431">
         <v>0</v>
       </c>
-    </row>
-    <row r="432" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P431" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="432" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A432" s="1" t="s">
         <v>465</v>
       </c>
@@ -24936,8 +25310,11 @@
       <c r="O432">
         <v>0</v>
       </c>
-    </row>
-    <row r="433" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P432" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="433" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A433" s="1" t="s">
         <v>466</v>
       </c>
@@ -24983,8 +25360,11 @@
       <c r="O433">
         <v>0</v>
       </c>
-    </row>
-    <row r="434" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P433" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="434" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A434" s="1" t="s">
         <v>467</v>
       </c>
@@ -25030,8 +25410,11 @@
       <c r="O434">
         <v>0</v>
       </c>
-    </row>
-    <row r="435" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P434" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="435" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A435" s="1" t="s">
         <v>468</v>
       </c>
@@ -25077,8 +25460,11 @@
       <c r="O435">
         <v>0</v>
       </c>
-    </row>
-    <row r="436" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P435" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="436" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A436" s="1" t="s">
         <v>469</v>
       </c>
@@ -25124,8 +25510,11 @@
       <c r="O436">
         <v>0</v>
       </c>
-    </row>
-    <row r="437" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P436" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="437" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A437" s="1" t="s">
         <v>470</v>
       </c>
@@ -25171,8 +25560,11 @@
       <c r="O437">
         <v>0</v>
       </c>
-    </row>
-    <row r="438" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P437" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="438" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A438" s="1" t="s">
         <v>471</v>
       </c>
@@ -25218,8 +25610,11 @@
       <c r="O438">
         <v>0</v>
       </c>
-    </row>
-    <row r="439" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P438" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="439" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A439" s="1" t="s">
         <v>472</v>
       </c>
@@ -25265,8 +25660,11 @@
       <c r="O439">
         <v>0</v>
       </c>
-    </row>
-    <row r="440" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P439" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="440" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A440" s="1" t="s">
         <v>473</v>
       </c>
@@ -25312,8 +25710,11 @@
       <c r="O440">
         <v>0</v>
       </c>
-    </row>
-    <row r="441" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P440" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="441" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A441" s="1" t="s">
         <v>474</v>
       </c>
@@ -25359,8 +25760,11 @@
       <c r="O441">
         <v>0</v>
       </c>
-    </row>
-    <row r="442" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P441" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="442" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A442" s="1" t="s">
         <v>475</v>
       </c>
@@ -25406,8 +25810,11 @@
       <c r="O442">
         <v>0</v>
       </c>
-    </row>
-    <row r="443" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P442" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="443" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A443" s="1" t="s">
         <v>476</v>
       </c>
@@ -25453,8 +25860,11 @@
       <c r="O443">
         <v>0</v>
       </c>
-    </row>
-    <row r="444" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P443" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="444" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A444" s="1" t="s">
         <v>477</v>
       </c>
@@ -25500,8 +25910,11 @@
       <c r="O444">
         <v>0</v>
       </c>
-    </row>
-    <row r="445" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P444" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="445" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A445" s="1" t="s">
         <v>478</v>
       </c>
@@ -25547,8 +25960,11 @@
       <c r="O445">
         <v>0</v>
       </c>
-    </row>
-    <row r="446" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P445" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="446" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A446" s="1" t="s">
         <v>479</v>
       </c>
@@ -25594,8 +26010,11 @@
       <c r="O446">
         <v>0</v>
       </c>
-    </row>
-    <row r="447" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P446" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="447" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A447" s="1" t="s">
         <v>480</v>
       </c>
@@ -25641,8 +26060,11 @@
       <c r="O447">
         <v>0</v>
       </c>
-    </row>
-    <row r="448" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P447" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="448" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A448" s="1" t="s">
         <v>481</v>
       </c>
@@ -25688,8 +26110,11 @@
       <c r="O448">
         <v>0</v>
       </c>
-    </row>
-    <row r="449" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P448" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="449" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A449" s="1" t="s">
         <v>482</v>
       </c>
@@ -25735,8 +26160,11 @@
       <c r="O449">
         <v>0</v>
       </c>
-    </row>
-    <row r="450" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P449" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="450" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A450" s="1" t="s">
         <v>483</v>
       </c>
@@ -25782,8 +26210,11 @@
       <c r="O450">
         <v>0</v>
       </c>
-    </row>
-    <row r="451" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P450" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="451" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A451" s="1" t="s">
         <v>484</v>
       </c>
@@ -25829,8 +26260,11 @@
       <c r="O451">
         <v>0</v>
       </c>
-    </row>
-    <row r="452" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P451" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="452" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A452" s="1" t="s">
         <v>485</v>
       </c>
@@ -25876,8 +26310,11 @@
       <c r="O452">
         <v>0</v>
       </c>
-    </row>
-    <row r="453" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P452" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="453" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A453" s="1" t="s">
         <v>486</v>
       </c>
@@ -25923,8 +26360,11 @@
       <c r="O453">
         <v>0</v>
       </c>
-    </row>
-    <row r="454" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P453" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="454" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A454" s="1" t="s">
         <v>487</v>
       </c>
@@ -25970,8 +26410,11 @@
       <c r="O454">
         <v>0</v>
       </c>
-    </row>
-    <row r="455" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P454" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="455" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A455" s="1" t="s">
         <v>488</v>
       </c>
@@ -26017,8 +26460,11 @@
       <c r="O455">
         <v>0</v>
       </c>
-    </row>
-    <row r="456" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P455" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="456" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A456" s="1" t="s">
         <v>489</v>
       </c>
@@ -26064,8 +26510,11 @@
       <c r="O456">
         <v>0</v>
       </c>
-    </row>
-    <row r="457" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P456" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="457" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A457" s="1" t="s">
         <v>490</v>
       </c>
@@ -26111,8 +26560,11 @@
       <c r="O457">
         <v>0</v>
       </c>
-    </row>
-    <row r="458" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P457" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="458" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A458" s="1" t="s">
         <v>491</v>
       </c>
@@ -26158,8 +26610,11 @@
       <c r="O458">
         <v>0</v>
       </c>
-    </row>
-    <row r="459" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P458" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="459" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A459" s="1" t="s">
         <v>492</v>
       </c>
@@ -26205,8 +26660,11 @@
       <c r="O459">
         <v>0</v>
       </c>
-    </row>
-    <row r="460" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P459" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="460" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A460" s="1" t="s">
         <v>493</v>
       </c>
@@ -26252,8 +26710,11 @@
       <c r="O460">
         <v>0</v>
       </c>
-    </row>
-    <row r="461" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P460" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="461" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A461" s="1" t="s">
         <v>494</v>
       </c>
@@ -26299,8 +26760,11 @@
       <c r="O461">
         <v>0</v>
       </c>
-    </row>
-    <row r="462" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P461" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="462" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A462" s="1" t="s">
         <v>495</v>
       </c>
@@ -26346,8 +26810,11 @@
       <c r="O462">
         <v>0</v>
       </c>
-    </row>
-    <row r="463" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P462" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="463" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A463" s="1" t="s">
         <v>496</v>
       </c>
@@ -26393,8 +26860,11 @@
       <c r="O463">
         <v>0</v>
       </c>
-    </row>
-    <row r="464" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P463" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="464" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A464" s="1" t="s">
         <v>497</v>
       </c>
@@ -26440,8 +26910,11 @@
       <c r="O464">
         <v>0</v>
       </c>
-    </row>
-    <row r="465" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P464" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="465" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A465" s="1" t="s">
         <v>498</v>
       </c>
@@ -26487,8 +26960,11 @@
       <c r="O465">
         <v>0</v>
       </c>
-    </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P465" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="466" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A466" s="1" t="s">
         <v>499</v>
       </c>
@@ -26534,8 +27010,11 @@
       <c r="O466">
         <v>0</v>
       </c>
-    </row>
-    <row r="467" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P466" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="467" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A467" s="1" t="s">
         <v>500</v>
       </c>
@@ -26581,8 +27060,11 @@
       <c r="O467">
         <v>0</v>
       </c>
-    </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P467" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="468" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A468" s="1" t="s">
         <v>501</v>
       </c>
@@ -26628,8 +27110,11 @@
       <c r="O468">
         <v>0</v>
       </c>
-    </row>
-    <row r="469" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P468" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="469" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A469" s="1" t="s">
         <v>502</v>
       </c>
@@ -26675,8 +27160,11 @@
       <c r="O469">
         <v>0</v>
       </c>
-    </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P469" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="470" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A470" s="1" t="s">
         <v>503</v>
       </c>
@@ -26722,8 +27210,11 @@
       <c r="O470">
         <v>0</v>
       </c>
-    </row>
-    <row r="471" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P470" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="471" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A471" s="1" t="s">
         <v>504</v>
       </c>
@@ -26769,8 +27260,11 @@
       <c r="O471">
         <v>0</v>
       </c>
-    </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P471" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="472" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A472" s="1" t="s">
         <v>27</v>
       </c>
@@ -26816,8 +27310,11 @@
       <c r="O472">
         <v>0</v>
       </c>
-    </row>
-    <row r="473" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P472" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="473" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A473" s="1" t="s">
         <v>29</v>
       </c>
@@ -26863,8 +27360,11 @@
       <c r="O473">
         <v>0</v>
       </c>
-    </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P473" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="474" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A474" s="1" t="s">
         <v>30</v>
       </c>
@@ -26910,8 +27410,11 @@
       <c r="O474">
         <v>0</v>
       </c>
-    </row>
-    <row r="475" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P474" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="475" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A475" s="1" t="s">
         <v>31</v>
       </c>
@@ -26957,8 +27460,11 @@
       <c r="O475">
         <v>0</v>
       </c>
-    </row>
-    <row r="476" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P475" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="476" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A476" s="1" t="s">
         <v>32</v>
       </c>
@@ -27004,8 +27510,11 @@
       <c r="O476">
         <v>0</v>
       </c>
-    </row>
-    <row r="477" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P476" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="477" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A477" s="1" t="s">
         <v>505</v>
       </c>
@@ -27051,8 +27560,11 @@
       <c r="O477">
         <v>0</v>
       </c>
-    </row>
-    <row r="478" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P477" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="478" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A478" s="1" t="s">
         <v>506</v>
       </c>
@@ -27098,8 +27610,11 @@
       <c r="O478">
         <v>0</v>
       </c>
-    </row>
-    <row r="479" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P478" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="479" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A479" s="1" t="s">
         <v>507</v>
       </c>
@@ -27145,8 +27660,11 @@
       <c r="O479">
         <v>0</v>
       </c>
-    </row>
-    <row r="480" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P479" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="480" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A480" s="1" t="s">
         <v>508</v>
       </c>
@@ -27192,8 +27710,11 @@
       <c r="O480">
         <v>0</v>
       </c>
-    </row>
-    <row r="481" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P480" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="481" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A481" s="1" t="s">
         <v>509</v>
       </c>
@@ -27239,8 +27760,11 @@
       <c r="O481">
         <v>0</v>
       </c>
-    </row>
-    <row r="482" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P481" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="482" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A482" s="1" t="s">
         <v>510</v>
       </c>
@@ -27286,8 +27810,11 @@
       <c r="O482">
         <v>0</v>
       </c>
-    </row>
-    <row r="483" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P482" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="483" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A483" s="1" t="s">
         <v>511</v>
       </c>
@@ -27333,8 +27860,11 @@
       <c r="O483">
         <v>0</v>
       </c>
-    </row>
-    <row r="484" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P483" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="484" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A484" s="1" t="s">
         <v>512</v>
       </c>
@@ -27380,8 +27910,11 @@
       <c r="O484">
         <v>0</v>
       </c>
-    </row>
-    <row r="485" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P484" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="485" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A485" s="1" t="s">
         <v>513</v>
       </c>
@@ -27427,8 +27960,11 @@
       <c r="O485">
         <v>0</v>
       </c>
-    </row>
-    <row r="486" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P485" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="486" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A486" s="1" t="s">
         <v>514</v>
       </c>
@@ -27474,8 +28010,11 @@
       <c r="O486">
         <v>0</v>
       </c>
-    </row>
-    <row r="487" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P486" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="487" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A487" s="1" t="s">
         <v>515</v>
       </c>
@@ -27521,8 +28060,11 @@
       <c r="O487">
         <v>0</v>
       </c>
-    </row>
-    <row r="488" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P487" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="488" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A488" s="1" t="s">
         <v>516</v>
       </c>
@@ -27568,8 +28110,11 @@
       <c r="O488">
         <v>0</v>
       </c>
-    </row>
-    <row r="489" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P488" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="489" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A489" s="1" t="s">
         <v>517</v>
       </c>
@@ -27615,8 +28160,11 @@
       <c r="O489">
         <v>0</v>
       </c>
-    </row>
-    <row r="490" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P489" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="490" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A490" s="1" t="s">
         <v>518</v>
       </c>
@@ -27662,8 +28210,11 @@
       <c r="O490">
         <v>0</v>
       </c>
-    </row>
-    <row r="491" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P490" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="491" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A491" s="1" t="s">
         <v>519</v>
       </c>
@@ -27709,8 +28260,11 @@
       <c r="O491">
         <v>0</v>
       </c>
-    </row>
-    <row r="492" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P491" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="492" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A492" s="1" t="s">
         <v>520</v>
       </c>
@@ -27756,8 +28310,11 @@
       <c r="O492">
         <v>0</v>
       </c>
-    </row>
-    <row r="493" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P492" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="493" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A493" s="1" t="s">
         <v>521</v>
       </c>
@@ -27803,8 +28360,11 @@
       <c r="O493">
         <v>0</v>
       </c>
-    </row>
-    <row r="494" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P493" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="494" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A494" s="1" t="s">
         <v>522</v>
       </c>
@@ -27850,8 +28410,11 @@
       <c r="O494">
         <v>0</v>
       </c>
-    </row>
-    <row r="495" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P494" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="495" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A495" s="1" t="s">
         <v>523</v>
       </c>
@@ -27897,8 +28460,11 @@
       <c r="O495">
         <v>0</v>
       </c>
-    </row>
-    <row r="496" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P495" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="496" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A496" s="1" t="s">
         <v>524</v>
       </c>
@@ -27944,8 +28510,11 @@
       <c r="O496">
         <v>0</v>
       </c>
-    </row>
-    <row r="497" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P496" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="497" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A497" s="1" t="s">
         <v>525</v>
       </c>
@@ -27991,8 +28560,11 @@
       <c r="O497">
         <v>0</v>
       </c>
-    </row>
-    <row r="498" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P497" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="498" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A498" s="1" t="s">
         <v>526</v>
       </c>
@@ -28038,8 +28610,11 @@
       <c r="O498">
         <v>0</v>
       </c>
-    </row>
-    <row r="499" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P498" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="499" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A499" s="1" t="s">
         <v>527</v>
       </c>
@@ -28085,8 +28660,11 @@
       <c r="O499">
         <v>0</v>
       </c>
-    </row>
-    <row r="500" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P499" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="500" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A500" s="1" t="s">
         <v>528</v>
       </c>
@@ -28132,8 +28710,11 @@
       <c r="O500">
         <v>0</v>
       </c>
-    </row>
-    <row r="501" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P500" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="501" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A501" s="1" t="s">
         <v>529</v>
       </c>
@@ -28179,8 +28760,11 @@
       <c r="O501">
         <v>0</v>
       </c>
-    </row>
-    <row r="502" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P501" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="502" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A502" s="1" t="s">
         <v>530</v>
       </c>
@@ -28226,8 +28810,11 @@
       <c r="O502">
         <v>0</v>
       </c>
-    </row>
-    <row r="503" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P502" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="503" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A503" s="1" t="s">
         <v>531</v>
       </c>
@@ -28273,8 +28860,11 @@
       <c r="O503">
         <v>0</v>
       </c>
-    </row>
-    <row r="504" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P503" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="504" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A504" s="1" t="s">
         <v>532</v>
       </c>
@@ -28320,8 +28910,11 @@
       <c r="O504">
         <v>0</v>
       </c>
-    </row>
-    <row r="505" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P504" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="505" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A505" s="1" t="s">
         <v>533</v>
       </c>
@@ -28367,8 +28960,11 @@
       <c r="O505">
         <v>0</v>
       </c>
-    </row>
-    <row r="506" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P505" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="506" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A506" s="1" t="s">
         <v>534</v>
       </c>
@@ -28414,8 +29010,11 @@
       <c r="O506">
         <v>0</v>
       </c>
-    </row>
-    <row r="507" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P506" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="507" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A507" s="1" t="s">
         <v>535</v>
       </c>
@@ -28461,8 +29060,11 @@
       <c r="O507">
         <v>0</v>
       </c>
-    </row>
-    <row r="508" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P507" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="508" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A508" s="1" t="s">
         <v>536</v>
       </c>
@@ -28508,8 +29110,11 @@
       <c r="O508">
         <v>0</v>
       </c>
-    </row>
-    <row r="509" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P508" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="509" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A509" s="1" t="s">
         <v>537</v>
       </c>
@@ -28555,8 +29160,11 @@
       <c r="O509">
         <v>0</v>
       </c>
-    </row>
-    <row r="510" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P509" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="510" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A510" s="1" t="s">
         <v>538</v>
       </c>
@@ -28602,8 +29210,11 @@
       <c r="O510">
         <v>0</v>
       </c>
-    </row>
-    <row r="511" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P510" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="511" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A511" s="1" t="s">
         <v>539</v>
       </c>
@@ -28649,8 +29260,11 @@
       <c r="O511">
         <v>0</v>
       </c>
-    </row>
-    <row r="512" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P511" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="512" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A512" s="1" t="s">
         <v>540</v>
       </c>
@@ -28696,8 +29310,11 @@
       <c r="O512">
         <v>0</v>
       </c>
-    </row>
-    <row r="513" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P512" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="513" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A513" s="1" t="s">
         <v>541</v>
       </c>
@@ -28743,8 +29360,11 @@
       <c r="O513">
         <v>0</v>
       </c>
-    </row>
-    <row r="514" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P513" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="514" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A514" s="1" t="s">
         <v>542</v>
       </c>
@@ -28790,8 +29410,11 @@
       <c r="O514">
         <v>0</v>
       </c>
-    </row>
-    <row r="515" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P514" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="515" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A515" s="1" t="s">
         <v>543</v>
       </c>
@@ -28837,8 +29460,11 @@
       <c r="O515">
         <v>0</v>
       </c>
-    </row>
-    <row r="516" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P515" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="516" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A516" s="1" t="s">
         <v>544</v>
       </c>
@@ -28884,8 +29510,11 @@
       <c r="O516">
         <v>0</v>
       </c>
-    </row>
-    <row r="517" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P516" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="517" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A517" s="1" t="s">
         <v>545</v>
       </c>
@@ -28931,8 +29560,11 @@
       <c r="O517">
         <v>0</v>
       </c>
-    </row>
-    <row r="518" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P517" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="518" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A518" s="1" t="s">
         <v>546</v>
       </c>
@@ -28978,8 +29610,11 @@
       <c r="O518">
         <v>0</v>
       </c>
-    </row>
-    <row r="519" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P518" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="519" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A519" s="1" t="s">
         <v>547</v>
       </c>
@@ -29025,8 +29660,11 @@
       <c r="O519">
         <v>0</v>
       </c>
-    </row>
-    <row r="520" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P519" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="520" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A520" s="1" t="s">
         <v>548</v>
       </c>
@@ -29072,8 +29710,11 @@
       <c r="O520">
         <v>0</v>
       </c>
-    </row>
-    <row r="521" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P520" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="521" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A521" s="1" t="s">
         <v>549</v>
       </c>
@@ -29119,8 +29760,11 @@
       <c r="O521">
         <v>0</v>
       </c>
-    </row>
-    <row r="522" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P521" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="522" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A522" s="1" t="s">
         <v>65</v>
       </c>
@@ -29166,8 +29810,11 @@
       <c r="O522">
         <v>0</v>
       </c>
-    </row>
-    <row r="523" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P522" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="523" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A523" s="1" t="s">
         <v>67</v>
       </c>
@@ -29213,8 +29860,11 @@
       <c r="O523">
         <v>0</v>
       </c>
-    </row>
-    <row r="524" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P523" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="524" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A524" s="1" t="s">
         <v>68</v>
       </c>
@@ -29260,8 +29910,11 @@
       <c r="O524">
         <v>0</v>
       </c>
-    </row>
-    <row r="525" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P524" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="525" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A525" s="1" t="s">
         <v>69</v>
       </c>
@@ -29307,8 +29960,11 @@
       <c r="O525">
         <v>0</v>
       </c>
-    </row>
-    <row r="526" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P525" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="526" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A526" s="1" t="s">
         <v>70</v>
       </c>
@@ -29354,8 +30010,11 @@
       <c r="O526">
         <v>0</v>
       </c>
-    </row>
-    <row r="527" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P526" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="527" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A527" s="1" t="s">
         <v>550</v>
       </c>
@@ -29401,8 +30060,11 @@
       <c r="O527">
         <v>0</v>
       </c>
-    </row>
-    <row r="528" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P527" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="528" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A528" s="1" t="s">
         <v>551</v>
       </c>
@@ -29448,8 +30110,11 @@
       <c r="O528">
         <v>0</v>
       </c>
-    </row>
-    <row r="529" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P528" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="529" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A529" s="1" t="s">
         <v>552</v>
       </c>
@@ -29495,8 +30160,11 @@
       <c r="O529">
         <v>0</v>
       </c>
-    </row>
-    <row r="530" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P529" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="530" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A530" s="1" t="s">
         <v>553</v>
       </c>
@@ -29542,8 +30210,11 @@
       <c r="O530">
         <v>0</v>
       </c>
-    </row>
-    <row r="531" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P530" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="531" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A531" s="1" t="s">
         <v>554</v>
       </c>
@@ -29589,8 +30260,11 @@
       <c r="O531">
         <v>0</v>
       </c>
-    </row>
-    <row r="532" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P531" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="532" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A532" s="1" t="s">
         <v>555</v>
       </c>
@@ -29636,8 +30310,11 @@
       <c r="O532">
         <v>0</v>
       </c>
-    </row>
-    <row r="533" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P532" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="533" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A533" s="1" t="s">
         <v>556</v>
       </c>
@@ -29683,8 +30360,11 @@
       <c r="O533">
         <v>0</v>
       </c>
-    </row>
-    <row r="534" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P533" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="534" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A534" s="1" t="s">
         <v>557</v>
       </c>
@@ -29730,8 +30410,11 @@
       <c r="O534">
         <v>0</v>
       </c>
-    </row>
-    <row r="535" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P534" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="535" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A535" s="1" t="s">
         <v>558</v>
       </c>
@@ -29777,8 +30460,11 @@
       <c r="O535">
         <v>0</v>
       </c>
-    </row>
-    <row r="536" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P535" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="536" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A536" s="1" t="s">
         <v>559</v>
       </c>
@@ -29824,8 +30510,11 @@
       <c r="O536">
         <v>0</v>
       </c>
-    </row>
-    <row r="537" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P536" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="537" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A537" s="1" t="s">
         <v>560</v>
       </c>
@@ -29871,8 +30560,11 @@
       <c r="O537">
         <v>0</v>
       </c>
-    </row>
-    <row r="538" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P537" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="538" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A538" s="1" t="s">
         <v>561</v>
       </c>
@@ -29918,8 +30610,11 @@
       <c r="O538">
         <v>0</v>
       </c>
-    </row>
-    <row r="539" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P538" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="539" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A539" s="1" t="s">
         <v>562</v>
       </c>
@@ -29965,8 +30660,11 @@
       <c r="O539">
         <v>0</v>
       </c>
-    </row>
-    <row r="540" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P539" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="540" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A540" s="1" t="s">
         <v>563</v>
       </c>
@@ -30012,8 +30710,11 @@
       <c r="O540">
         <v>0</v>
       </c>
-    </row>
-    <row r="541" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P540" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="541" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A541" s="1" t="s">
         <v>564</v>
       </c>
@@ -30059,8 +30760,11 @@
       <c r="O541">
         <v>0</v>
       </c>
-    </row>
-    <row r="542" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P541" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="542" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A542" s="1" t="s">
         <v>565</v>
       </c>
@@ -30106,8 +30810,11 @@
       <c r="O542">
         <v>0</v>
       </c>
-    </row>
-    <row r="543" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P542" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="543" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A543" s="1" t="s">
         <v>566</v>
       </c>
@@ -30153,8 +30860,11 @@
       <c r="O543">
         <v>0</v>
       </c>
-    </row>
-    <row r="544" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P543" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="544" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A544" s="1" t="s">
         <v>567</v>
       </c>
@@ -30200,8 +30910,11 @@
       <c r="O544">
         <v>0</v>
       </c>
-    </row>
-    <row r="545" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P544" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="545" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A545" s="1" t="s">
         <v>568</v>
       </c>
@@ -30247,8 +30960,11 @@
       <c r="O545">
         <v>0</v>
       </c>
-    </row>
-    <row r="546" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P545" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="546" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A546" s="1" t="s">
         <v>569</v>
       </c>
@@ -30294,8 +31010,11 @@
       <c r="O546">
         <v>0</v>
       </c>
-    </row>
-    <row r="547" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P546" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="547" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A547" s="1" t="s">
         <v>10</v>
       </c>
@@ -30341,8 +31060,11 @@
       <c r="O547">
         <v>0</v>
       </c>
-    </row>
-    <row r="548" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P547" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="548" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A548" s="1" t="s">
         <v>12</v>
       </c>
@@ -30388,8 +31110,11 @@
       <c r="O548">
         <v>0</v>
       </c>
-    </row>
-    <row r="549" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P548" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="549" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A549" s="1" t="s">
         <v>13</v>
       </c>
@@ -30435,8 +31160,11 @@
       <c r="O549">
         <v>0</v>
       </c>
-    </row>
-    <row r="550" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P549" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="550" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A550" s="1" t="s">
         <v>14</v>
       </c>
@@ -30482,8 +31210,11 @@
       <c r="O550">
         <v>0</v>
       </c>
-    </row>
-    <row r="551" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P550" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="551" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A551" s="1" t="s">
         <v>570</v>
       </c>
@@ -30529,8 +31260,11 @@
       <c r="O551">
         <v>0</v>
       </c>
-    </row>
-    <row r="552" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P551" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="552" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A552" s="1" t="s">
         <v>571</v>
       </c>
@@ -30576,8 +31310,11 @@
       <c r="O552">
         <v>0</v>
       </c>
-    </row>
-    <row r="553" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P552" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="553" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A553" s="1" t="s">
         <v>572</v>
       </c>
@@ -30623,8 +31360,11 @@
       <c r="O553">
         <v>0</v>
       </c>
-    </row>
-    <row r="554" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P553" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="554" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A554" s="1" t="s">
         <v>573</v>
       </c>
@@ -30670,8 +31410,11 @@
       <c r="O554">
         <v>0</v>
       </c>
-    </row>
-    <row r="555" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P554" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="555" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A555" s="1" t="s">
         <v>574</v>
       </c>
@@ -30717,8 +31460,11 @@
       <c r="O555">
         <v>0</v>
       </c>
-    </row>
-    <row r="556" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P555" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="556" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A556" s="1" t="s">
         <v>575</v>
       </c>
@@ -30764,8 +31510,11 @@
       <c r="O556">
         <v>0</v>
       </c>
-    </row>
-    <row r="557" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P556" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="557" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A557" s="1" t="s">
         <v>576</v>
       </c>
@@ -30811,8 +31560,11 @@
       <c r="O557">
         <v>0</v>
       </c>
-    </row>
-    <row r="558" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P557" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="558" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A558" s="1" t="s">
         <v>577</v>
       </c>
@@ -30858,8 +31610,11 @@
       <c r="O558">
         <v>0</v>
       </c>
-    </row>
-    <row r="559" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P558" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="559" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A559" s="1" t="s">
         <v>578</v>
       </c>
@@ -30905,8 +31660,11 @@
       <c r="O559">
         <v>0</v>
       </c>
-    </row>
-    <row r="560" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P559" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="560" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A560" s="1" t="s">
         <v>579</v>
       </c>
@@ -30952,8 +31710,11 @@
       <c r="O560">
         <v>0</v>
       </c>
-    </row>
-    <row r="561" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P560" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="561" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A561" s="1" t="s">
         <v>580</v>
       </c>
@@ -30999,8 +31760,11 @@
       <c r="O561">
         <v>0</v>
       </c>
-    </row>
-    <row r="562" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P561" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="562" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A562" s="1" t="s">
         <v>581</v>
       </c>
@@ -31046,8 +31810,11 @@
       <c r="O562">
         <v>0</v>
       </c>
-    </row>
-    <row r="563" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P562" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="563" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A563" s="1" t="s">
         <v>582</v>
       </c>
@@ -31093,8 +31860,11 @@
       <c r="O563">
         <v>0</v>
       </c>
-    </row>
-    <row r="564" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P563" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="564" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A564" s="1" t="s">
         <v>583</v>
       </c>
@@ -31141,7 +31911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A565" s="1" t="s">
         <v>584</v>
       </c>
@@ -31188,7 +31958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="566" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A566" s="1" t="s">
         <v>585</v>
       </c>
@@ -31235,7 +32005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A567" s="1" t="s">
         <v>586</v>
       </c>
@@ -31282,7 +32052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A568" s="1" t="s">
         <v>587</v>
       </c>
@@ -31329,7 +32099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A569" s="1" t="s">
         <v>588</v>
       </c>
@@ -31376,7 +32146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A570" s="1" t="s">
         <v>589</v>
       </c>
@@ -31423,7 +32193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A571" s="1" t="s">
         <v>590</v>
       </c>
@@ -31470,7 +32240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A572" s="1" t="s">
         <v>591</v>
       </c>
@@ -31517,7 +32287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A573" s="1" t="s">
         <v>592</v>
       </c>
@@ -31564,7 +32334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A574" s="1" t="s">
         <v>593</v>
       </c>
@@ -31611,7 +32381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A575" s="1" t="s">
         <v>594</v>
       </c>
@@ -31658,7 +32428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A576" s="1" t="s">
         <v>595</v>
       </c>
@@ -31705,7 +32475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A577" s="1" t="s">
         <v>596</v>
       </c>
@@ -31752,7 +32522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="578" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A578" s="1" t="s">
         <v>597</v>
       </c>
@@ -31799,7 +32569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="579" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A579" s="1" t="s">
         <v>598</v>
       </c>
@@ -31846,7 +32616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A580" s="1" t="s">
         <v>599</v>
       </c>
@@ -31893,7 +32663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A581" s="1" t="s">
         <v>600</v>
       </c>
@@ -31940,7 +32710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A582" s="1" t="s">
         <v>601</v>
       </c>
@@ -31987,7 +32757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="583" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A583" s="1" t="s">
         <v>602</v>
       </c>
@@ -32034,7 +32804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="584" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A584" s="1" t="s">
         <v>603</v>
       </c>
@@ -32081,7 +32851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A585" s="1" t="s">
         <v>604</v>
       </c>
@@ -32128,7 +32898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="586" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A586" s="1" t="s">
         <v>605</v>
       </c>
@@ -32175,7 +32945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="587" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A587" s="1" t="s">
         <v>606</v>
       </c>
@@ -32222,7 +32992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="588" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A588" s="1" t="s">
         <v>607</v>
       </c>
@@ -32269,7 +33039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="589" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A589" s="1" t="s">
         <v>608</v>
       </c>
@@ -32316,7 +33086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="590" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A590" s="1" t="s">
         <v>609</v>
       </c>
@@ -32363,7 +33133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="591" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A591" s="1" t="s">
         <v>610</v>
       </c>
@@ -32410,7 +33180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A592" s="1" t="s">
         <v>611</v>
       </c>
@@ -32457,7 +33227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A593" s="1" t="s">
         <v>612</v>
       </c>
@@ -32504,7 +33274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A594" s="1" t="s">
         <v>613</v>
       </c>
@@ -32551,7 +33321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="595" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A595" s="1" t="s">
         <v>614</v>
       </c>
@@ -32598,7 +33368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="596" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A596" s="1" t="s">
         <v>615</v>
       </c>
@@ -32645,7 +33415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="597" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A597" s="1" t="s">
         <v>616</v>
       </c>
@@ -32692,7 +33462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A598" s="1" t="s">
         <v>617</v>
       </c>
@@ -32739,7 +33509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="599" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A599" s="1" t="s">
         <v>618</v>
       </c>
@@ -32786,7 +33556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A600" s="1" t="s">
         <v>619</v>
       </c>
@@ -32833,7 +33603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="601" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A601" s="1" t="s">
         <v>620</v>
       </c>
@@ -32880,7 +33650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="602" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A602" s="1" t="s">
         <v>621</v>
       </c>
@@ -32927,7 +33697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A603" s="1" t="s">
         <v>622</v>
       </c>
@@ -32974,7 +33744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="604" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A604" s="1" t="s">
         <v>623</v>
       </c>
@@ -33021,7 +33791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="605" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A605" s="1" t="s">
         <v>624</v>
       </c>
@@ -33068,7 +33838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="606" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A606" s="1" t="s">
         <v>625</v>
       </c>
@@ -33115,7 +33885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A607" s="1" t="s">
         <v>626</v>
       </c>
@@ -33162,7 +33932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="608" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A608" s="1" t="s">
         <v>627</v>
       </c>
@@ -33209,7 +33979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="609" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A609" s="1" t="s">
         <v>628</v>
       </c>
@@ -33256,7 +34026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="610" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A610" s="1" t="s">
         <v>629</v>
       </c>
@@ -33303,7 +34073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="611" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A611" s="1" t="s">
         <v>630</v>
       </c>
@@ -33350,7 +34120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A612" s="1" t="s">
         <v>631</v>
       </c>
@@ -33397,7 +34167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="613" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A613" s="1" t="s">
         <v>632</v>
       </c>
@@ -33444,7 +34214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="614" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A614" s="1" t="s">
         <v>633</v>
       </c>
@@ -33491,7 +34261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="615" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A615" s="1" t="s">
         <v>634</v>
       </c>
@@ -33538,7 +34308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="616" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A616" s="1" t="s">
         <v>635</v>
       </c>
@@ -33585,7 +34355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="617" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A617" s="1" t="s">
         <v>636</v>
       </c>
@@ -33632,7 +34402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="618" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A618" s="1" t="s">
         <v>637</v>
       </c>
@@ -33679,7 +34449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A619" s="1" t="s">
         <v>638</v>
       </c>
@@ -33726,7 +34496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="620" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A620" s="1" t="s">
         <v>639</v>
       </c>
@@ -33773,7 +34543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A621" s="1" t="s">
         <v>640</v>
       </c>
@@ -33820,7 +34590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="622" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A622" s="1" t="s">
         <v>641</v>
       </c>
@@ -33867,7 +34637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="623" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A623" s="1" t="s">
         <v>642</v>
       </c>
@@ -33914,7 +34684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="624" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A624" s="1" t="s">
         <v>643</v>
       </c>
@@ -33961,7 +34731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="625" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A625" s="1" t="s">
         <v>644</v>
       </c>
@@ -34008,7 +34778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="626" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A626" s="1" t="s">
         <v>645</v>
       </c>
@@ -34055,7 +34825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="627" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A627" s="1" t="s">
         <v>646</v>
       </c>
@@ -34102,7 +34872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="628" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A628" s="1" t="s">
         <v>647</v>
       </c>
@@ -34149,7 +34919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="629" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A629" s="1" t="s">
         <v>648</v>
       </c>
@@ -34196,7 +34966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="630" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A630" s="1" t="s">
         <v>649</v>
       </c>
@@ -34243,7 +35013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="631" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A631" s="1" t="s">
         <v>650</v>
       </c>
@@ -34290,7 +35060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="632" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A632" s="1" t="s">
         <v>651</v>
       </c>
@@ -34337,7 +35107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="633" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A633" s="1" t="s">
         <v>652</v>
       </c>
@@ -34384,7 +35154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="634" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A634" s="1" t="s">
         <v>653</v>
       </c>
@@ -34431,7 +35201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="635" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A635" s="1" t="s">
         <v>654</v>
       </c>
@@ -34478,7 +35248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="636" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A636" s="1" t="s">
         <v>655</v>
       </c>
@@ -34525,7 +35295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="637" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A637" s="1" t="s">
         <v>656</v>
       </c>
@@ -34572,7 +35342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="638" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A638" s="1" t="s">
         <v>657</v>
       </c>
@@ -34619,7 +35389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="639" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A639" s="1" t="s">
         <v>658</v>
       </c>
@@ -34666,7 +35436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="640" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A640" s="1" t="s">
         <v>659</v>
       </c>
@@ -34713,7 +35483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="641" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A641" s="1" t="s">
         <v>660</v>
       </c>
@@ -34760,7 +35530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="642" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A642" s="1" t="s">
         <v>661</v>
       </c>
@@ -34807,7 +35577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="643" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A643" s="1" t="s">
         <v>662</v>
       </c>
@@ -34854,7 +35624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="644" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A644" s="1" t="s">
         <v>663</v>
       </c>
@@ -34901,7 +35671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="645" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A645" s="1" t="s">
         <v>664</v>
       </c>
@@ -34948,7 +35718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="646" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A646" s="1" t="s">
         <v>665</v>
       </c>
@@ -34995,7 +35765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="647" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A647" s="1" t="s">
         <v>666</v>
       </c>
@@ -35042,7 +35812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="648" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A648" s="1" t="s">
         <v>563</v>
       </c>
@@ -35089,7 +35859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="649" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A649" s="1" t="s">
         <v>667</v>
       </c>
@@ -35136,7 +35906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="650" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A650" s="1" t="s">
         <v>668</v>
       </c>
@@ -35183,7 +35953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="651" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A651" s="1" t="s">
         <v>669</v>
       </c>
@@ -35230,7 +36000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="652" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A652" s="1" t="s">
         <v>670</v>
       </c>
@@ -35277,7 +36047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="653" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A653" s="1" t="s">
         <v>671</v>
       </c>
@@ -35324,7 +36094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="654" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A654" s="1" t="s">
         <v>672</v>
       </c>
@@ -35371,7 +36141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="655" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A655" s="1" t="s">
         <v>673</v>
       </c>
@@ -35418,7 +36188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="656" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A656" s="1" t="s">
         <v>674</v>
       </c>
@@ -35465,7 +36235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="657" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A657" s="1" t="s">
         <v>675</v>
       </c>
@@ -35512,7 +36282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="658" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A658" s="1" t="s">
         <v>676</v>
       </c>
@@ -35559,7 +36329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="659" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A659" s="1" t="s">
         <v>677</v>
       </c>
@@ -35606,7 +36376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="660" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A660" s="1" t="s">
         <v>678</v>
       </c>
@@ -35653,7 +36423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="661" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A661" s="1" t="s">
         <v>679</v>
       </c>
@@ -35700,7 +36470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="662" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A662" s="1" t="s">
         <v>680</v>
       </c>
@@ -35747,7 +36517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="663" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A663" s="1" t="s">
         <v>681</v>
       </c>
@@ -35794,7 +36564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="664" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A664" s="1" t="s">
         <v>682</v>
       </c>
@@ -35841,7 +36611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="665" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A665" s="1" t="s">
         <v>683</v>
       </c>
@@ -35888,7 +36658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="666" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A666" s="1" t="s">
         <v>684</v>
       </c>
@@ -35935,7 +36705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="667" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A667" s="1" t="s">
         <v>685</v>
       </c>
@@ -35982,7 +36752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="668" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A668" s="1" t="s">
         <v>686</v>
       </c>
@@ -36029,7 +36799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="669" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A669" s="1" t="s">
         <v>687</v>
       </c>
@@ -36076,7 +36846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="670" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A670" s="1" t="s">
         <v>688</v>
       </c>
@@ -36123,7 +36893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="671" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A671" s="1" t="s">
         <v>689</v>
       </c>
@@ -36170,7 +36940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="672" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A672" s="1" t="s">
         <v>690</v>
       </c>
@@ -36217,7 +36987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="673" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A673" s="1" t="s">
         <v>691</v>
       </c>
@@ -36264,7 +37034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="674" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A674" s="1" t="s">
         <v>692</v>
       </c>
@@ -36311,7 +37081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="675" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A675" s="1" t="s">
         <v>693</v>
       </c>
@@ -36358,7 +37128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="676" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A676" s="1" t="s">
         <v>694</v>
       </c>
@@ -36405,7 +37175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="677" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A677" s="1" t="s">
         <v>695</v>
       </c>
@@ -36452,7 +37222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="678" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A678" s="1" t="s">
         <v>696</v>
       </c>
@@ -36499,7 +37269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A679" s="1" t="s">
         <v>697</v>
       </c>
@@ -36546,7 +37316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="680" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A680" s="1" t="s">
         <v>698</v>
       </c>
@@ -36593,7 +37363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="681" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A681" s="1" t="s">
         <v>699</v>
       </c>
@@ -36640,7 +37410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="682" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A682" s="1" t="s">
         <v>700</v>
       </c>
@@ -36687,7 +37457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="683" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A683" s="1" t="s">
         <v>701</v>
       </c>
@@ -36734,7 +37504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="684" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A684" s="1" t="s">
         <v>702</v>
       </c>
@@ -36781,7 +37551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="685" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A685" s="1" t="s">
         <v>703</v>
       </c>
@@ -36828,7 +37598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="686" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A686" s="1" t="s">
         <v>704</v>
       </c>
@@ -36875,7 +37645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="687" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A687" s="1" t="s">
         <v>705</v>
       </c>
@@ -36922,7 +37692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="688" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A688" s="1" t="s">
         <v>706</v>
       </c>
@@ -36969,7 +37739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="689" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A689" s="1" t="s">
         <v>707</v>
       </c>
@@ -37016,7 +37786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="690" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A690" s="1" t="s">
         <v>708</v>
       </c>
@@ -37063,7 +37833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="691" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A691" s="1" t="s">
         <v>709</v>
       </c>
@@ -37110,7 +37880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="692" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A692" s="1" t="s">
         <v>710</v>
       </c>
@@ -37157,7 +37927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="693" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A693" s="1" t="s">
         <v>711</v>
       </c>
@@ -37204,7 +37974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="694" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A694" s="1" t="s">
         <v>712</v>
       </c>
@@ -37251,7 +38021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="695" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A695" s="1" t="s">
         <v>713</v>
       </c>
@@ -37298,7 +38068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="696" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A696" s="1" t="s">
         <v>714</v>
       </c>
@@ -37345,7 +38115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="697" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A697" s="1" t="s">
         <v>715</v>
       </c>
@@ -37392,7 +38162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="698" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A698" s="1" t="s">
         <v>716</v>
       </c>
@@ -37439,7 +38209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="699" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A699" s="1" t="s">
         <v>717</v>
       </c>
@@ -37486,7 +38256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="700" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A700" s="1" t="s">
         <v>718</v>
       </c>
@@ -37533,7 +38303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="701" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A701" s="1" t="s">
         <v>719</v>
       </c>
@@ -37580,7 +38350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="702" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A702" s="1" t="s">
         <v>720</v>
       </c>
@@ -37627,7 +38397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="703" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A703" s="1" t="s">
         <v>721</v>
       </c>
@@ -37674,7 +38444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="704" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A704" s="1" t="s">
         <v>722</v>
       </c>
@@ -37721,7 +38491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="705" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A705" s="1" t="s">
         <v>723</v>
       </c>
@@ -37768,7 +38538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="706" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A706" s="1" t="s">
         <v>724</v>
       </c>
@@ -37815,7 +38585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="707" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A707" s="1" t="s">
         <v>725</v>
       </c>
@@ -37862,7 +38632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="708" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A708" s="1" t="s">
         <v>726</v>
       </c>
@@ -37909,7 +38679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="709" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A709" s="1" t="s">
         <v>727</v>
       </c>
@@ -37956,7 +38726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="710" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A710" s="1" t="s">
         <v>728</v>
       </c>
@@ -38003,7 +38773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="711" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A711" s="1" t="s">
         <v>729</v>
       </c>
@@ -38050,7 +38820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="712" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A712" s="1" t="s">
         <v>730</v>
       </c>
@@ -38097,7 +38867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="713" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A713" s="1" t="s">
         <v>731</v>
       </c>
@@ -38144,7 +38914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="714" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A714" s="1" t="s">
         <v>732</v>
       </c>
@@ -38191,7 +38961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="715" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A715" s="1" t="s">
         <v>733</v>
       </c>
@@ -38238,7 +39008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="716" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A716" s="1" t="s">
         <v>734</v>
       </c>
@@ -38285,7 +39055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="717" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A717" s="1" t="s">
         <v>735</v>
       </c>
@@ -38332,7 +39102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="718" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A718" s="1" t="s">
         <v>736</v>
       </c>
@@ -38379,7 +39149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="719" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A719" s="1" t="s">
         <v>737</v>
       </c>
@@ -38426,7 +39196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="720" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A720" s="1" t="s">
         <v>738</v>
       </c>
@@ -38473,7 +39243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="721" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A721" s="1" t="s">
         <v>739</v>
       </c>
@@ -38520,7 +39290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="722" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A722" s="1" t="s">
         <v>740</v>
       </c>
@@ -38567,7 +39337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="723" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A723" s="1" t="s">
         <v>741</v>
       </c>
@@ -38614,7 +39384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="724" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A724" s="1" t="s">
         <v>742</v>
       </c>
@@ -38661,7 +39431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="725" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A725" s="1" t="s">
         <v>743</v>
       </c>
@@ -38708,7 +39478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="726" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A726" s="1" t="s">
         <v>744</v>
       </c>
@@ -38755,7 +39525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="727" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A727" s="1" t="s">
         <v>745</v>
       </c>
@@ -38802,7 +39572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="728" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A728" s="1" t="s">
         <v>746</v>
       </c>
@@ -38849,7 +39619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="729" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A729" s="1" t="s">
         <v>747</v>
       </c>
@@ -38896,7 +39666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="730" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A730" s="1" t="s">
         <v>748</v>
       </c>
@@ -38943,7 +39713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="731" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A731" s="1" t="s">
         <v>749</v>
       </c>
@@ -38990,7 +39760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="732" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A732" s="1" t="s">
         <v>750</v>
       </c>
@@ -39037,7 +39807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="733" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A733" s="1" t="s">
         <v>751</v>
       </c>
@@ -39084,7 +39854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="734" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A734" s="1" t="s">
         <v>752</v>
       </c>
@@ -39131,7 +39901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="735" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A735" s="1" t="s">
         <v>753</v>
       </c>
@@ -39178,7 +39948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="736" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A736" s="1" t="s">
         <v>67</v>
       </c>
@@ -39225,7 +39995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="737" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A737" s="1" t="s">
         <v>754</v>
       </c>
@@ -39272,7 +40042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="738" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A738" s="1" t="s">
         <v>755</v>
       </c>
@@ -39319,7 +40089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="739" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A739" s="1" t="s">
         <v>756</v>
       </c>
@@ -39366,7 +40136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="740" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A740" s="1" t="s">
         <v>757</v>
       </c>
@@ -39413,7 +40183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="741" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A741" s="1" t="s">
         <v>758</v>
       </c>
@@ -39460,7 +40230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="742" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A742" s="1" t="s">
         <v>759</v>
       </c>
@@ -39507,7 +40277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="743" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A743" s="1" t="s">
         <v>760</v>
       </c>
@@ -39554,7 +40324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="744" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A744" s="1" t="s">
         <v>761</v>
       </c>
@@ -39601,7 +40371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="745" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A745" s="1" t="s">
         <v>762</v>
       </c>
@@ -39648,7 +40418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="746" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A746" s="1" t="s">
         <v>763</v>
       </c>
@@ -39695,7 +40465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="747" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A747" s="1" t="s">
         <v>601</v>
       </c>
@@ -39742,7 +40512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="748" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A748" s="1" t="s">
         <v>602</v>
       </c>
@@ -39789,7 +40559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="749" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A749" s="1" t="s">
         <v>764</v>
       </c>
@@ -39836,7 +40606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="750" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A750" s="1" t="s">
         <v>765</v>
       </c>
@@ -39883,7 +40653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="751" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A751" s="1" t="s">
         <v>766</v>
       </c>
@@ -39930,7 +40700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="752" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A752" s="1" t="s">
         <v>767</v>
       </c>
@@ -39977,7 +40747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="753" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A753" s="1" t="s">
         <v>768</v>
       </c>
@@ -40024,7 +40794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="754" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A754" s="1" t="s">
         <v>769</v>
       </c>
@@ -40071,7 +40841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="755" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A755" s="1" t="s">
         <v>770</v>
       </c>
@@ -40118,7 +40888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="756" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A756" s="1" t="s">
         <v>771</v>
       </c>
@@ -40165,7 +40935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="757" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A757" s="1" t="s">
         <v>772</v>
       </c>
@@ -40212,7 +40982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="758" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A758" s="1" t="s">
         <v>773</v>
       </c>
@@ -40259,7 +41029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="759" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A759" s="1" t="s">
         <v>774</v>
       </c>
@@ -40306,7 +41076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="760" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A760" s="1" t="s">
         <v>775</v>
       </c>
@@ -40353,7 +41123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="761" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A761" s="1" t="s">
         <v>776</v>
       </c>
@@ -40400,7 +41170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="762" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A762" s="1" t="s">
         <v>777</v>
       </c>
@@ -40447,7 +41217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="763" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A763" s="1" t="s">
         <v>778</v>
       </c>
@@ -40494,7 +41264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="764" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A764" s="1" t="s">
         <v>779</v>
       </c>
@@ -40541,7 +41311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="765" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A765" s="1" t="s">
         <v>780</v>
       </c>
@@ -40588,7 +41358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="766" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A766" s="1" t="s">
         <v>781</v>
       </c>
@@ -40635,7 +41405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="767" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A767" s="1" t="s">
         <v>782</v>
       </c>
@@ -40682,7 +41452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="768" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A768" s="1" t="s">
         <v>783</v>
       </c>
@@ -40729,7 +41499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="769" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A769" s="1" t="s">
         <v>784</v>
       </c>
@@ -40776,7 +41546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="770" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A770" s="1" t="s">
         <v>785</v>
       </c>
@@ -40823,7 +41593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="771" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A771" s="1" t="s">
         <v>786</v>
       </c>
@@ -40870,7 +41640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="772" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A772" s="1" t="s">
         <v>787</v>
       </c>
@@ -40917,7 +41687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="773" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A773" s="1" t="s">
         <v>788</v>
       </c>
@@ -40964,7 +41734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="774" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A774" s="1" t="s">
         <v>789</v>
       </c>
@@ -41011,7 +41781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="775" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A775" s="1" t="s">
         <v>790</v>
       </c>
@@ -41058,7 +41828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="776" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A776" s="1" t="s">
         <v>791</v>
       </c>
@@ -41105,7 +41875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="777" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A777" s="1" t="s">
         <v>792</v>
       </c>
@@ -41152,7 +41922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="778" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A778" s="1" t="s">
         <v>793</v>
       </c>
@@ -41199,7 +41969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="779" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A779" s="1" t="s">
         <v>794</v>
       </c>
@@ -41246,7 +42016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="780" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A780" s="1" t="s">
         <v>795</v>
       </c>
@@ -41293,7 +42063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="781" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A781" s="1" t="s">
         <v>796</v>
       </c>
@@ -41340,7 +42110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="782" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A782" s="1" t="s">
         <v>797</v>
       </c>
@@ -41387,7 +42157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="783" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A783" s="1" t="s">
         <v>798</v>
       </c>
@@ -41434,7 +42204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="784" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A784" s="1" t="s">
         <v>799</v>
       </c>
@@ -41481,7 +42251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="785" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A785" s="1" t="s">
         <v>800</v>
       </c>
@@ -41528,7 +42298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="786" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A786" s="1" t="s">
         <v>801</v>
       </c>
@@ -41575,7 +42345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="787" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A787" s="1" t="s">
         <v>802</v>
       </c>
@@ -41622,7 +42392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="788" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A788" s="1" t="s">
         <v>803</v>
       </c>
@@ -41669,7 +42439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="789" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A789" s="1" t="s">
         <v>804</v>
       </c>
@@ -41716,7 +42486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="790" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A790" s="1" t="s">
         <v>805</v>
       </c>
@@ -41763,7 +42533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="791" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A791" s="1" t="s">
         <v>806</v>
       </c>
@@ -41810,7 +42580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="792" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A792" s="1" t="s">
         <v>807</v>
       </c>
@@ -41857,7 +42627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="793" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A793" s="1" t="s">
         <v>808</v>
       </c>
@@ -41904,7 +42674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="794" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A794" s="1" t="s">
         <v>809</v>
       </c>
@@ -41951,7 +42721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="795" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A795" s="1" t="s">
         <v>810</v>
       </c>
@@ -41998,7 +42768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="796" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A796" s="1" t="s">
         <v>811</v>
       </c>
@@ -42045,7 +42815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="797" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A797" s="1" t="s">
         <v>812</v>
       </c>
@@ -42092,7 +42862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="798" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A798" s="1" t="s">
         <v>813</v>
       </c>
@@ -42139,7 +42909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="799" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A799" s="1" t="s">
         <v>814</v>
       </c>
@@ -42186,7 +42956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="800" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A800" s="1" t="s">
         <v>815</v>
       </c>
@@ -42233,7 +43003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="801" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A801" s="1" t="s">
         <v>816</v>
       </c>
@@ -42280,7 +43050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="802" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A802" s="1" t="s">
         <v>817</v>
       </c>
@@ -42327,7 +43097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="803" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A803" s="1" t="s">
         <v>818</v>
       </c>
@@ -42374,7 +43144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="804" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A804" s="1" t="s">
         <v>819</v>
       </c>
@@ -42421,7 +43191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="805" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A805" s="1" t="s">
         <v>820</v>
       </c>
@@ -42468,7 +43238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="806" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A806" s="1" t="s">
         <v>821</v>
       </c>
@@ -42515,7 +43285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="807" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A807" s="1" t="s">
         <v>822</v>
       </c>
@@ -42562,7 +43332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="808" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A808" s="1" t="s">
         <v>823</v>
       </c>
@@ -42609,7 +43379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="809" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A809" s="1" t="s">
         <v>824</v>
       </c>
@@ -42656,7 +43426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="810" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A810" s="1" t="s">
         <v>825</v>
       </c>
@@ -42703,7 +43473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="811" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A811" s="1" t="s">
         <v>826</v>
       </c>
@@ -42750,7 +43520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="812" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A812" s="1" t="s">
         <v>827</v>
       </c>
@@ -42797,7 +43567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="813" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A813" s="1" t="s">
         <v>828</v>
       </c>
@@ -42844,7 +43614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="814" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A814" s="1" t="s">
         <v>829</v>
       </c>
@@ -42891,7 +43661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="815" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A815" s="1" t="s">
         <v>393</v>
       </c>
@@ -42938,7 +43708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="816" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A816" s="1" t="s">
         <v>830</v>
       </c>
@@ -42985,7 +43755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="817" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A817" s="1" t="s">
         <v>831</v>
       </c>
@@ -43032,7 +43802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="818" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A818" s="1" t="s">
         <v>832</v>
       </c>
@@ -43079,7 +43849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="819" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A819" s="1" t="s">
         <v>833</v>
       </c>
@@ -43126,7 +43896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="820" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A820" s="1" t="s">
         <v>834</v>
       </c>
@@ -43173,7 +43943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="821" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A821" s="1" t="s">
         <v>835</v>
       </c>
@@ -43220,7 +43990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="822" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A822" s="1" t="s">
         <v>836</v>
       </c>
@@ -43267,7 +44037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="823" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A823" s="1" t="s">
         <v>837</v>
       </c>
@@ -43314,7 +44084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="824" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A824" s="1" t="s">
         <v>838</v>
       </c>
@@ -43361,7 +44131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="825" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A825" s="1" t="s">
         <v>46</v>
       </c>
@@ -43408,7 +44178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="826" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A826" s="1" t="s">
         <v>839</v>
       </c>
@@ -43455,7 +44225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="827" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A827" s="1" t="s">
         <v>39</v>
       </c>
@@ -43502,7 +44272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="828" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A828" s="1" t="s">
         <v>391</v>
       </c>
@@ -43549,7 +44319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="829" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A829" s="1" t="s">
         <v>392</v>
       </c>
@@ -43596,7 +44366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="830" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A830" t="s">
         <v>1002</v>
       </c>
@@ -43643,7 +44413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="831" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A831" t="s">
         <v>1003</v>
       </c>
@@ -43690,7 +44460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="832" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A832" t="s">
         <v>1004</v>
       </c>
@@ -43737,7 +44507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="833" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A833" t="s">
         <v>1005</v>
       </c>
@@ -43784,7 +44554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="834" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A834" t="s">
         <v>1006</v>
       </c>
@@ -43831,7 +44601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="835" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A835" t="s">
         <v>1007</v>
       </c>
@@ -43878,7 +44648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="836" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A836" t="s">
         <v>1008</v>
       </c>
@@ -43925,7 +44695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="837" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A837" t="s">
         <v>1009</v>
       </c>
@@ -43972,7 +44742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="838" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A838" t="s">
         <v>1010</v>
       </c>
@@ -44019,7 +44789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="839" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A839" t="s">
         <v>1011</v>
       </c>
@@ -44066,7 +44836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="840" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A840" t="s">
         <v>1012</v>
       </c>
@@ -44113,7 +44883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="841" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A841" t="s">
         <v>1013</v>
       </c>
@@ -44160,7 +44930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="842" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A842" t="s">
         <v>1014</v>
       </c>
@@ -44207,7 +44977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="843" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A843" t="s">
         <v>1015</v>
       </c>
@@ -44254,7 +45024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="844" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A844" t="s">
         <v>1016</v>
       </c>
@@ -44301,7 +45071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="845" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A845" t="s">
         <v>1017</v>
       </c>
@@ -44348,7 +45118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="846" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A846" t="s">
         <v>1018</v>
       </c>
@@ -44395,7 +45165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="847" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A847" t="s">
         <v>1019</v>
       </c>
@@ -44442,7 +45212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="848" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A848" t="s">
         <v>1020</v>
       </c>
@@ -44489,7 +45259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="849" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A849" t="s">
         <v>1021</v>
       </c>
@@ -44536,7 +45306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="850" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A850" t="s">
         <v>1022</v>
       </c>
@@ -44583,7 +45353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="851" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A851" t="s">
         <v>1023</v>
       </c>
@@ -44630,7 +45400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="852" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A852" t="s">
         <v>1024</v>
       </c>
@@ -44677,7 +45447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="853" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A853" t="s">
         <v>1025</v>
       </c>
@@ -44724,7 +45494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="854" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A854" t="s">
         <v>1026</v>
       </c>
@@ -44771,7 +45541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="855" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A855" t="s">
         <v>1027</v>
       </c>
@@ -44818,7 +45588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="856" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A856" t="s">
         <v>1028</v>
       </c>
@@ -44865,7 +45635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="857" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A857" t="s">
         <v>1029</v>
       </c>
@@ -44912,7 +45682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="858" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A858" t="s">
         <v>1030</v>
       </c>
@@ -44959,7 +45729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="859" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A859" t="s">
         <v>1031</v>
       </c>
@@ -45006,7 +45776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="860" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A860" t="s">
         <v>1032</v>
       </c>
@@ -45053,7 +45823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="861" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A861" t="s">
         <v>1033</v>
       </c>
@@ -45100,7 +45870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="862" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A862" t="s">
         <v>1034</v>
       </c>
@@ -45147,7 +45917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="863" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A863" t="s">
         <v>1035</v>
       </c>
@@ -45194,7 +45964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="864" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A864" t="s">
         <v>1036</v>
       </c>
@@ -45241,7 +46011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="865" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A865" s="1" t="s">
         <v>1037</v>
       </c>
@@ -45291,7 +46061,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="866" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A866" s="1" t="s">
         <v>1038</v>
       </c>
@@ -45341,7 +46111,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="867" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A867" s="1" t="s">
         <v>1039</v>
       </c>

--- a/file/players_updated.xlsx
+++ b/file/players_updated.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.abraga\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.abraga\Downloads\personal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B85BCC1C-4AB9-406C-9BB4-7D52A817D38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D925DF6E-2F43-49CD-856E-CC63959C5A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3179" uniqueCount="1095">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3480" uniqueCount="1103">
   <si>
     <t>PlayerName</t>
   </si>
@@ -3031,9 +3031,6 @@
     <t>senka</t>
   </si>
   <si>
-    <t>soufly</t>
-  </si>
-  <si>
     <t>AZUWU</t>
   </si>
   <si>
@@ -3305,6 +3302,33 @@
   </si>
   <si>
     <t>Singapore</t>
+  </si>
+  <si>
+    <t>Jordan</t>
+  </si>
+  <si>
+    <t>Lebanon</t>
+  </si>
+  <si>
+    <t>Palestine</t>
+  </si>
+  <si>
+    <t>Ireland</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>United Kingom</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>POland</t>
   </si>
 </sst>
 </file>
@@ -3761,7 +3785,7 @@
         <v>996</v>
       </c>
       <c r="P1" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
@@ -3811,7 +3835,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
@@ -3861,7 +3885,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
@@ -3911,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
@@ -3961,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
@@ -4011,7 +4035,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
@@ -4061,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
@@ -4111,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
@@ -4161,7 +4185,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
@@ -4211,7 +4235,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
@@ -4261,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
@@ -4311,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
@@ -4361,7 +4385,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
@@ -4411,7 +4435,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
@@ -4461,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
@@ -4511,7 +4535,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.35">
@@ -4561,7 +4585,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.35">
@@ -4611,7 +4635,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.35">
@@ -4661,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.35">
@@ -4711,7 +4735,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
@@ -4761,7 +4785,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
@@ -4811,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
@@ -4861,7 +4885,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
@@ -4911,7 +4935,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.35">
@@ -4961,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.35">
@@ -5011,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.35">
@@ -5061,7 +5085,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.35">
@@ -5111,7 +5135,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.35">
@@ -5161,7 +5185,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.35">
@@ -5211,7 +5235,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.35">
@@ -5261,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.35">
@@ -5311,7 +5335,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.35">
@@ -5361,7 +5385,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.35">
@@ -5411,7 +5435,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.35">
@@ -5461,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.35">
@@ -5511,7 +5535,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.35">
@@ -5561,7 +5585,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.35">
@@ -5611,7 +5635,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.35">
@@ -5661,7 +5685,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.35">
@@ -5711,7 +5735,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.35">
@@ -5761,7 +5785,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.35">
@@ -5811,7 +5835,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.35">
@@ -5861,7 +5885,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.35">
@@ -5911,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.35">
@@ -5961,7 +5985,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.35">
@@ -6011,7 +6035,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.35">
@@ -6061,7 +6085,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.35">
@@ -6111,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.35">
@@ -6161,7 +6185,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.35">
@@ -6211,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="P50" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.35">
@@ -6261,7 +6285,7 @@
         <v>0</v>
       </c>
       <c r="P51" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.35">
@@ -6311,7 +6335,7 @@
         <v>0</v>
       </c>
       <c r="P52" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.35">
@@ -6361,7 +6385,7 @@
         <v>0</v>
       </c>
       <c r="P53" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.35">
@@ -6411,7 +6435,7 @@
         <v>0</v>
       </c>
       <c r="P54" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.35">
@@ -6461,7 +6485,7 @@
         <v>0</v>
       </c>
       <c r="P55" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.35">
@@ -6511,7 +6535,7 @@
         <v>0</v>
       </c>
       <c r="P56" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.35">
@@ -6561,7 +6585,7 @@
         <v>0</v>
       </c>
       <c r="P57" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.35">
@@ -6611,7 +6635,7 @@
         <v>0</v>
       </c>
       <c r="P58" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.35">
@@ -6661,7 +6685,7 @@
         <v>0</v>
       </c>
       <c r="P59" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.35">
@@ -6711,7 +6735,7 @@
         <v>0</v>
       </c>
       <c r="P60" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.35">
@@ -6761,7 +6785,7 @@
         <v>0</v>
       </c>
       <c r="P61" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.35">
@@ -6811,7 +6835,7 @@
         <v>0</v>
       </c>
       <c r="P62" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.35">
@@ -6861,7 +6885,7 @@
         <v>0</v>
       </c>
       <c r="P63" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.35">
@@ -6911,7 +6935,7 @@
         <v>0</v>
       </c>
       <c r="P64" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.35">
@@ -6961,7 +6985,7 @@
         <v>0</v>
       </c>
       <c r="P65" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.35">
@@ -7011,7 +7035,7 @@
         <v>0</v>
       </c>
       <c r="P66" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.35">
@@ -7061,7 +7085,7 @@
         <v>0</v>
       </c>
       <c r="P67" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.35">
@@ -7111,7 +7135,7 @@
         <v>0</v>
       </c>
       <c r="P68" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.35">
@@ -7161,7 +7185,7 @@
         <v>0</v>
       </c>
       <c r="P69" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.35">
@@ -7211,7 +7235,7 @@
         <v>0</v>
       </c>
       <c r="P70" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.35">
@@ -7261,7 +7285,7 @@
         <v>0</v>
       </c>
       <c r="P71" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.35">
@@ -7311,7 +7335,7 @@
         <v>0</v>
       </c>
       <c r="P72" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.35">
@@ -7361,7 +7385,7 @@
         <v>0</v>
       </c>
       <c r="P73" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.35">
@@ -7411,7 +7435,7 @@
         <v>0</v>
       </c>
       <c r="P74" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.35">
@@ -7461,7 +7485,7 @@
         <v>0</v>
       </c>
       <c r="P75" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.35">
@@ -7511,7 +7535,7 @@
         <v>0</v>
       </c>
       <c r="P76" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.35">
@@ -7561,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="P77" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.35">
@@ -7611,7 +7635,7 @@
         <v>0</v>
       </c>
       <c r="P78" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.35">
@@ -7661,7 +7685,7 @@
         <v>0</v>
       </c>
       <c r="P79" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.35">
@@ -7711,7 +7735,7 @@
         <v>0</v>
       </c>
       <c r="P80" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.35">
@@ -7761,7 +7785,7 @@
         <v>0</v>
       </c>
       <c r="P81" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.35">
@@ -7811,7 +7835,7 @@
         <v>0</v>
       </c>
       <c r="P82" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.35">
@@ -7861,7 +7885,7 @@
         <v>0</v>
       </c>
       <c r="P83" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.35">
@@ -7911,7 +7935,7 @@
         <v>0</v>
       </c>
       <c r="P84" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.35">
@@ -7961,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="P85" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.35">
@@ -8011,7 +8035,7 @@
         <v>0</v>
       </c>
       <c r="P86" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.35">
@@ -8061,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="P87" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.35">
@@ -8111,7 +8135,7 @@
         <v>0</v>
       </c>
       <c r="P88" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.35">
@@ -8161,7 +8185,7 @@
         <v>0</v>
       </c>
       <c r="P89" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.35">
@@ -8211,7 +8235,7 @@
         <v>0</v>
       </c>
       <c r="P90" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.35">
@@ -8261,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="P91" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.35">
@@ -8311,7 +8335,7 @@
         <v>0</v>
       </c>
       <c r="P92" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.35">
@@ -8361,7 +8385,7 @@
         <v>0</v>
       </c>
       <c r="P93" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.35">
@@ -8411,7 +8435,7 @@
         <v>0</v>
       </c>
       <c r="P94" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.35">
@@ -8461,7 +8485,7 @@
         <v>0</v>
       </c>
       <c r="P95" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.35">
@@ -8511,7 +8535,7 @@
         <v>0</v>
       </c>
       <c r="P96" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.35">
@@ -8561,7 +8585,7 @@
         <v>0</v>
       </c>
       <c r="P97" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.35">
@@ -8611,7 +8635,7 @@
         <v>0</v>
       </c>
       <c r="P98" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.35">
@@ -8661,7 +8685,7 @@
         <v>0</v>
       </c>
       <c r="P99" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.35">
@@ -8711,7 +8735,7 @@
         <v>0</v>
       </c>
       <c r="P100" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.35">
@@ -8761,7 +8785,7 @@
         <v>0</v>
       </c>
       <c r="P101" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.35">
@@ -8811,7 +8835,7 @@
         <v>0</v>
       </c>
       <c r="P102" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.35">
@@ -8861,7 +8885,7 @@
         <v>0</v>
       </c>
       <c r="P103" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.35">
@@ -8911,7 +8935,7 @@
         <v>0</v>
       </c>
       <c r="P104" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.35">
@@ -8961,7 +8985,7 @@
         <v>0</v>
       </c>
       <c r="P105" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.35">
@@ -9011,7 +9035,7 @@
         <v>0</v>
       </c>
       <c r="P106" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.35">
@@ -9061,7 +9085,7 @@
         <v>0</v>
       </c>
       <c r="P107" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.35">
@@ -9111,7 +9135,7 @@
         <v>0</v>
       </c>
       <c r="P108" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.35">
@@ -9161,7 +9185,7 @@
         <v>0</v>
       </c>
       <c r="P109" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.35">
@@ -9211,7 +9235,7 @@
         <v>0</v>
       </c>
       <c r="P110" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.35">
@@ -9261,7 +9285,7 @@
         <v>0</v>
       </c>
       <c r="P111" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.35">
@@ -9311,7 +9335,7 @@
         <v>0</v>
       </c>
       <c r="P112" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.35">
@@ -9361,7 +9385,7 @@
         <v>0</v>
       </c>
       <c r="P113" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.35">
@@ -9411,7 +9435,7 @@
         <v>0</v>
       </c>
       <c r="P114" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.35">
@@ -9461,7 +9485,7 @@
         <v>0</v>
       </c>
       <c r="P115" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.35">
@@ -9511,7 +9535,7 @@
         <v>0</v>
       </c>
       <c r="P116" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.35">
@@ -9561,7 +9585,7 @@
         <v>0</v>
       </c>
       <c r="P117" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.35">
@@ -9611,7 +9635,7 @@
         <v>0</v>
       </c>
       <c r="P118" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.35">
@@ -9661,7 +9685,7 @@
         <v>0</v>
       </c>
       <c r="P119" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.35">
@@ -9711,7 +9735,7 @@
         <v>0</v>
       </c>
       <c r="P120" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.35">
@@ -9761,7 +9785,7 @@
         <v>0</v>
       </c>
       <c r="P121" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.35">
@@ -9811,7 +9835,7 @@
         <v>0</v>
       </c>
       <c r="P122" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.35">
@@ -9861,7 +9885,7 @@
         <v>0</v>
       </c>
       <c r="P123" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.35">
@@ -9911,7 +9935,7 @@
         <v>0</v>
       </c>
       <c r="P124" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.35">
@@ -9961,7 +9985,7 @@
         <v>0</v>
       </c>
       <c r="P125" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.35">
@@ -10011,7 +10035,7 @@
         <v>0</v>
       </c>
       <c r="P126" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.35">
@@ -10061,7 +10085,7 @@
         <v>0</v>
       </c>
       <c r="P127" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.35">
@@ -10111,7 +10135,7 @@
         <v>0</v>
       </c>
       <c r="P128" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.35">
@@ -10161,7 +10185,7 @@
         <v>0</v>
       </c>
       <c r="P129" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.35">
@@ -10211,7 +10235,7 @@
         <v>0</v>
       </c>
       <c r="P130" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.35">
@@ -10261,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="P131" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.35">
@@ -10311,7 +10335,7 @@
         <v>0</v>
       </c>
       <c r="P132" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.35">
@@ -10361,7 +10385,7 @@
         <v>0</v>
       </c>
       <c r="P133" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.35">
@@ -10411,7 +10435,7 @@
         <v>0</v>
       </c>
       <c r="P134" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.35">
@@ -10461,7 +10485,7 @@
         <v>0</v>
       </c>
       <c r="P135" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.35">
@@ -10511,7 +10535,7 @@
         <v>0</v>
       </c>
       <c r="P136" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.35">
@@ -10561,7 +10585,7 @@
         <v>0</v>
       </c>
       <c r="P137" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.35">
@@ -10611,7 +10635,7 @@
         <v>0</v>
       </c>
       <c r="P138" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.35">
@@ -10661,7 +10685,7 @@
         <v>0</v>
       </c>
       <c r="P139" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.35">
@@ -10711,7 +10735,7 @@
         <v>0</v>
       </c>
       <c r="P140" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.35">
@@ -10761,7 +10785,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.35">
@@ -10811,7 +10835,7 @@
         <v>0</v>
       </c>
       <c r="P142" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.35">
@@ -10861,7 +10885,7 @@
         <v>0</v>
       </c>
       <c r="P143" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.35">
@@ -10911,7 +10935,7 @@
         <v>0</v>
       </c>
       <c r="P144" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.35">
@@ -10961,7 +10985,7 @@
         <v>0</v>
       </c>
       <c r="P145" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="146" spans="1:16" x14ac:dyDescent="0.35">
@@ -11011,7 +11035,7 @@
         <v>0</v>
       </c>
       <c r="P146" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="147" spans="1:16" x14ac:dyDescent="0.35">
@@ -11061,7 +11085,7 @@
         <v>0</v>
       </c>
       <c r="P147" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="148" spans="1:16" x14ac:dyDescent="0.35">
@@ -11111,7 +11135,7 @@
         <v>0</v>
       </c>
       <c r="P148" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.35">
@@ -11161,7 +11185,7 @@
         <v>0</v>
       </c>
       <c r="P149" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="150" spans="1:16" x14ac:dyDescent="0.35">
@@ -11211,7 +11235,7 @@
         <v>0</v>
       </c>
       <c r="P150" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.35">
@@ -11261,7 +11285,7 @@
         <v>0</v>
       </c>
       <c r="P151" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.35">
@@ -11311,7 +11335,7 @@
         <v>0</v>
       </c>
       <c r="P152" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.35">
@@ -11361,7 +11385,7 @@
         <v>0</v>
       </c>
       <c r="P153" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.35">
@@ -11411,7 +11435,7 @@
         <v>0</v>
       </c>
       <c r="P154" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.35">
@@ -11461,7 +11485,7 @@
         <v>0</v>
       </c>
       <c r="P155" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.35">
@@ -11511,7 +11535,7 @@
         <v>0</v>
       </c>
       <c r="P156" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.35">
@@ -11561,7 +11585,7 @@
         <v>0</v>
       </c>
       <c r="P157" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.35">
@@ -11611,7 +11635,7 @@
         <v>0</v>
       </c>
       <c r="P158" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.35">
@@ -11661,7 +11685,7 @@
         <v>0</v>
       </c>
       <c r="P159" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.35">
@@ -11711,7 +11735,7 @@
         <v>0</v>
       </c>
       <c r="P160" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="161" spans="1:16" x14ac:dyDescent="0.35">
@@ -11761,7 +11785,7 @@
         <v>0</v>
       </c>
       <c r="P161" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="162" spans="1:16" x14ac:dyDescent="0.35">
@@ -11811,7 +11835,7 @@
         <v>0</v>
       </c>
       <c r="P162" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="163" spans="1:16" x14ac:dyDescent="0.35">
@@ -11861,7 +11885,7 @@
         <v>0</v>
       </c>
       <c r="P163" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="164" spans="1:16" x14ac:dyDescent="0.35">
@@ -11911,7 +11935,7 @@
         <v>0</v>
       </c>
       <c r="P164" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="165" spans="1:16" x14ac:dyDescent="0.35">
@@ -11961,7 +11985,7 @@
         <v>0</v>
       </c>
       <c r="P165" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="166" spans="1:16" x14ac:dyDescent="0.35">
@@ -12011,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="P166" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="167" spans="1:16" x14ac:dyDescent="0.35">
@@ -12061,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="P167" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="168" spans="1:16" x14ac:dyDescent="0.35">
@@ -12111,7 +12135,7 @@
         <v>0</v>
       </c>
       <c r="P168" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="169" spans="1:16" x14ac:dyDescent="0.35">
@@ -12161,7 +12185,7 @@
         <v>0</v>
       </c>
       <c r="P169" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="170" spans="1:16" x14ac:dyDescent="0.35">
@@ -12211,7 +12235,7 @@
         <v>0</v>
       </c>
       <c r="P170" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="171" spans="1:16" x14ac:dyDescent="0.35">
@@ -12261,7 +12285,7 @@
         <v>0</v>
       </c>
       <c r="P171" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="172" spans="1:16" x14ac:dyDescent="0.35">
@@ -12311,7 +12335,7 @@
         <v>0</v>
       </c>
       <c r="P172" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="173" spans="1:16" x14ac:dyDescent="0.35">
@@ -12361,7 +12385,7 @@
         <v>0</v>
       </c>
       <c r="P173" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="174" spans="1:16" x14ac:dyDescent="0.35">
@@ -12411,7 +12435,7 @@
         <v>0</v>
       </c>
       <c r="P174" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="175" spans="1:16" x14ac:dyDescent="0.35">
@@ -12461,7 +12485,7 @@
         <v>0</v>
       </c>
       <c r="P175" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="176" spans="1:16" x14ac:dyDescent="0.35">
@@ -12511,7 +12535,7 @@
         <v>0</v>
       </c>
       <c r="P176" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="177" spans="1:16" x14ac:dyDescent="0.35">
@@ -12561,7 +12585,7 @@
         <v>0</v>
       </c>
       <c r="P177" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="178" spans="1:16" x14ac:dyDescent="0.35">
@@ -12611,7 +12635,7 @@
         <v>0</v>
       </c>
       <c r="P178" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="179" spans="1:16" x14ac:dyDescent="0.35">
@@ -12661,7 +12685,7 @@
         <v>0</v>
       </c>
       <c r="P179" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="180" spans="1:16" x14ac:dyDescent="0.35">
@@ -12711,7 +12735,7 @@
         <v>0</v>
       </c>
       <c r="P180" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="181" spans="1:16" x14ac:dyDescent="0.35">
@@ -12761,7 +12785,7 @@
         <v>0</v>
       </c>
       <c r="P181" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="182" spans="1:16" x14ac:dyDescent="0.35">
@@ -12811,7 +12835,7 @@
         <v>0</v>
       </c>
       <c r="P182" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="183" spans="1:16" x14ac:dyDescent="0.35">
@@ -12861,7 +12885,7 @@
         <v>0</v>
       </c>
       <c r="P183" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="184" spans="1:16" x14ac:dyDescent="0.35">
@@ -12911,7 +12935,7 @@
         <v>0</v>
       </c>
       <c r="P184" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="185" spans="1:16" x14ac:dyDescent="0.35">
@@ -12961,7 +12985,7 @@
         <v>0</v>
       </c>
       <c r="P185" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.35">
@@ -13011,7 +13035,7 @@
         <v>0</v>
       </c>
       <c r="P186" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="187" spans="1:16" x14ac:dyDescent="0.35">
@@ -13061,7 +13085,7 @@
         <v>0</v>
       </c>
       <c r="P187" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="188" spans="1:16" x14ac:dyDescent="0.35">
@@ -13111,7 +13135,7 @@
         <v>0</v>
       </c>
       <c r="P188" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="189" spans="1:16" x14ac:dyDescent="0.35">
@@ -13161,7 +13185,7 @@
         <v>0</v>
       </c>
       <c r="P189" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="190" spans="1:16" x14ac:dyDescent="0.35">
@@ -13211,7 +13235,7 @@
         <v>0</v>
       </c>
       <c r="P190" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="191" spans="1:16" x14ac:dyDescent="0.35">
@@ -13261,7 +13285,7 @@
         <v>0</v>
       </c>
       <c r="P191" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="192" spans="1:16" x14ac:dyDescent="0.35">
@@ -13311,7 +13335,7 @@
         <v>0</v>
       </c>
       <c r="P192" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="193" spans="1:16" x14ac:dyDescent="0.35">
@@ -13361,7 +13385,7 @@
         <v>0</v>
       </c>
       <c r="P193" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="194" spans="1:16" x14ac:dyDescent="0.35">
@@ -13411,7 +13435,7 @@
         <v>0</v>
       </c>
       <c r="P194" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="195" spans="1:16" x14ac:dyDescent="0.35">
@@ -13461,7 +13485,7 @@
         <v>0</v>
       </c>
       <c r="P195" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="196" spans="1:16" x14ac:dyDescent="0.35">
@@ -13511,7 +13535,7 @@
         <v>0</v>
       </c>
       <c r="P196" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="197" spans="1:16" x14ac:dyDescent="0.35">
@@ -13561,7 +13585,7 @@
         <v>0</v>
       </c>
       <c r="P197" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="198" spans="1:16" x14ac:dyDescent="0.35">
@@ -13611,7 +13635,7 @@
         <v>0</v>
       </c>
       <c r="P198" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="199" spans="1:16" x14ac:dyDescent="0.35">
@@ -13661,7 +13685,7 @@
         <v>0</v>
       </c>
       <c r="P199" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.35">
@@ -13711,7 +13735,7 @@
         <v>0</v>
       </c>
       <c r="P200" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="201" spans="1:16" x14ac:dyDescent="0.35">
@@ -13761,7 +13785,7 @@
         <v>0</v>
       </c>
       <c r="P201" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.35">
@@ -13811,7 +13835,7 @@
         <v>0</v>
       </c>
       <c r="P202" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.35">
@@ -13861,7 +13885,7 @@
         <v>0</v>
       </c>
       <c r="P203" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.35">
@@ -13911,7 +13935,7 @@
         <v>0</v>
       </c>
       <c r="P204" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="205" spans="1:16" x14ac:dyDescent="0.35">
@@ -13961,7 +13985,7 @@
         <v>0</v>
       </c>
       <c r="P205" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.35">
@@ -14011,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="P206" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.35">
@@ -14061,7 +14085,7 @@
         <v>0</v>
       </c>
       <c r="P207" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.35">
@@ -14111,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="P208" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.35">
@@ -14161,7 +14185,7 @@
         <v>0</v>
       </c>
       <c r="P209" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.35">
@@ -14211,7 +14235,7 @@
         <v>0</v>
       </c>
       <c r="P210" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.35">
@@ -14261,7 +14285,7 @@
         <v>0</v>
       </c>
       <c r="P211" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.35">
@@ -14311,7 +14335,7 @@
         <v>0</v>
       </c>
       <c r="P212" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.35">
@@ -14361,7 +14385,7 @@
         <v>0</v>
       </c>
       <c r="P213" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.35">
@@ -14411,7 +14435,7 @@
         <v>0</v>
       </c>
       <c r="P214" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="215" spans="1:16" x14ac:dyDescent="0.35">
@@ -14461,7 +14485,7 @@
         <v>0</v>
       </c>
       <c r="P215" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.35">
@@ -14511,7 +14535,7 @@
         <v>0</v>
       </c>
       <c r="P216" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.35">
@@ -14561,7 +14585,7 @@
         <v>0</v>
       </c>
       <c r="P217" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.35">
@@ -14611,7 +14635,7 @@
         <v>0</v>
       </c>
       <c r="P218" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.35">
@@ -14661,7 +14685,7 @@
         <v>0</v>
       </c>
       <c r="P219" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.35">
@@ -14711,7 +14735,7 @@
         <v>0</v>
       </c>
       <c r="P220" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.35">
@@ -14761,7 +14785,7 @@
         <v>0</v>
       </c>
       <c r="P221" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="222" spans="1:16" x14ac:dyDescent="0.35">
@@ -14811,7 +14835,7 @@
         <v>0</v>
       </c>
       <c r="P222" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="223" spans="1:16" x14ac:dyDescent="0.35">
@@ -14861,7 +14885,7 @@
         <v>0</v>
       </c>
       <c r="P223" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="224" spans="1:16" x14ac:dyDescent="0.35">
@@ -14911,7 +14935,7 @@
         <v>0</v>
       </c>
       <c r="P224" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="225" spans="1:16" x14ac:dyDescent="0.35">
@@ -14961,7 +14985,7 @@
         <v>0</v>
       </c>
       <c r="P225" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="226" spans="1:16" x14ac:dyDescent="0.35">
@@ -15011,7 +15035,7 @@
         <v>0</v>
       </c>
       <c r="P226" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="227" spans="1:16" x14ac:dyDescent="0.35">
@@ -15061,7 +15085,7 @@
         <v>0</v>
       </c>
       <c r="P227" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="228" spans="1:16" x14ac:dyDescent="0.35">
@@ -15111,7 +15135,7 @@
         <v>0</v>
       </c>
       <c r="P228" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="229" spans="1:16" x14ac:dyDescent="0.35">
@@ -15161,7 +15185,7 @@
         <v>0</v>
       </c>
       <c r="P229" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="230" spans="1:16" x14ac:dyDescent="0.35">
@@ -15211,7 +15235,7 @@
         <v>0</v>
       </c>
       <c r="P230" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="231" spans="1:16" x14ac:dyDescent="0.35">
@@ -15261,7 +15285,7 @@
         <v>0</v>
       </c>
       <c r="P231" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.35">
@@ -15311,7 +15335,7 @@
         <v>0</v>
       </c>
       <c r="P232" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.35">
@@ -15361,7 +15385,7 @@
         <v>0</v>
       </c>
       <c r="P233" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="234" spans="1:16" x14ac:dyDescent="0.35">
@@ -15411,7 +15435,7 @@
         <v>0</v>
       </c>
       <c r="P234" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="235" spans="1:16" x14ac:dyDescent="0.35">
@@ -15461,7 +15485,7 @@
         <v>0</v>
       </c>
       <c r="P235" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="236" spans="1:16" x14ac:dyDescent="0.35">
@@ -15511,7 +15535,7 @@
         <v>0</v>
       </c>
       <c r="P236" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="237" spans="1:16" x14ac:dyDescent="0.35">
@@ -15561,7 +15585,7 @@
         <v>0</v>
       </c>
       <c r="P237" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="238" spans="1:16" x14ac:dyDescent="0.35">
@@ -15611,7 +15635,7 @@
         <v>0</v>
       </c>
       <c r="P238" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.35">
@@ -15661,7 +15685,7 @@
         <v>0</v>
       </c>
       <c r="P239" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="240" spans="1:16" x14ac:dyDescent="0.35">
@@ -15711,7 +15735,7 @@
         <v>0</v>
       </c>
       <c r="P240" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.35">
@@ -15761,7 +15785,7 @@
         <v>0</v>
       </c>
       <c r="P241" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.35">
@@ -15811,7 +15835,7 @@
         <v>0</v>
       </c>
       <c r="P242" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.35">
@@ -15861,7 +15885,7 @@
         <v>0</v>
       </c>
       <c r="P243" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.35">
@@ -15911,7 +15935,7 @@
         <v>0</v>
       </c>
       <c r="P244" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="245" spans="1:16" x14ac:dyDescent="0.35">
@@ -15961,7 +15985,7 @@
         <v>0</v>
       </c>
       <c r="P245" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.35">
@@ -16011,7 +16035,7 @@
         <v>0</v>
       </c>
       <c r="P246" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.35">
@@ -16061,7 +16085,7 @@
         <v>0</v>
       </c>
       <c r="P247" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.35">
@@ -16111,7 +16135,7 @@
         <v>0</v>
       </c>
       <c r="P248" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.35">
@@ -16161,7 +16185,7 @@
         <v>0</v>
       </c>
       <c r="P249" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.35">
@@ -16211,7 +16235,7 @@
         <v>0</v>
       </c>
       <c r="P250" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.35">
@@ -16261,7 +16285,7 @@
         <v>0</v>
       </c>
       <c r="P251" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.35">
@@ -16311,7 +16335,7 @@
         <v>0</v>
       </c>
       <c r="P252" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.35">
@@ -16361,7 +16385,7 @@
         <v>0</v>
       </c>
       <c r="P253" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="254" spans="1:16" x14ac:dyDescent="0.35">
@@ -16411,7 +16435,7 @@
         <v>0</v>
       </c>
       <c r="P254" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.35">
@@ -16461,7 +16485,7 @@
         <v>0</v>
       </c>
       <c r="P255" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.35">
@@ -16511,7 +16535,7 @@
         <v>0</v>
       </c>
       <c r="P256" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="257" spans="1:16" x14ac:dyDescent="0.35">
@@ -16561,7 +16585,7 @@
         <v>0</v>
       </c>
       <c r="P257" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="258" spans="1:16" x14ac:dyDescent="0.35">
@@ -16611,7 +16635,7 @@
         <v>0</v>
       </c>
       <c r="P258" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="259" spans="1:16" x14ac:dyDescent="0.35">
@@ -16661,7 +16685,7 @@
         <v>0</v>
       </c>
       <c r="P259" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="260" spans="1:16" x14ac:dyDescent="0.35">
@@ -16711,7 +16735,7 @@
         <v>0</v>
       </c>
       <c r="P260" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="261" spans="1:16" x14ac:dyDescent="0.35">
@@ -16761,7 +16785,7 @@
         <v>0</v>
       </c>
       <c r="P261" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="262" spans="1:16" x14ac:dyDescent="0.35">
@@ -16811,7 +16835,7 @@
         <v>0</v>
       </c>
       <c r="P262" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="263" spans="1:16" x14ac:dyDescent="0.35">
@@ -16861,7 +16885,7 @@
         <v>0</v>
       </c>
       <c r="P263" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="264" spans="1:16" x14ac:dyDescent="0.35">
@@ -16911,7 +16935,7 @@
         <v>0</v>
       </c>
       <c r="P264" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="265" spans="1:16" x14ac:dyDescent="0.35">
@@ -16961,7 +16985,7 @@
         <v>0</v>
       </c>
       <c r="P265" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="266" spans="1:16" x14ac:dyDescent="0.35">
@@ -17011,7 +17035,7 @@
         <v>0</v>
       </c>
       <c r="P266" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="267" spans="1:16" x14ac:dyDescent="0.35">
@@ -17061,7 +17085,7 @@
         <v>0</v>
       </c>
       <c r="P267" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="268" spans="1:16" x14ac:dyDescent="0.35">
@@ -17111,7 +17135,7 @@
         <v>0</v>
       </c>
       <c r="P268" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="269" spans="1:16" x14ac:dyDescent="0.35">
@@ -17161,7 +17185,7 @@
         <v>0</v>
       </c>
       <c r="P269" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="270" spans="1:16" x14ac:dyDescent="0.35">
@@ -17211,7 +17235,7 @@
         <v>0</v>
       </c>
       <c r="P270" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="271" spans="1:16" x14ac:dyDescent="0.35">
@@ -17261,7 +17285,7 @@
         <v>0</v>
       </c>
       <c r="P271" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="272" spans="1:16" x14ac:dyDescent="0.35">
@@ -17311,7 +17335,7 @@
         <v>0</v>
       </c>
       <c r="P272" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="273" spans="1:16" x14ac:dyDescent="0.35">
@@ -17361,7 +17385,7 @@
         <v>0</v>
       </c>
       <c r="P273" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="274" spans="1:16" x14ac:dyDescent="0.35">
@@ -17411,7 +17435,7 @@
         <v>0</v>
       </c>
       <c r="P274" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="275" spans="1:16" x14ac:dyDescent="0.35">
@@ -17461,7 +17485,7 @@
         <v>0</v>
       </c>
       <c r="P275" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="276" spans="1:16" x14ac:dyDescent="0.35">
@@ -17511,7 +17535,7 @@
         <v>0</v>
       </c>
       <c r="P276" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="277" spans="1:16" x14ac:dyDescent="0.35">
@@ -17561,7 +17585,7 @@
         <v>0</v>
       </c>
       <c r="P277" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="278" spans="1:16" x14ac:dyDescent="0.35">
@@ -17611,7 +17635,7 @@
         <v>0</v>
       </c>
       <c r="P278" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="279" spans="1:16" x14ac:dyDescent="0.35">
@@ -17661,7 +17685,7 @@
         <v>0</v>
       </c>
       <c r="P279" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="280" spans="1:16" x14ac:dyDescent="0.35">
@@ -17711,7 +17735,7 @@
         <v>0</v>
       </c>
       <c r="P280" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="281" spans="1:16" x14ac:dyDescent="0.35">
@@ -17761,7 +17785,7 @@
         <v>0</v>
       </c>
       <c r="P281" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="282" spans="1:16" x14ac:dyDescent="0.35">
@@ -17811,7 +17835,7 @@
         <v>0</v>
       </c>
       <c r="P282" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="283" spans="1:16" x14ac:dyDescent="0.35">
@@ -17861,7 +17885,7 @@
         <v>0</v>
       </c>
       <c r="P283" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="284" spans="1:16" x14ac:dyDescent="0.35">
@@ -17911,7 +17935,7 @@
         <v>0</v>
       </c>
       <c r="P284" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="285" spans="1:16" x14ac:dyDescent="0.35">
@@ -17961,7 +17985,7 @@
         <v>0</v>
       </c>
       <c r="P285" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="286" spans="1:16" x14ac:dyDescent="0.35">
@@ -18011,7 +18035,7 @@
         <v>0</v>
       </c>
       <c r="P286" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="287" spans="1:16" x14ac:dyDescent="0.35">
@@ -18061,7 +18085,7 @@
         <v>0</v>
       </c>
       <c r="P287" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="288" spans="1:16" x14ac:dyDescent="0.35">
@@ -18111,7 +18135,7 @@
         <v>0</v>
       </c>
       <c r="P288" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="289" spans="1:16" x14ac:dyDescent="0.35">
@@ -18161,7 +18185,7 @@
         <v>0</v>
       </c>
       <c r="P289" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="290" spans="1:16" x14ac:dyDescent="0.35">
@@ -18211,7 +18235,7 @@
         <v>0</v>
       </c>
       <c r="P290" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="291" spans="1:16" x14ac:dyDescent="0.35">
@@ -18261,7 +18285,7 @@
         <v>0</v>
       </c>
       <c r="P291" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="292" spans="1:16" x14ac:dyDescent="0.35">
@@ -18311,7 +18335,7 @@
         <v>0</v>
       </c>
       <c r="P292" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="293" spans="1:16" x14ac:dyDescent="0.35">
@@ -18361,7 +18385,7 @@
         <v>0</v>
       </c>
       <c r="P293" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="294" spans="1:16" x14ac:dyDescent="0.35">
@@ -18411,7 +18435,7 @@
         <v>0</v>
       </c>
       <c r="P294" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="295" spans="1:16" x14ac:dyDescent="0.35">
@@ -18461,7 +18485,7 @@
         <v>0</v>
       </c>
       <c r="P295" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="296" spans="1:16" x14ac:dyDescent="0.35">
@@ -18511,7 +18535,7 @@
         <v>0</v>
       </c>
       <c r="P296" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="297" spans="1:16" x14ac:dyDescent="0.35">
@@ -18561,7 +18585,7 @@
         <v>0</v>
       </c>
       <c r="P297" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="298" spans="1:16" x14ac:dyDescent="0.35">
@@ -18611,7 +18635,7 @@
         <v>0</v>
       </c>
       <c r="P298" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="299" spans="1:16" x14ac:dyDescent="0.35">
@@ -18661,7 +18685,7 @@
         <v>0</v>
       </c>
       <c r="P299" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="300" spans="1:16" x14ac:dyDescent="0.35">
@@ -18711,7 +18735,7 @@
         <v>0</v>
       </c>
       <c r="P300" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="301" spans="1:16" x14ac:dyDescent="0.35">
@@ -18761,7 +18785,7 @@
         <v>0</v>
       </c>
       <c r="P301" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="302" spans="1:16" x14ac:dyDescent="0.35">
@@ -18811,7 +18835,7 @@
         <v>0</v>
       </c>
       <c r="P302" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="303" spans="1:16" x14ac:dyDescent="0.35">
@@ -18861,7 +18885,7 @@
         <v>0</v>
       </c>
       <c r="P303" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="304" spans="1:16" x14ac:dyDescent="0.35">
@@ -18911,7 +18935,7 @@
         <v>0</v>
       </c>
       <c r="P304" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="305" spans="1:16" x14ac:dyDescent="0.35">
@@ -18961,7 +18985,7 @@
         <v>0</v>
       </c>
       <c r="P305" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="306" spans="1:16" x14ac:dyDescent="0.35">
@@ -19011,7 +19035,7 @@
         <v>0</v>
       </c>
       <c r="P306" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="307" spans="1:16" x14ac:dyDescent="0.35">
@@ -19061,7 +19085,7 @@
         <v>0</v>
       </c>
       <c r="P307" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="308" spans="1:16" x14ac:dyDescent="0.35">
@@ -19111,7 +19135,7 @@
         <v>0</v>
       </c>
       <c r="P308" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="309" spans="1:16" x14ac:dyDescent="0.35">
@@ -19161,7 +19185,7 @@
         <v>0</v>
       </c>
       <c r="P309" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="310" spans="1:16" x14ac:dyDescent="0.35">
@@ -19211,7 +19235,7 @@
         <v>0</v>
       </c>
       <c r="P310" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="311" spans="1:16" x14ac:dyDescent="0.35">
@@ -19261,7 +19285,7 @@
         <v>0</v>
       </c>
       <c r="P311" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="312" spans="1:16" x14ac:dyDescent="0.35">
@@ -19311,7 +19335,7 @@
         <v>0</v>
       </c>
       <c r="P312" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="313" spans="1:16" x14ac:dyDescent="0.35">
@@ -19361,7 +19385,7 @@
         <v>0</v>
       </c>
       <c r="P313" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="314" spans="1:16" x14ac:dyDescent="0.35">
@@ -19411,7 +19435,7 @@
         <v>0</v>
       </c>
       <c r="P314" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="315" spans="1:16" x14ac:dyDescent="0.35">
@@ -19461,7 +19485,7 @@
         <v>0</v>
       </c>
       <c r="P315" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="316" spans="1:16" x14ac:dyDescent="0.35">
@@ -19511,7 +19535,7 @@
         <v>0</v>
       </c>
       <c r="P316" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="317" spans="1:16" x14ac:dyDescent="0.35">
@@ -19561,7 +19585,7 @@
         <v>0</v>
       </c>
       <c r="P317" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="318" spans="1:16" x14ac:dyDescent="0.35">
@@ -19611,7 +19635,7 @@
         <v>0</v>
       </c>
       <c r="P318" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="319" spans="1:16" x14ac:dyDescent="0.35">
@@ -19661,7 +19685,7 @@
         <v>0</v>
       </c>
       <c r="P319" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="320" spans="1:16" x14ac:dyDescent="0.35">
@@ -19711,7 +19735,7 @@
         <v>0</v>
       </c>
       <c r="P320" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="321" spans="1:16" x14ac:dyDescent="0.35">
@@ -19761,7 +19785,7 @@
         <v>0</v>
       </c>
       <c r="P321" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="322" spans="1:16" x14ac:dyDescent="0.35">
@@ -19811,7 +19835,7 @@
         <v>0</v>
       </c>
       <c r="P322" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="323" spans="1:16" x14ac:dyDescent="0.35">
@@ -19861,7 +19885,7 @@
         <v>0</v>
       </c>
       <c r="P323" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="324" spans="1:16" x14ac:dyDescent="0.35">
@@ -19911,7 +19935,7 @@
         <v>0</v>
       </c>
       <c r="P324" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="325" spans="1:16" x14ac:dyDescent="0.35">
@@ -19961,7 +19985,7 @@
         <v>0</v>
       </c>
       <c r="P325" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="326" spans="1:16" x14ac:dyDescent="0.35">
@@ -20011,7 +20035,7 @@
         <v>0</v>
       </c>
       <c r="P326" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="327" spans="1:16" x14ac:dyDescent="0.35">
@@ -20061,7 +20085,7 @@
         <v>0</v>
       </c>
       <c r="P327" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="328" spans="1:16" x14ac:dyDescent="0.35">
@@ -20111,7 +20135,7 @@
         <v>0</v>
       </c>
       <c r="P328" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="329" spans="1:16" x14ac:dyDescent="0.35">
@@ -20161,7 +20185,7 @@
         <v>0</v>
       </c>
       <c r="P329" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="330" spans="1:16" x14ac:dyDescent="0.35">
@@ -20211,7 +20235,7 @@
         <v>0</v>
       </c>
       <c r="P330" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="331" spans="1:16" x14ac:dyDescent="0.35">
@@ -20261,7 +20285,7 @@
         <v>0</v>
       </c>
       <c r="P331" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="332" spans="1:16" x14ac:dyDescent="0.35">
@@ -20311,7 +20335,7 @@
         <v>0</v>
       </c>
       <c r="P332" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="333" spans="1:16" x14ac:dyDescent="0.35">
@@ -20361,7 +20385,7 @@
         <v>0</v>
       </c>
       <c r="P333" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="334" spans="1:16" x14ac:dyDescent="0.35">
@@ -20411,7 +20435,7 @@
         <v>0</v>
       </c>
       <c r="P334" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="335" spans="1:16" x14ac:dyDescent="0.35">
@@ -20461,7 +20485,7 @@
         <v>0</v>
       </c>
       <c r="P335" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="336" spans="1:16" x14ac:dyDescent="0.35">
@@ -20511,7 +20535,7 @@
         <v>0</v>
       </c>
       <c r="P336" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="337" spans="1:16" x14ac:dyDescent="0.35">
@@ -20561,7 +20585,7 @@
         <v>0</v>
       </c>
       <c r="P337" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="338" spans="1:16" x14ac:dyDescent="0.35">
@@ -20611,7 +20635,7 @@
         <v>0</v>
       </c>
       <c r="P338" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="339" spans="1:16" x14ac:dyDescent="0.35">
@@ -20661,7 +20685,7 @@
         <v>0</v>
       </c>
       <c r="P339" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="340" spans="1:16" x14ac:dyDescent="0.35">
@@ -20711,7 +20735,7 @@
         <v>0</v>
       </c>
       <c r="P340" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="341" spans="1:16" x14ac:dyDescent="0.35">
@@ -20761,7 +20785,7 @@
         <v>0</v>
       </c>
       <c r="P341" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="342" spans="1:16" x14ac:dyDescent="0.35">
@@ -20811,7 +20835,7 @@
         <v>0</v>
       </c>
       <c r="P342" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="343" spans="1:16" x14ac:dyDescent="0.35">
@@ -20861,7 +20885,7 @@
         <v>0</v>
       </c>
       <c r="P343" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="344" spans="1:16" x14ac:dyDescent="0.35">
@@ -20911,7 +20935,7 @@
         <v>0</v>
       </c>
       <c r="P344" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="345" spans="1:16" x14ac:dyDescent="0.35">
@@ -20961,7 +20985,7 @@
         <v>0</v>
       </c>
       <c r="P345" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="346" spans="1:16" x14ac:dyDescent="0.35">
@@ -21011,7 +21035,7 @@
         <v>0</v>
       </c>
       <c r="P346" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="347" spans="1:16" x14ac:dyDescent="0.35">
@@ -21061,7 +21085,7 @@
         <v>0</v>
       </c>
       <c r="P347" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="348" spans="1:16" x14ac:dyDescent="0.35">
@@ -21111,7 +21135,7 @@
         <v>0</v>
       </c>
       <c r="P348" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="349" spans="1:16" x14ac:dyDescent="0.35">
@@ -21161,7 +21185,7 @@
         <v>0</v>
       </c>
       <c r="P349" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="350" spans="1:16" x14ac:dyDescent="0.35">
@@ -21211,7 +21235,7 @@
         <v>0</v>
       </c>
       <c r="P350" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="351" spans="1:16" x14ac:dyDescent="0.35">
@@ -21261,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="P351" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="352" spans="1:16" x14ac:dyDescent="0.35">
@@ -21311,7 +21335,7 @@
         <v>0</v>
       </c>
       <c r="P352" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="353" spans="1:16" x14ac:dyDescent="0.35">
@@ -21361,7 +21385,7 @@
         <v>0</v>
       </c>
       <c r="P353" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="354" spans="1:16" x14ac:dyDescent="0.35">
@@ -21411,7 +21435,7 @@
         <v>0</v>
       </c>
       <c r="P354" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="355" spans="1:16" x14ac:dyDescent="0.35">
@@ -21461,7 +21485,7 @@
         <v>0</v>
       </c>
       <c r="P355" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="356" spans="1:16" x14ac:dyDescent="0.35">
@@ -21511,7 +21535,7 @@
         <v>0</v>
       </c>
       <c r="P356" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="357" spans="1:16" x14ac:dyDescent="0.35">
@@ -21561,7 +21585,7 @@
         <v>0</v>
       </c>
       <c r="P357" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="358" spans="1:16" x14ac:dyDescent="0.35">
@@ -21611,7 +21635,7 @@
         <v>0</v>
       </c>
       <c r="P358" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="359" spans="1:16" x14ac:dyDescent="0.35">
@@ -21661,7 +21685,7 @@
         <v>0</v>
       </c>
       <c r="P359" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="360" spans="1:16" x14ac:dyDescent="0.35">
@@ -21711,7 +21735,7 @@
         <v>0</v>
       </c>
       <c r="P360" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="361" spans="1:16" x14ac:dyDescent="0.35">
@@ -21761,7 +21785,7 @@
         <v>0</v>
       </c>
       <c r="P361" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="362" spans="1:16" x14ac:dyDescent="0.35">
@@ -21811,7 +21835,7 @@
         <v>0</v>
       </c>
       <c r="P362" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="363" spans="1:16" x14ac:dyDescent="0.35">
@@ -21861,7 +21885,7 @@
         <v>0</v>
       </c>
       <c r="P363" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="364" spans="1:16" x14ac:dyDescent="0.35">
@@ -21911,7 +21935,7 @@
         <v>0</v>
       </c>
       <c r="P364" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="365" spans="1:16" x14ac:dyDescent="0.35">
@@ -21961,7 +21985,7 @@
         <v>0</v>
       </c>
       <c r="P365" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="366" spans="1:16" x14ac:dyDescent="0.35">
@@ -22011,7 +22035,7 @@
         <v>0</v>
       </c>
       <c r="P366" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="367" spans="1:16" x14ac:dyDescent="0.35">
@@ -22061,7 +22085,7 @@
         <v>0</v>
       </c>
       <c r="P367" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="368" spans="1:16" x14ac:dyDescent="0.35">
@@ -22111,7 +22135,7 @@
         <v>0</v>
       </c>
       <c r="P368" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="369" spans="1:16" x14ac:dyDescent="0.35">
@@ -22161,7 +22185,7 @@
         <v>0</v>
       </c>
       <c r="P369" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="370" spans="1:16" x14ac:dyDescent="0.35">
@@ -22211,7 +22235,7 @@
         <v>0</v>
       </c>
       <c r="P370" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="371" spans="1:16" x14ac:dyDescent="0.35">
@@ -22261,7 +22285,7 @@
         <v>0</v>
       </c>
       <c r="P371" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="372" spans="1:16" x14ac:dyDescent="0.35">
@@ -22311,7 +22335,7 @@
         <v>0</v>
       </c>
       <c r="P372" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="373" spans="1:16" x14ac:dyDescent="0.35">
@@ -22361,7 +22385,7 @@
         <v>0</v>
       </c>
       <c r="P373" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="374" spans="1:16" x14ac:dyDescent="0.35">
@@ -22411,7 +22435,7 @@
         <v>0</v>
       </c>
       <c r="P374" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="375" spans="1:16" x14ac:dyDescent="0.35">
@@ -22461,7 +22485,7 @@
         <v>0</v>
       </c>
       <c r="P375" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="376" spans="1:16" x14ac:dyDescent="0.35">
@@ -22511,7 +22535,7 @@
         <v>0</v>
       </c>
       <c r="P376" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="377" spans="1:16" x14ac:dyDescent="0.35">
@@ -22561,7 +22585,7 @@
         <v>0</v>
       </c>
       <c r="P377" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="378" spans="1:16" x14ac:dyDescent="0.35">
@@ -22611,7 +22635,7 @@
         <v>0</v>
       </c>
       <c r="P378" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="379" spans="1:16" x14ac:dyDescent="0.35">
@@ -22661,7 +22685,7 @@
         <v>0</v>
       </c>
       <c r="P379" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="380" spans="1:16" x14ac:dyDescent="0.35">
@@ -22711,7 +22735,7 @@
         <v>0</v>
       </c>
       <c r="P380" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="381" spans="1:16" x14ac:dyDescent="0.35">
@@ -22761,7 +22785,7 @@
         <v>0</v>
       </c>
       <c r="P381" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="382" spans="1:16" x14ac:dyDescent="0.35">
@@ -22811,7 +22835,7 @@
         <v>0</v>
       </c>
       <c r="P382" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="383" spans="1:16" x14ac:dyDescent="0.35">
@@ -22861,7 +22885,7 @@
         <v>0</v>
       </c>
       <c r="P383" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="384" spans="1:16" x14ac:dyDescent="0.35">
@@ -22911,7 +22935,7 @@
         <v>0</v>
       </c>
       <c r="P384" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="385" spans="1:16" x14ac:dyDescent="0.35">
@@ -22961,7 +22985,7 @@
         <v>0</v>
       </c>
       <c r="P385" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="386" spans="1:16" x14ac:dyDescent="0.35">
@@ -23011,7 +23035,7 @@
         <v>0</v>
       </c>
       <c r="P386" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="387" spans="1:16" x14ac:dyDescent="0.35">
@@ -23061,7 +23085,7 @@
         <v>0</v>
       </c>
       <c r="P387" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="388" spans="1:16" x14ac:dyDescent="0.35">
@@ -23111,7 +23135,7 @@
         <v>0</v>
       </c>
       <c r="P388" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="389" spans="1:16" x14ac:dyDescent="0.35">
@@ -23161,7 +23185,7 @@
         <v>0</v>
       </c>
       <c r="P389" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="390" spans="1:16" x14ac:dyDescent="0.35">
@@ -23211,7 +23235,7 @@
         <v>0</v>
       </c>
       <c r="P390" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="391" spans="1:16" x14ac:dyDescent="0.35">
@@ -23261,7 +23285,7 @@
         <v>0</v>
       </c>
       <c r="P391" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="392" spans="1:16" x14ac:dyDescent="0.35">
@@ -23311,7 +23335,7 @@
         <v>0</v>
       </c>
       <c r="P392" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="393" spans="1:16" x14ac:dyDescent="0.35">
@@ -23361,7 +23385,7 @@
         <v>0</v>
       </c>
       <c r="P393" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="394" spans="1:16" x14ac:dyDescent="0.35">
@@ -23411,7 +23435,7 @@
         <v>0</v>
       </c>
       <c r="P394" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="395" spans="1:16" x14ac:dyDescent="0.35">
@@ -23461,7 +23485,7 @@
         <v>0</v>
       </c>
       <c r="P395" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="396" spans="1:16" x14ac:dyDescent="0.35">
@@ -23511,7 +23535,7 @@
         <v>0</v>
       </c>
       <c r="P396" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="397" spans="1:16" x14ac:dyDescent="0.35">
@@ -23561,7 +23585,7 @@
         <v>0</v>
       </c>
       <c r="P397" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="398" spans="1:16" x14ac:dyDescent="0.35">
@@ -23611,7 +23635,7 @@
         <v>0</v>
       </c>
       <c r="P398" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="399" spans="1:16" x14ac:dyDescent="0.35">
@@ -23661,7 +23685,7 @@
         <v>0</v>
       </c>
       <c r="P399" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="400" spans="1:16" x14ac:dyDescent="0.35">
@@ -23711,7 +23735,7 @@
         <v>0</v>
       </c>
       <c r="P400" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="401" spans="1:16" x14ac:dyDescent="0.35">
@@ -23761,7 +23785,7 @@
         <v>0</v>
       </c>
       <c r="P401" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="402" spans="1:16" x14ac:dyDescent="0.35">
@@ -23811,7 +23835,7 @@
         <v>0</v>
       </c>
       <c r="P402" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="403" spans="1:16" x14ac:dyDescent="0.35">
@@ -23861,7 +23885,7 @@
         <v>0</v>
       </c>
       <c r="P403" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="404" spans="1:16" x14ac:dyDescent="0.35">
@@ -23911,7 +23935,7 @@
         <v>0</v>
       </c>
       <c r="P404" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="405" spans="1:16" x14ac:dyDescent="0.35">
@@ -23961,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="P405" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="406" spans="1:16" x14ac:dyDescent="0.35">
@@ -24011,7 +24035,7 @@
         <v>0</v>
       </c>
       <c r="P406" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="407" spans="1:16" x14ac:dyDescent="0.35">
@@ -24061,7 +24085,7 @@
         <v>0</v>
       </c>
       <c r="P407" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="408" spans="1:16" x14ac:dyDescent="0.35">
@@ -24111,7 +24135,7 @@
         <v>0</v>
       </c>
       <c r="P408" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="409" spans="1:16" x14ac:dyDescent="0.35">
@@ -24161,7 +24185,7 @@
         <v>0</v>
       </c>
       <c r="P409" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="410" spans="1:16" x14ac:dyDescent="0.35">
@@ -24211,7 +24235,7 @@
         <v>0</v>
       </c>
       <c r="P410" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="411" spans="1:16" x14ac:dyDescent="0.35">
@@ -24261,7 +24285,7 @@
         <v>0</v>
       </c>
       <c r="P411" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="412" spans="1:16" x14ac:dyDescent="0.35">
@@ -24311,7 +24335,7 @@
         <v>0</v>
       </c>
       <c r="P412" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="413" spans="1:16" x14ac:dyDescent="0.35">
@@ -24361,7 +24385,7 @@
         <v>0</v>
       </c>
       <c r="P413" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="414" spans="1:16" x14ac:dyDescent="0.35">
@@ -24411,7 +24435,7 @@
         <v>0</v>
       </c>
       <c r="P414" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="415" spans="1:16" x14ac:dyDescent="0.35">
@@ -24461,7 +24485,7 @@
         <v>0</v>
       </c>
       <c r="P415" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="416" spans="1:16" x14ac:dyDescent="0.35">
@@ -24511,7 +24535,7 @@
         <v>0</v>
       </c>
       <c r="P416" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="417" spans="1:16" x14ac:dyDescent="0.35">
@@ -24561,7 +24585,7 @@
         <v>0</v>
       </c>
       <c r="P417" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="418" spans="1:16" x14ac:dyDescent="0.35">
@@ -24611,7 +24635,7 @@
         <v>0</v>
       </c>
       <c r="P418" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="419" spans="1:16" x14ac:dyDescent="0.35">
@@ -24661,7 +24685,7 @@
         <v>0</v>
       </c>
       <c r="P419" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="420" spans="1:16" x14ac:dyDescent="0.35">
@@ -24711,7 +24735,7 @@
         <v>0</v>
       </c>
       <c r="P420" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="421" spans="1:16" x14ac:dyDescent="0.35">
@@ -24761,7 +24785,7 @@
         <v>0</v>
       </c>
       <c r="P421" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="422" spans="1:16" x14ac:dyDescent="0.35">
@@ -24811,7 +24835,7 @@
         <v>0</v>
       </c>
       <c r="P422" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="423" spans="1:16" x14ac:dyDescent="0.35">
@@ -24861,7 +24885,7 @@
         <v>0</v>
       </c>
       <c r="P423" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="424" spans="1:16" x14ac:dyDescent="0.35">
@@ -24911,7 +24935,7 @@
         <v>0</v>
       </c>
       <c r="P424" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="425" spans="1:16" x14ac:dyDescent="0.35">
@@ -24961,7 +24985,7 @@
         <v>0</v>
       </c>
       <c r="P425" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="426" spans="1:16" x14ac:dyDescent="0.35">
@@ -25011,7 +25035,7 @@
         <v>0</v>
       </c>
       <c r="P426" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="427" spans="1:16" x14ac:dyDescent="0.35">
@@ -25061,7 +25085,7 @@
         <v>0</v>
       </c>
       <c r="P427" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="428" spans="1:16" x14ac:dyDescent="0.35">
@@ -25111,7 +25135,7 @@
         <v>0</v>
       </c>
       <c r="P428" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="429" spans="1:16" x14ac:dyDescent="0.35">
@@ -25161,7 +25185,7 @@
         <v>0</v>
       </c>
       <c r="P429" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="430" spans="1:16" x14ac:dyDescent="0.35">
@@ -25211,7 +25235,7 @@
         <v>0</v>
       </c>
       <c r="P430" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="431" spans="1:16" x14ac:dyDescent="0.35">
@@ -25261,7 +25285,7 @@
         <v>0</v>
       </c>
       <c r="P431" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="432" spans="1:16" x14ac:dyDescent="0.35">
@@ -25311,7 +25335,7 @@
         <v>0</v>
       </c>
       <c r="P432" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="433" spans="1:16" x14ac:dyDescent="0.35">
@@ -25361,7 +25385,7 @@
         <v>0</v>
       </c>
       <c r="P433" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="434" spans="1:16" x14ac:dyDescent="0.35">
@@ -25411,7 +25435,7 @@
         <v>0</v>
       </c>
       <c r="P434" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="435" spans="1:16" x14ac:dyDescent="0.35">
@@ -25461,7 +25485,7 @@
         <v>0</v>
       </c>
       <c r="P435" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="436" spans="1:16" x14ac:dyDescent="0.35">
@@ -25511,7 +25535,7 @@
         <v>0</v>
       </c>
       <c r="P436" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="437" spans="1:16" x14ac:dyDescent="0.35">
@@ -25561,7 +25585,7 @@
         <v>0</v>
       </c>
       <c r="P437" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="438" spans="1:16" x14ac:dyDescent="0.35">
@@ -25611,7 +25635,7 @@
         <v>0</v>
       </c>
       <c r="P438" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="439" spans="1:16" x14ac:dyDescent="0.35">
@@ -25661,7 +25685,7 @@
         <v>0</v>
       </c>
       <c r="P439" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="440" spans="1:16" x14ac:dyDescent="0.35">
@@ -25711,7 +25735,7 @@
         <v>0</v>
       </c>
       <c r="P440" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="441" spans="1:16" x14ac:dyDescent="0.35">
@@ -25761,7 +25785,7 @@
         <v>0</v>
       </c>
       <c r="P441" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="442" spans="1:16" x14ac:dyDescent="0.35">
@@ -25811,7 +25835,7 @@
         <v>0</v>
       </c>
       <c r="P442" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="443" spans="1:16" x14ac:dyDescent="0.35">
@@ -25861,7 +25885,7 @@
         <v>0</v>
       </c>
       <c r="P443" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="444" spans="1:16" x14ac:dyDescent="0.35">
@@ -25911,7 +25935,7 @@
         <v>0</v>
       </c>
       <c r="P444" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="445" spans="1:16" x14ac:dyDescent="0.35">
@@ -25961,7 +25985,7 @@
         <v>0</v>
       </c>
       <c r="P445" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="446" spans="1:16" x14ac:dyDescent="0.35">
@@ -26011,7 +26035,7 @@
         <v>0</v>
       </c>
       <c r="P446" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="447" spans="1:16" x14ac:dyDescent="0.35">
@@ -26061,7 +26085,7 @@
         <v>0</v>
       </c>
       <c r="P447" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="448" spans="1:16" x14ac:dyDescent="0.35">
@@ -26111,7 +26135,7 @@
         <v>0</v>
       </c>
       <c r="P448" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="449" spans="1:16" x14ac:dyDescent="0.35">
@@ -26161,7 +26185,7 @@
         <v>0</v>
       </c>
       <c r="P449" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="450" spans="1:16" x14ac:dyDescent="0.35">
@@ -26211,7 +26235,7 @@
         <v>0</v>
       </c>
       <c r="P450" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="451" spans="1:16" x14ac:dyDescent="0.35">
@@ -26261,7 +26285,7 @@
         <v>0</v>
       </c>
       <c r="P451" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="452" spans="1:16" x14ac:dyDescent="0.35">
@@ -26311,7 +26335,7 @@
         <v>0</v>
       </c>
       <c r="P452" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="453" spans="1:16" x14ac:dyDescent="0.35">
@@ -26361,7 +26385,7 @@
         <v>0</v>
       </c>
       <c r="P453" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="454" spans="1:16" x14ac:dyDescent="0.35">
@@ -26411,7 +26435,7 @@
         <v>0</v>
       </c>
       <c r="P454" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="455" spans="1:16" x14ac:dyDescent="0.35">
@@ -26461,7 +26485,7 @@
         <v>0</v>
       </c>
       <c r="P455" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="456" spans="1:16" x14ac:dyDescent="0.35">
@@ -26511,7 +26535,7 @@
         <v>0</v>
       </c>
       <c r="P456" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="457" spans="1:16" x14ac:dyDescent="0.35">
@@ -26561,7 +26585,7 @@
         <v>0</v>
       </c>
       <c r="P457" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="458" spans="1:16" x14ac:dyDescent="0.35">
@@ -26611,7 +26635,7 @@
         <v>0</v>
       </c>
       <c r="P458" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="459" spans="1:16" x14ac:dyDescent="0.35">
@@ -26661,7 +26685,7 @@
         <v>0</v>
       </c>
       <c r="P459" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="460" spans="1:16" x14ac:dyDescent="0.35">
@@ -26711,7 +26735,7 @@
         <v>0</v>
       </c>
       <c r="P460" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="461" spans="1:16" x14ac:dyDescent="0.35">
@@ -26761,7 +26785,7 @@
         <v>0</v>
       </c>
       <c r="P461" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="462" spans="1:16" x14ac:dyDescent="0.35">
@@ -26811,7 +26835,7 @@
         <v>0</v>
       </c>
       <c r="P462" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="463" spans="1:16" x14ac:dyDescent="0.35">
@@ -26861,7 +26885,7 @@
         <v>0</v>
       </c>
       <c r="P463" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="464" spans="1:16" x14ac:dyDescent="0.35">
@@ -26911,7 +26935,7 @@
         <v>0</v>
       </c>
       <c r="P464" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="465" spans="1:16" x14ac:dyDescent="0.35">
@@ -26961,7 +26985,7 @@
         <v>0</v>
       </c>
       <c r="P465" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="466" spans="1:16" x14ac:dyDescent="0.35">
@@ -27011,7 +27035,7 @@
         <v>0</v>
       </c>
       <c r="P466" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="467" spans="1:16" x14ac:dyDescent="0.35">
@@ -27061,7 +27085,7 @@
         <v>0</v>
       </c>
       <c r="P467" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="468" spans="1:16" x14ac:dyDescent="0.35">
@@ -27111,7 +27135,7 @@
         <v>0</v>
       </c>
       <c r="P468" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="469" spans="1:16" x14ac:dyDescent="0.35">
@@ -27161,7 +27185,7 @@
         <v>0</v>
       </c>
       <c r="P469" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="470" spans="1:16" x14ac:dyDescent="0.35">
@@ -27211,7 +27235,7 @@
         <v>0</v>
       </c>
       <c r="P470" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="471" spans="1:16" x14ac:dyDescent="0.35">
@@ -27261,7 +27285,7 @@
         <v>0</v>
       </c>
       <c r="P471" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="472" spans="1:16" x14ac:dyDescent="0.35">
@@ -27311,7 +27335,7 @@
         <v>0</v>
       </c>
       <c r="P472" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="473" spans="1:16" x14ac:dyDescent="0.35">
@@ -27361,7 +27385,7 @@
         <v>0</v>
       </c>
       <c r="P473" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="474" spans="1:16" x14ac:dyDescent="0.35">
@@ -27411,7 +27435,7 @@
         <v>0</v>
       </c>
       <c r="P474" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="475" spans="1:16" x14ac:dyDescent="0.35">
@@ -27461,7 +27485,7 @@
         <v>0</v>
       </c>
       <c r="P475" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="476" spans="1:16" x14ac:dyDescent="0.35">
@@ -27511,7 +27535,7 @@
         <v>0</v>
       </c>
       <c r="P476" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="477" spans="1:16" x14ac:dyDescent="0.35">
@@ -27561,7 +27585,7 @@
         <v>0</v>
       </c>
       <c r="P477" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="478" spans="1:16" x14ac:dyDescent="0.35">
@@ -27611,7 +27635,7 @@
         <v>0</v>
       </c>
       <c r="P478" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="479" spans="1:16" x14ac:dyDescent="0.35">
@@ -27661,7 +27685,7 @@
         <v>0</v>
       </c>
       <c r="P479" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="480" spans="1:16" x14ac:dyDescent="0.35">
@@ -27711,7 +27735,7 @@
         <v>0</v>
       </c>
       <c r="P480" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="481" spans="1:16" x14ac:dyDescent="0.35">
@@ -27761,7 +27785,7 @@
         <v>0</v>
       </c>
       <c r="P481" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="482" spans="1:16" x14ac:dyDescent="0.35">
@@ -27811,7 +27835,7 @@
         <v>0</v>
       </c>
       <c r="P482" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="483" spans="1:16" x14ac:dyDescent="0.35">
@@ -27861,7 +27885,7 @@
         <v>0</v>
       </c>
       <c r="P483" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="484" spans="1:16" x14ac:dyDescent="0.35">
@@ -27911,7 +27935,7 @@
         <v>0</v>
       </c>
       <c r="P484" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="485" spans="1:16" x14ac:dyDescent="0.35">
@@ -27961,7 +27985,7 @@
         <v>0</v>
       </c>
       <c r="P485" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="486" spans="1:16" x14ac:dyDescent="0.35">
@@ -28011,7 +28035,7 @@
         <v>0</v>
       </c>
       <c r="P486" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="487" spans="1:16" x14ac:dyDescent="0.35">
@@ -28061,7 +28085,7 @@
         <v>0</v>
       </c>
       <c r="P487" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="488" spans="1:16" x14ac:dyDescent="0.35">
@@ -28111,7 +28135,7 @@
         <v>0</v>
       </c>
       <c r="P488" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="489" spans="1:16" x14ac:dyDescent="0.35">
@@ -28161,7 +28185,7 @@
         <v>0</v>
       </c>
       <c r="P489" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="490" spans="1:16" x14ac:dyDescent="0.35">
@@ -28211,7 +28235,7 @@
         <v>0</v>
       </c>
       <c r="P490" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="491" spans="1:16" x14ac:dyDescent="0.35">
@@ -28261,7 +28285,7 @@
         <v>0</v>
       </c>
       <c r="P491" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="492" spans="1:16" x14ac:dyDescent="0.35">
@@ -28311,7 +28335,7 @@
         <v>0</v>
       </c>
       <c r="P492" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="493" spans="1:16" x14ac:dyDescent="0.35">
@@ -28361,7 +28385,7 @@
         <v>0</v>
       </c>
       <c r="P493" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="494" spans="1:16" x14ac:dyDescent="0.35">
@@ -28411,7 +28435,7 @@
         <v>0</v>
       </c>
       <c r="P494" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="495" spans="1:16" x14ac:dyDescent="0.35">
@@ -28461,7 +28485,7 @@
         <v>0</v>
       </c>
       <c r="P495" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="496" spans="1:16" x14ac:dyDescent="0.35">
@@ -28511,7 +28535,7 @@
         <v>0</v>
       </c>
       <c r="P496" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="497" spans="1:16" x14ac:dyDescent="0.35">
@@ -28561,7 +28585,7 @@
         <v>0</v>
       </c>
       <c r="P497" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="498" spans="1:16" x14ac:dyDescent="0.35">
@@ -28611,7 +28635,7 @@
         <v>0</v>
       </c>
       <c r="P498" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="499" spans="1:16" x14ac:dyDescent="0.35">
@@ -28661,7 +28685,7 @@
         <v>0</v>
       </c>
       <c r="P499" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="500" spans="1:16" x14ac:dyDescent="0.35">
@@ -28711,7 +28735,7 @@
         <v>0</v>
       </c>
       <c r="P500" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="501" spans="1:16" x14ac:dyDescent="0.35">
@@ -28761,7 +28785,7 @@
         <v>0</v>
       </c>
       <c r="P501" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="502" spans="1:16" x14ac:dyDescent="0.35">
@@ -28811,7 +28835,7 @@
         <v>0</v>
       </c>
       <c r="P502" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="503" spans="1:16" x14ac:dyDescent="0.35">
@@ -28861,7 +28885,7 @@
         <v>0</v>
       </c>
       <c r="P503" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="504" spans="1:16" x14ac:dyDescent="0.35">
@@ -28911,7 +28935,7 @@
         <v>0</v>
       </c>
       <c r="P504" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="505" spans="1:16" x14ac:dyDescent="0.35">
@@ -28961,7 +28985,7 @@
         <v>0</v>
       </c>
       <c r="P505" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="506" spans="1:16" x14ac:dyDescent="0.35">
@@ -29011,7 +29035,7 @@
         <v>0</v>
       </c>
       <c r="P506" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="507" spans="1:16" x14ac:dyDescent="0.35">
@@ -29061,7 +29085,7 @@
         <v>0</v>
       </c>
       <c r="P507" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="508" spans="1:16" x14ac:dyDescent="0.35">
@@ -29111,7 +29135,7 @@
         <v>0</v>
       </c>
       <c r="P508" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="509" spans="1:16" x14ac:dyDescent="0.35">
@@ -29161,7 +29185,7 @@
         <v>0</v>
       </c>
       <c r="P509" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="510" spans="1:16" x14ac:dyDescent="0.35">
@@ -29211,7 +29235,7 @@
         <v>0</v>
       </c>
       <c r="P510" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="511" spans="1:16" x14ac:dyDescent="0.35">
@@ -29261,7 +29285,7 @@
         <v>0</v>
       </c>
       <c r="P511" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="512" spans="1:16" x14ac:dyDescent="0.35">
@@ -29311,7 +29335,7 @@
         <v>0</v>
       </c>
       <c r="P512" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="513" spans="1:16" x14ac:dyDescent="0.35">
@@ -29361,7 +29385,7 @@
         <v>0</v>
       </c>
       <c r="P513" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="514" spans="1:16" x14ac:dyDescent="0.35">
@@ -29411,7 +29435,7 @@
         <v>0</v>
       </c>
       <c r="P514" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="515" spans="1:16" x14ac:dyDescent="0.35">
@@ -29461,7 +29485,7 @@
         <v>0</v>
       </c>
       <c r="P515" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="516" spans="1:16" x14ac:dyDescent="0.35">
@@ -29511,7 +29535,7 @@
         <v>0</v>
       </c>
       <c r="P516" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="517" spans="1:16" x14ac:dyDescent="0.35">
@@ -29561,7 +29585,7 @@
         <v>0</v>
       </c>
       <c r="P517" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="518" spans="1:16" x14ac:dyDescent="0.35">
@@ -29611,7 +29635,7 @@
         <v>0</v>
       </c>
       <c r="P518" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="519" spans="1:16" x14ac:dyDescent="0.35">
@@ -29661,7 +29685,7 @@
         <v>0</v>
       </c>
       <c r="P519" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="520" spans="1:16" x14ac:dyDescent="0.35">
@@ -29711,7 +29735,7 @@
         <v>0</v>
       </c>
       <c r="P520" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="521" spans="1:16" x14ac:dyDescent="0.35">
@@ -29761,7 +29785,7 @@
         <v>0</v>
       </c>
       <c r="P521" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="522" spans="1:16" x14ac:dyDescent="0.35">
@@ -29811,7 +29835,7 @@
         <v>0</v>
       </c>
       <c r="P522" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="523" spans="1:16" x14ac:dyDescent="0.35">
@@ -29861,7 +29885,7 @@
         <v>0</v>
       </c>
       <c r="P523" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="524" spans="1:16" x14ac:dyDescent="0.35">
@@ -29911,7 +29935,7 @@
         <v>0</v>
       </c>
       <c r="P524" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="525" spans="1:16" x14ac:dyDescent="0.35">
@@ -29961,7 +29985,7 @@
         <v>0</v>
       </c>
       <c r="P525" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="526" spans="1:16" x14ac:dyDescent="0.35">
@@ -30011,7 +30035,7 @@
         <v>0</v>
       </c>
       <c r="P526" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="527" spans="1:16" x14ac:dyDescent="0.35">
@@ -30061,7 +30085,7 @@
         <v>0</v>
       </c>
       <c r="P527" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="528" spans="1:16" x14ac:dyDescent="0.35">
@@ -30111,7 +30135,7 @@
         <v>0</v>
       </c>
       <c r="P528" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="529" spans="1:16" x14ac:dyDescent="0.35">
@@ -30161,7 +30185,7 @@
         <v>0</v>
       </c>
       <c r="P529" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="530" spans="1:16" x14ac:dyDescent="0.35">
@@ -30211,7 +30235,7 @@
         <v>0</v>
       </c>
       <c r="P530" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="531" spans="1:16" x14ac:dyDescent="0.35">
@@ -30261,7 +30285,7 @@
         <v>0</v>
       </c>
       <c r="P531" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="532" spans="1:16" x14ac:dyDescent="0.35">
@@ -30311,7 +30335,7 @@
         <v>0</v>
       </c>
       <c r="P532" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="533" spans="1:16" x14ac:dyDescent="0.35">
@@ -30361,7 +30385,7 @@
         <v>0</v>
       </c>
       <c r="P533" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="534" spans="1:16" x14ac:dyDescent="0.35">
@@ -30411,7 +30435,7 @@
         <v>0</v>
       </c>
       <c r="P534" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="535" spans="1:16" x14ac:dyDescent="0.35">
@@ -30461,7 +30485,7 @@
         <v>0</v>
       </c>
       <c r="P535" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="536" spans="1:16" x14ac:dyDescent="0.35">
@@ -30511,7 +30535,7 @@
         <v>0</v>
       </c>
       <c r="P536" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="537" spans="1:16" x14ac:dyDescent="0.35">
@@ -30561,7 +30585,7 @@
         <v>0</v>
       </c>
       <c r="P537" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="538" spans="1:16" x14ac:dyDescent="0.35">
@@ -30611,7 +30635,7 @@
         <v>0</v>
       </c>
       <c r="P538" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="539" spans="1:16" x14ac:dyDescent="0.35">
@@ -30661,7 +30685,7 @@
         <v>0</v>
       </c>
       <c r="P539" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="540" spans="1:16" x14ac:dyDescent="0.35">
@@ -30711,7 +30735,7 @@
         <v>0</v>
       </c>
       <c r="P540" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="541" spans="1:16" x14ac:dyDescent="0.35">
@@ -30761,7 +30785,7 @@
         <v>0</v>
       </c>
       <c r="P541" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="542" spans="1:16" x14ac:dyDescent="0.35">
@@ -30811,7 +30835,7 @@
         <v>0</v>
       </c>
       <c r="P542" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="543" spans="1:16" x14ac:dyDescent="0.35">
@@ -30861,7 +30885,7 @@
         <v>0</v>
       </c>
       <c r="P543" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="544" spans="1:16" x14ac:dyDescent="0.35">
@@ -30911,7 +30935,7 @@
         <v>0</v>
       </c>
       <c r="P544" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="545" spans="1:16" x14ac:dyDescent="0.35">
@@ -30961,7 +30985,7 @@
         <v>0</v>
       </c>
       <c r="P545" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="546" spans="1:16" x14ac:dyDescent="0.35">
@@ -31011,7 +31035,7 @@
         <v>0</v>
       </c>
       <c r="P546" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="547" spans="1:16" x14ac:dyDescent="0.35">
@@ -31061,7 +31085,7 @@
         <v>0</v>
       </c>
       <c r="P547" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="548" spans="1:16" x14ac:dyDescent="0.35">
@@ -31111,7 +31135,7 @@
         <v>0</v>
       </c>
       <c r="P548" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="549" spans="1:16" x14ac:dyDescent="0.35">
@@ -31161,7 +31185,7 @@
         <v>0</v>
       </c>
       <c r="P549" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="550" spans="1:16" x14ac:dyDescent="0.35">
@@ -31211,7 +31235,7 @@
         <v>0</v>
       </c>
       <c r="P550" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="551" spans="1:16" x14ac:dyDescent="0.35">
@@ -31261,7 +31285,7 @@
         <v>0</v>
       </c>
       <c r="P551" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="552" spans="1:16" x14ac:dyDescent="0.35">
@@ -31311,7 +31335,7 @@
         <v>0</v>
       </c>
       <c r="P552" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="553" spans="1:16" x14ac:dyDescent="0.35">
@@ -31361,7 +31385,7 @@
         <v>0</v>
       </c>
       <c r="P553" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="554" spans="1:16" x14ac:dyDescent="0.35">
@@ -31411,7 +31435,7 @@
         <v>0</v>
       </c>
       <c r="P554" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="555" spans="1:16" x14ac:dyDescent="0.35">
@@ -31461,7 +31485,7 @@
         <v>0</v>
       </c>
       <c r="P555" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="556" spans="1:16" x14ac:dyDescent="0.35">
@@ -31511,7 +31535,7 @@
         <v>0</v>
       </c>
       <c r="P556" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="557" spans="1:16" x14ac:dyDescent="0.35">
@@ -31561,7 +31585,7 @@
         <v>0</v>
       </c>
       <c r="P557" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="558" spans="1:16" x14ac:dyDescent="0.35">
@@ -31611,7 +31635,7 @@
         <v>0</v>
       </c>
       <c r="P558" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="559" spans="1:16" x14ac:dyDescent="0.35">
@@ -31661,7 +31685,7 @@
         <v>0</v>
       </c>
       <c r="P559" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="560" spans="1:16" x14ac:dyDescent="0.35">
@@ -31711,7 +31735,7 @@
         <v>0</v>
       </c>
       <c r="P560" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="561" spans="1:16" x14ac:dyDescent="0.35">
@@ -31761,7 +31785,7 @@
         <v>0</v>
       </c>
       <c r="P561" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="562" spans="1:16" x14ac:dyDescent="0.35">
@@ -31811,7 +31835,7 @@
         <v>0</v>
       </c>
       <c r="P562" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="563" spans="1:16" x14ac:dyDescent="0.35">
@@ -31861,7 +31885,7 @@
         <v>0</v>
       </c>
       <c r="P563" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="564" spans="1:16" x14ac:dyDescent="0.35">
@@ -31910,6 +31934,9 @@
       <c r="O564">
         <v>0</v>
       </c>
+      <c r="P564" t="s">
+        <v>1068</v>
+      </c>
     </row>
     <row r="565" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A565" s="1" t="s">
@@ -31957,6 +31984,9 @@
       <c r="O565">
         <v>0</v>
       </c>
+      <c r="P565" t="s">
+        <v>1078</v>
+      </c>
     </row>
     <row r="566" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A566" s="1" t="s">
@@ -32004,6 +32034,9 @@
       <c r="O566">
         <v>0</v>
       </c>
+      <c r="P566" t="s">
+        <v>1076</v>
+      </c>
     </row>
     <row r="567" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A567" s="1" t="s">
@@ -32051,6 +32084,9 @@
       <c r="O567">
         <v>0</v>
       </c>
+      <c r="P567" t="s">
+        <v>1041</v>
+      </c>
     </row>
     <row r="568" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A568" s="1" t="s">
@@ -32098,6 +32134,9 @@
       <c r="O568">
         <v>0</v>
       </c>
+      <c r="P568" t="s">
+        <v>1041</v>
+      </c>
     </row>
     <row r="569" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A569" s="1" t="s">
@@ -32145,6 +32184,9 @@
       <c r="O569">
         <v>0</v>
       </c>
+      <c r="P569" t="s">
+        <v>1055</v>
+      </c>
     </row>
     <row r="570" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A570" s="1" t="s">
@@ -32192,6 +32234,9 @@
       <c r="O570">
         <v>0</v>
       </c>
+      <c r="P570" t="s">
+        <v>1077</v>
+      </c>
     </row>
     <row r="571" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A571" s="1" t="s">
@@ -32239,6 +32284,9 @@
       <c r="O571">
         <v>0</v>
       </c>
+      <c r="P571" t="s">
+        <v>1077</v>
+      </c>
     </row>
     <row r="572" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A572" s="1" t="s">
@@ -32286,6 +32334,9 @@
       <c r="O572">
         <v>0</v>
       </c>
+      <c r="P572" t="s">
+        <v>1064</v>
+      </c>
     </row>
     <row r="573" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A573" s="1" t="s">
@@ -32333,6 +32384,9 @@
       <c r="O573">
         <v>0</v>
       </c>
+      <c r="P573" t="s">
+        <v>1064</v>
+      </c>
     </row>
     <row r="574" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A574" s="1" t="s">
@@ -32380,6 +32434,9 @@
       <c r="O574">
         <v>0</v>
       </c>
+      <c r="P574" t="s">
+        <v>1064</v>
+      </c>
     </row>
     <row r="575" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A575" s="1" t="s">
@@ -32427,6 +32484,9 @@
       <c r="O575">
         <v>0</v>
       </c>
+      <c r="P575" t="s">
+        <v>1064</v>
+      </c>
     </row>
     <row r="576" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A576" s="1" t="s">
@@ -32474,8 +32534,11 @@
       <c r="O576">
         <v>0</v>
       </c>
-    </row>
-    <row r="577" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P576" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="577" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A577" s="1" t="s">
         <v>596</v>
       </c>
@@ -32521,8 +32584,11 @@
       <c r="O577">
         <v>0</v>
       </c>
-    </row>
-    <row r="578" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P577" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="578" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A578" s="1" t="s">
         <v>597</v>
       </c>
@@ -32568,8 +32634,11 @@
       <c r="O578">
         <v>0</v>
       </c>
-    </row>
-    <row r="579" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P578" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="579" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A579" s="1" t="s">
         <v>598</v>
       </c>
@@ -32615,8 +32684,11 @@
       <c r="O579">
         <v>0</v>
       </c>
-    </row>
-    <row r="580" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P579" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="580" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A580" s="1" t="s">
         <v>599</v>
       </c>
@@ -32662,8 +32734,11 @@
       <c r="O580">
         <v>0</v>
       </c>
-    </row>
-    <row r="581" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P580" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="581" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A581" s="1" t="s">
         <v>600</v>
       </c>
@@ -32709,8 +32784,11 @@
       <c r="O581">
         <v>0</v>
       </c>
-    </row>
-    <row r="582" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P581" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="582" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A582" s="1" t="s">
         <v>601</v>
       </c>
@@ -32756,8 +32834,11 @@
       <c r="O582">
         <v>0</v>
       </c>
-    </row>
-    <row r="583" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P582" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="583" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A583" s="1" t="s">
         <v>602</v>
       </c>
@@ -32803,8 +32884,11 @@
       <c r="O583">
         <v>0</v>
       </c>
-    </row>
-    <row r="584" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P583" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="584" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A584" s="1" t="s">
         <v>603</v>
       </c>
@@ -32850,8 +32934,11 @@
       <c r="O584">
         <v>0</v>
       </c>
-    </row>
-    <row r="585" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P584" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="585" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A585" s="1" t="s">
         <v>604</v>
       </c>
@@ -32897,8 +32984,11 @@
       <c r="O585">
         <v>0</v>
       </c>
-    </row>
-    <row r="586" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P585" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="586" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A586" s="1" t="s">
         <v>605</v>
       </c>
@@ -32944,8 +33034,11 @@
       <c r="O586">
         <v>0</v>
       </c>
-    </row>
-    <row r="587" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P586" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="587" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A587" s="1" t="s">
         <v>606</v>
       </c>
@@ -32991,8 +33084,11 @@
       <c r="O587">
         <v>0</v>
       </c>
-    </row>
-    <row r="588" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P587" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="588" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A588" s="1" t="s">
         <v>607</v>
       </c>
@@ -33038,8 +33134,11 @@
       <c r="O588">
         <v>0</v>
       </c>
-    </row>
-    <row r="589" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P588" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="589" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A589" s="1" t="s">
         <v>608</v>
       </c>
@@ -33085,8 +33184,11 @@
       <c r="O589">
         <v>0</v>
       </c>
-    </row>
-    <row r="590" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P589" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="590" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A590" s="1" t="s">
         <v>609</v>
       </c>
@@ -33132,8 +33234,11 @@
       <c r="O590">
         <v>0</v>
       </c>
-    </row>
-    <row r="591" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P590" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="591" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A591" s="1" t="s">
         <v>610</v>
       </c>
@@ -33179,8 +33284,11 @@
       <c r="O591">
         <v>0</v>
       </c>
-    </row>
-    <row r="592" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P591" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="592" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A592" s="1" t="s">
         <v>611</v>
       </c>
@@ -33226,8 +33334,11 @@
       <c r="O592">
         <v>0</v>
       </c>
-    </row>
-    <row r="593" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P592" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="593" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A593" s="1" t="s">
         <v>612</v>
       </c>
@@ -33273,8 +33384,11 @@
       <c r="O593">
         <v>0</v>
       </c>
-    </row>
-    <row r="594" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P593" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="594" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A594" s="1" t="s">
         <v>613</v>
       </c>
@@ -33320,8 +33434,11 @@
       <c r="O594">
         <v>0</v>
       </c>
-    </row>
-    <row r="595" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P594" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="595" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A595" s="1" t="s">
         <v>614</v>
       </c>
@@ -33367,8 +33484,11 @@
       <c r="O595">
         <v>0</v>
       </c>
-    </row>
-    <row r="596" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P595" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="596" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A596" s="1" t="s">
         <v>615</v>
       </c>
@@ -33414,8 +33534,11 @@
       <c r="O596">
         <v>0</v>
       </c>
-    </row>
-    <row r="597" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P596" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="597" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A597" s="1" t="s">
         <v>616</v>
       </c>
@@ -33461,8 +33584,11 @@
       <c r="O597">
         <v>0</v>
       </c>
-    </row>
-    <row r="598" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P597" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="598" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A598" s="1" t="s">
         <v>617</v>
       </c>
@@ -33508,8 +33634,11 @@
       <c r="O598">
         <v>0</v>
       </c>
-    </row>
-    <row r="599" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P598" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="599" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A599" s="1" t="s">
         <v>618</v>
       </c>
@@ -33555,8 +33684,11 @@
       <c r="O599">
         <v>0</v>
       </c>
-    </row>
-    <row r="600" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P599" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="600" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A600" s="1" t="s">
         <v>619</v>
       </c>
@@ -33602,8 +33734,11 @@
       <c r="O600">
         <v>0</v>
       </c>
-    </row>
-    <row r="601" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P600" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="601" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A601" s="1" t="s">
         <v>620</v>
       </c>
@@ -33649,8 +33784,11 @@
       <c r="O601">
         <v>0</v>
       </c>
-    </row>
-    <row r="602" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P601" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="602" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A602" s="1" t="s">
         <v>621</v>
       </c>
@@ -33696,8 +33834,11 @@
       <c r="O602">
         <v>0</v>
       </c>
-    </row>
-    <row r="603" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P602" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="603" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A603" s="1" t="s">
         <v>622</v>
       </c>
@@ -33743,8 +33884,11 @@
       <c r="O603">
         <v>0</v>
       </c>
-    </row>
-    <row r="604" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P603" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="604" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A604" s="1" t="s">
         <v>623</v>
       </c>
@@ -33790,8 +33934,11 @@
       <c r="O604">
         <v>0</v>
       </c>
-    </row>
-    <row r="605" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P604" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="605" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A605" s="1" t="s">
         <v>624</v>
       </c>
@@ -33837,8 +33984,11 @@
       <c r="O605">
         <v>0</v>
       </c>
-    </row>
-    <row r="606" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P605" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="606" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A606" s="1" t="s">
         <v>625</v>
       </c>
@@ -33884,8 +34034,11 @@
       <c r="O606">
         <v>0</v>
       </c>
-    </row>
-    <row r="607" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P606" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="607" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A607" s="1" t="s">
         <v>626</v>
       </c>
@@ -33931,8 +34084,11 @@
       <c r="O607">
         <v>0</v>
       </c>
-    </row>
-    <row r="608" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P607" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="608" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A608" s="1" t="s">
         <v>627</v>
       </c>
@@ -33978,8 +34134,11 @@
       <c r="O608">
         <v>0</v>
       </c>
-    </row>
-    <row r="609" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P608" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="609" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A609" s="1" t="s">
         <v>628</v>
       </c>
@@ -34025,8 +34184,11 @@
       <c r="O609">
         <v>0</v>
       </c>
-    </row>
-    <row r="610" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P609" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="610" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A610" s="1" t="s">
         <v>629</v>
       </c>
@@ -34072,8 +34234,11 @@
       <c r="O610">
         <v>0</v>
       </c>
-    </row>
-    <row r="611" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P610" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="611" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A611" s="1" t="s">
         <v>630</v>
       </c>
@@ -34119,8 +34284,11 @@
       <c r="O611">
         <v>0</v>
       </c>
-    </row>
-    <row r="612" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P611" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="612" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A612" s="1" t="s">
         <v>631</v>
       </c>
@@ -34166,8 +34334,11 @@
       <c r="O612">
         <v>0</v>
       </c>
-    </row>
-    <row r="613" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P612" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="613" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A613" s="1" t="s">
         <v>632</v>
       </c>
@@ -34213,8 +34384,11 @@
       <c r="O613">
         <v>0</v>
       </c>
-    </row>
-    <row r="614" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P613" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="614" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A614" s="1" t="s">
         <v>633</v>
       </c>
@@ -34260,8 +34434,11 @@
       <c r="O614">
         <v>0</v>
       </c>
-    </row>
-    <row r="615" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P614" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="615" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A615" s="1" t="s">
         <v>634</v>
       </c>
@@ -34307,8 +34484,11 @@
       <c r="O615">
         <v>0</v>
       </c>
-    </row>
-    <row r="616" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P615" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="616" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A616" s="1" t="s">
         <v>635</v>
       </c>
@@ -34354,8 +34534,11 @@
       <c r="O616">
         <v>0</v>
       </c>
-    </row>
-    <row r="617" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P616" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="617" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A617" s="1" t="s">
         <v>636</v>
       </c>
@@ -34401,8 +34584,11 @@
       <c r="O617">
         <v>0</v>
       </c>
-    </row>
-    <row r="618" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P617" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="618" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A618" s="1" t="s">
         <v>637</v>
       </c>
@@ -34448,8 +34634,11 @@
       <c r="O618">
         <v>0</v>
       </c>
-    </row>
-    <row r="619" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P618" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="619" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A619" s="1" t="s">
         <v>638</v>
       </c>
@@ -34495,8 +34684,11 @@
       <c r="O619">
         <v>0</v>
       </c>
-    </row>
-    <row r="620" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P619" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="620" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A620" s="1" t="s">
         <v>639</v>
       </c>
@@ -34542,8 +34734,11 @@
       <c r="O620">
         <v>0</v>
       </c>
-    </row>
-    <row r="621" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P620" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="621" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A621" s="1" t="s">
         <v>640</v>
       </c>
@@ -34589,8 +34784,11 @@
       <c r="O621">
         <v>0</v>
       </c>
-    </row>
-    <row r="622" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P621" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="622" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A622" s="1" t="s">
         <v>641</v>
       </c>
@@ -34636,8 +34834,11 @@
       <c r="O622">
         <v>0</v>
       </c>
-    </row>
-    <row r="623" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P622" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="623" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A623" s="1" t="s">
         <v>642</v>
       </c>
@@ -34683,8 +34884,11 @@
       <c r="O623">
         <v>0</v>
       </c>
-    </row>
-    <row r="624" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P623" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="624" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A624" s="1" t="s">
         <v>643</v>
       </c>
@@ -34730,8 +34934,11 @@
       <c r="O624">
         <v>0</v>
       </c>
-    </row>
-    <row r="625" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P624" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="625" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A625" s="1" t="s">
         <v>644</v>
       </c>
@@ -34777,8 +34984,11 @@
       <c r="O625">
         <v>0</v>
       </c>
-    </row>
-    <row r="626" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P625" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="626" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A626" s="1" t="s">
         <v>645</v>
       </c>
@@ -34824,8 +35034,11 @@
       <c r="O626">
         <v>0</v>
       </c>
-    </row>
-    <row r="627" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P626" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="627" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A627" s="1" t="s">
         <v>646</v>
       </c>
@@ -34871,8 +35084,11 @@
       <c r="O627">
         <v>0</v>
       </c>
-    </row>
-    <row r="628" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P627" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="628" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A628" s="1" t="s">
         <v>647</v>
       </c>
@@ -34918,8 +35134,11 @@
       <c r="O628">
         <v>0</v>
       </c>
-    </row>
-    <row r="629" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P628" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="629" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A629" s="1" t="s">
         <v>648</v>
       </c>
@@ -34965,8 +35184,11 @@
       <c r="O629">
         <v>0</v>
       </c>
-    </row>
-    <row r="630" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P629" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="630" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A630" s="1" t="s">
         <v>649</v>
       </c>
@@ -35012,8 +35234,11 @@
       <c r="O630">
         <v>0</v>
       </c>
-    </row>
-    <row r="631" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P630" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="631" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A631" s="1" t="s">
         <v>650</v>
       </c>
@@ -35059,8 +35284,11 @@
       <c r="O631">
         <v>0</v>
       </c>
-    </row>
-    <row r="632" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P631" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="632" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A632" s="1" t="s">
         <v>651</v>
       </c>
@@ -35106,8 +35334,11 @@
       <c r="O632">
         <v>0</v>
       </c>
-    </row>
-    <row r="633" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P632" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="633" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A633" s="1" t="s">
         <v>652</v>
       </c>
@@ -35153,8 +35384,11 @@
       <c r="O633">
         <v>0</v>
       </c>
-    </row>
-    <row r="634" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P633" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="634" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A634" s="1" t="s">
         <v>653</v>
       </c>
@@ -35200,8 +35434,11 @@
       <c r="O634">
         <v>0</v>
       </c>
-    </row>
-    <row r="635" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P634" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="635" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A635" s="1" t="s">
         <v>654</v>
       </c>
@@ -35247,8 +35484,11 @@
       <c r="O635">
         <v>0</v>
       </c>
-    </row>
-    <row r="636" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P635" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="636" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A636" s="1" t="s">
         <v>655</v>
       </c>
@@ -35294,8 +35534,11 @@
       <c r="O636">
         <v>0</v>
       </c>
-    </row>
-    <row r="637" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P636" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="637" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A637" s="1" t="s">
         <v>656</v>
       </c>
@@ -35341,8 +35584,11 @@
       <c r="O637">
         <v>0</v>
       </c>
-    </row>
-    <row r="638" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P637" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="638" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A638" s="1" t="s">
         <v>657</v>
       </c>
@@ -35388,8 +35634,11 @@
       <c r="O638">
         <v>0</v>
       </c>
-    </row>
-    <row r="639" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P638" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="639" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A639" s="1" t="s">
         <v>658</v>
       </c>
@@ -35435,8 +35684,11 @@
       <c r="O639">
         <v>0</v>
       </c>
-    </row>
-    <row r="640" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P639" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="640" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A640" s="1" t="s">
         <v>659</v>
       </c>
@@ -35482,8 +35734,11 @@
       <c r="O640">
         <v>0</v>
       </c>
-    </row>
-    <row r="641" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P640" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="641" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A641" s="1" t="s">
         <v>660</v>
       </c>
@@ -35529,8 +35784,11 @@
       <c r="O641">
         <v>0</v>
       </c>
-    </row>
-    <row r="642" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P641" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="642" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A642" s="1" t="s">
         <v>661</v>
       </c>
@@ -35576,8 +35834,11 @@
       <c r="O642">
         <v>0</v>
       </c>
-    </row>
-    <row r="643" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P642" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="643" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A643" s="1" t="s">
         <v>662</v>
       </c>
@@ -35623,8 +35884,11 @@
       <c r="O643">
         <v>0</v>
       </c>
-    </row>
-    <row r="644" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P643" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="644" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A644" s="1" t="s">
         <v>663</v>
       </c>
@@ -35670,8 +35934,11 @@
       <c r="O644">
         <v>0</v>
       </c>
-    </row>
-    <row r="645" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P644" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="645" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A645" s="1" t="s">
         <v>664</v>
       </c>
@@ -35717,8 +35984,11 @@
       <c r="O645">
         <v>0</v>
       </c>
-    </row>
-    <row r="646" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P645" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="646" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A646" s="1" t="s">
         <v>665</v>
       </c>
@@ -35764,8 +36034,11 @@
       <c r="O646">
         <v>0</v>
       </c>
-    </row>
-    <row r="647" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P646" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="647" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A647" s="1" t="s">
         <v>666</v>
       </c>
@@ -35811,8 +36084,11 @@
       <c r="O647">
         <v>0</v>
       </c>
-    </row>
-    <row r="648" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P647" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="648" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A648" s="1" t="s">
         <v>563</v>
       </c>
@@ -35858,8 +36134,11 @@
       <c r="O648">
         <v>0</v>
       </c>
-    </row>
-    <row r="649" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P648" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="649" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A649" s="1" t="s">
         <v>667</v>
       </c>
@@ -35905,8 +36184,11 @@
       <c r="O649">
         <v>0</v>
       </c>
-    </row>
-    <row r="650" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P649" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="650" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A650" s="1" t="s">
         <v>668</v>
       </c>
@@ -35952,8 +36234,11 @@
       <c r="O650">
         <v>0</v>
       </c>
-    </row>
-    <row r="651" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P650" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="651" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A651" s="1" t="s">
         <v>669</v>
       </c>
@@ -35999,8 +36284,11 @@
       <c r="O651">
         <v>0</v>
       </c>
-    </row>
-    <row r="652" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P651" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="652" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A652" s="1" t="s">
         <v>670</v>
       </c>
@@ -36046,8 +36334,11 @@
       <c r="O652">
         <v>0</v>
       </c>
-    </row>
-    <row r="653" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P652" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="653" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A653" s="1" t="s">
         <v>671</v>
       </c>
@@ -36093,8 +36384,11 @@
       <c r="O653">
         <v>0</v>
       </c>
-    </row>
-    <row r="654" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P653" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="654" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A654" s="1" t="s">
         <v>672</v>
       </c>
@@ -36140,8 +36434,11 @@
       <c r="O654">
         <v>0</v>
       </c>
-    </row>
-    <row r="655" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P654" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="655" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A655" s="1" t="s">
         <v>673</v>
       </c>
@@ -36187,8 +36484,11 @@
       <c r="O655">
         <v>0</v>
       </c>
-    </row>
-    <row r="656" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P655" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="656" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A656" s="1" t="s">
         <v>674</v>
       </c>
@@ -36234,8 +36534,11 @@
       <c r="O656">
         <v>0</v>
       </c>
-    </row>
-    <row r="657" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P656" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="657" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A657" s="1" t="s">
         <v>675</v>
       </c>
@@ -36281,8 +36584,11 @@
       <c r="O657">
         <v>0</v>
       </c>
-    </row>
-    <row r="658" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P657" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="658" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A658" s="1" t="s">
         <v>676</v>
       </c>
@@ -36328,8 +36634,11 @@
       <c r="O658">
         <v>0</v>
       </c>
-    </row>
-    <row r="659" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P658" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="659" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A659" s="1" t="s">
         <v>677</v>
       </c>
@@ -36375,8 +36684,11 @@
       <c r="O659">
         <v>0</v>
       </c>
-    </row>
-    <row r="660" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P659" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="660" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A660" s="1" t="s">
         <v>678</v>
       </c>
@@ -36422,8 +36734,11 @@
       <c r="O660">
         <v>0</v>
       </c>
-    </row>
-    <row r="661" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P660" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="661" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A661" s="1" t="s">
         <v>679</v>
       </c>
@@ -36469,8 +36784,11 @@
       <c r="O661">
         <v>0</v>
       </c>
-    </row>
-    <row r="662" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P661" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="662" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A662" s="1" t="s">
         <v>680</v>
       </c>
@@ -36516,8 +36834,11 @@
       <c r="O662">
         <v>0</v>
       </c>
-    </row>
-    <row r="663" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P662" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="663" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A663" s="1" t="s">
         <v>681</v>
       </c>
@@ -36563,8 +36884,11 @@
       <c r="O663">
         <v>0</v>
       </c>
-    </row>
-    <row r="664" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P663" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="664" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A664" s="1" t="s">
         <v>682</v>
       </c>
@@ -36610,8 +36934,11 @@
       <c r="O664">
         <v>0</v>
       </c>
-    </row>
-    <row r="665" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P664" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="665" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A665" s="1" t="s">
         <v>683</v>
       </c>
@@ -36657,8 +36984,11 @@
       <c r="O665">
         <v>0</v>
       </c>
-    </row>
-    <row r="666" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P665" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="666" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A666" s="1" t="s">
         <v>684</v>
       </c>
@@ -36704,8 +37034,11 @@
       <c r="O666">
         <v>0</v>
       </c>
-    </row>
-    <row r="667" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P666" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="667" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A667" s="1" t="s">
         <v>685</v>
       </c>
@@ -36751,8 +37084,11 @@
       <c r="O667">
         <v>0</v>
       </c>
-    </row>
-    <row r="668" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P667" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="668" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A668" s="1" t="s">
         <v>686</v>
       </c>
@@ -36798,8 +37134,11 @@
       <c r="O668">
         <v>0</v>
       </c>
-    </row>
-    <row r="669" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P668" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="669" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A669" s="1" t="s">
         <v>687</v>
       </c>
@@ -36845,8 +37184,11 @@
       <c r="O669">
         <v>0</v>
       </c>
-    </row>
-    <row r="670" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P669" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="670" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A670" s="1" t="s">
         <v>688</v>
       </c>
@@ -36892,8 +37234,11 @@
       <c r="O670">
         <v>0</v>
       </c>
-    </row>
-    <row r="671" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P670" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="671" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A671" s="1" t="s">
         <v>689</v>
       </c>
@@ -36939,8 +37284,11 @@
       <c r="O671">
         <v>0</v>
       </c>
-    </row>
-    <row r="672" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P671" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="672" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A672" s="1" t="s">
         <v>690</v>
       </c>
@@ -36986,8 +37334,11 @@
       <c r="O672">
         <v>0</v>
       </c>
-    </row>
-    <row r="673" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P672" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="673" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A673" s="1" t="s">
         <v>691</v>
       </c>
@@ -37033,8 +37384,11 @@
       <c r="O673">
         <v>0</v>
       </c>
-    </row>
-    <row r="674" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P673" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="674" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A674" s="1" t="s">
         <v>692</v>
       </c>
@@ -37080,8 +37434,11 @@
       <c r="O674">
         <v>0</v>
       </c>
-    </row>
-    <row r="675" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P674" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="675" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A675" s="1" t="s">
         <v>693</v>
       </c>
@@ -37127,8 +37484,11 @@
       <c r="O675">
         <v>0</v>
       </c>
-    </row>
-    <row r="676" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P675" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="676" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A676" s="1" t="s">
         <v>694</v>
       </c>
@@ -37174,8 +37534,11 @@
       <c r="O676">
         <v>0</v>
       </c>
-    </row>
-    <row r="677" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P676" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="677" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A677" s="1" t="s">
         <v>695</v>
       </c>
@@ -37221,8 +37584,11 @@
       <c r="O677">
         <v>0</v>
       </c>
-    </row>
-    <row r="678" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P677" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="678" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A678" s="1" t="s">
         <v>696</v>
       </c>
@@ -37268,8 +37634,11 @@
       <c r="O678">
         <v>0</v>
       </c>
-    </row>
-    <row r="679" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P678" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="679" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A679" s="1" t="s">
         <v>697</v>
       </c>
@@ -37315,8 +37684,11 @@
       <c r="O679">
         <v>0</v>
       </c>
-    </row>
-    <row r="680" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P679" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="680" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A680" s="1" t="s">
         <v>698</v>
       </c>
@@ -37362,8 +37734,11 @@
       <c r="O680">
         <v>0</v>
       </c>
-    </row>
-    <row r="681" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P680" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="681" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A681" s="1" t="s">
         <v>699</v>
       </c>
@@ -37409,8 +37784,11 @@
       <c r="O681">
         <v>0</v>
       </c>
-    </row>
-    <row r="682" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P681" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="682" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A682" s="1" t="s">
         <v>700</v>
       </c>
@@ -37456,8 +37834,11 @@
       <c r="O682">
         <v>0</v>
       </c>
-    </row>
-    <row r="683" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P682" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="683" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A683" s="1" t="s">
         <v>701</v>
       </c>
@@ -37503,8 +37884,11 @@
       <c r="O683">
         <v>0</v>
       </c>
-    </row>
-    <row r="684" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P683" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="684" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A684" s="1" t="s">
         <v>702</v>
       </c>
@@ -37550,8 +37934,11 @@
       <c r="O684">
         <v>0</v>
       </c>
-    </row>
-    <row r="685" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P684" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="685" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A685" s="1" t="s">
         <v>703</v>
       </c>
@@ -37597,8 +37984,11 @@
       <c r="O685">
         <v>0</v>
       </c>
-    </row>
-    <row r="686" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P685" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="686" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A686" s="1" t="s">
         <v>704</v>
       </c>
@@ -37644,8 +38034,11 @@
       <c r="O686">
         <v>0</v>
       </c>
-    </row>
-    <row r="687" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P686" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="687" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A687" s="1" t="s">
         <v>705</v>
       </c>
@@ -37691,8 +38084,11 @@
       <c r="O687">
         <v>0</v>
       </c>
-    </row>
-    <row r="688" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P687" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="688" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A688" s="1" t="s">
         <v>706</v>
       </c>
@@ -37738,8 +38134,11 @@
       <c r="O688">
         <v>0</v>
       </c>
-    </row>
-    <row r="689" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P688" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="689" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A689" s="1" t="s">
         <v>707</v>
       </c>
@@ -37785,8 +38184,11 @@
       <c r="O689">
         <v>0</v>
       </c>
-    </row>
-    <row r="690" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P689" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="690" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A690" s="1" t="s">
         <v>708</v>
       </c>
@@ -37832,8 +38234,11 @@
       <c r="O690">
         <v>0</v>
       </c>
-    </row>
-    <row r="691" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P690" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="691" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A691" s="1" t="s">
         <v>709</v>
       </c>
@@ -37879,8 +38284,11 @@
       <c r="O691">
         <v>0</v>
       </c>
-    </row>
-    <row r="692" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P691" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="692" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A692" s="1" t="s">
         <v>710</v>
       </c>
@@ -37926,8 +38334,11 @@
       <c r="O692">
         <v>0</v>
       </c>
-    </row>
-    <row r="693" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P692" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="693" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A693" s="1" t="s">
         <v>711</v>
       </c>
@@ -37973,8 +38384,11 @@
       <c r="O693">
         <v>0</v>
       </c>
-    </row>
-    <row r="694" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P693" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="694" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A694" s="1" t="s">
         <v>712</v>
       </c>
@@ -38020,8 +38434,11 @@
       <c r="O694">
         <v>0</v>
       </c>
-    </row>
-    <row r="695" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P694" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="695" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A695" s="1" t="s">
         <v>713</v>
       </c>
@@ -38067,8 +38484,11 @@
       <c r="O695">
         <v>0</v>
       </c>
-    </row>
-    <row r="696" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P695" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="696" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A696" s="1" t="s">
         <v>714</v>
       </c>
@@ -38114,8 +38534,11 @@
       <c r="O696">
         <v>0</v>
       </c>
-    </row>
-    <row r="697" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P696" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="697" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A697" s="1" t="s">
         <v>715</v>
       </c>
@@ -38161,8 +38584,11 @@
       <c r="O697">
         <v>0</v>
       </c>
-    </row>
-    <row r="698" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P697" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="698" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A698" s="1" t="s">
         <v>716</v>
       </c>
@@ -38208,8 +38634,11 @@
       <c r="O698">
         <v>0</v>
       </c>
-    </row>
-    <row r="699" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P698" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="699" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A699" s="1" t="s">
         <v>717</v>
       </c>
@@ -38255,8 +38684,11 @@
       <c r="O699">
         <v>0</v>
       </c>
-    </row>
-    <row r="700" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P699" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="700" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A700" s="1" t="s">
         <v>718</v>
       </c>
@@ -38302,8 +38734,11 @@
       <c r="O700">
         <v>0</v>
       </c>
-    </row>
-    <row r="701" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P700" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="701" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A701" s="1" t="s">
         <v>719</v>
       </c>
@@ -38349,8 +38784,11 @@
       <c r="O701">
         <v>0</v>
       </c>
-    </row>
-    <row r="702" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P701" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="702" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A702" s="1" t="s">
         <v>720</v>
       </c>
@@ -38396,8 +38834,11 @@
       <c r="O702">
         <v>0</v>
       </c>
-    </row>
-    <row r="703" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P702" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="703" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A703" s="1" t="s">
         <v>721</v>
       </c>
@@ -38443,8 +38884,11 @@
       <c r="O703">
         <v>0</v>
       </c>
-    </row>
-    <row r="704" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P703" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="704" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A704" s="1" t="s">
         <v>722</v>
       </c>
@@ -38490,8 +38934,11 @@
       <c r="O704">
         <v>0</v>
       </c>
-    </row>
-    <row r="705" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P704" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="705" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A705" s="1" t="s">
         <v>723</v>
       </c>
@@ -38537,8 +38984,11 @@
       <c r="O705">
         <v>0</v>
       </c>
-    </row>
-    <row r="706" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P705" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="706" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A706" s="1" t="s">
         <v>724</v>
       </c>
@@ -38584,8 +39034,11 @@
       <c r="O706">
         <v>0</v>
       </c>
-    </row>
-    <row r="707" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P706" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="707" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A707" s="1" t="s">
         <v>725</v>
       </c>
@@ -38631,8 +39084,11 @@
       <c r="O707">
         <v>0</v>
       </c>
-    </row>
-    <row r="708" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P707" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="708" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A708" s="1" t="s">
         <v>726</v>
       </c>
@@ -38678,8 +39134,11 @@
       <c r="O708">
         <v>0</v>
       </c>
-    </row>
-    <row r="709" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P708" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="709" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A709" s="1" t="s">
         <v>727</v>
       </c>
@@ -38725,8 +39184,11 @@
       <c r="O709">
         <v>0</v>
       </c>
-    </row>
-    <row r="710" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P709" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="710" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A710" s="1" t="s">
         <v>728</v>
       </c>
@@ -38772,8 +39234,11 @@
       <c r="O710">
         <v>0</v>
       </c>
-    </row>
-    <row r="711" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P710" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="711" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A711" s="1" t="s">
         <v>729</v>
       </c>
@@ -38819,8 +39284,11 @@
       <c r="O711">
         <v>0</v>
       </c>
-    </row>
-    <row r="712" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P711" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="712" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A712" s="1" t="s">
         <v>730</v>
       </c>
@@ -38866,8 +39334,11 @@
       <c r="O712">
         <v>0</v>
       </c>
-    </row>
-    <row r="713" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P712" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="713" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A713" s="1" t="s">
         <v>731</v>
       </c>
@@ -38913,8 +39384,11 @@
       <c r="O713">
         <v>0</v>
       </c>
-    </row>
-    <row r="714" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P713" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="714" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A714" s="1" t="s">
         <v>732</v>
       </c>
@@ -38960,8 +39434,11 @@
       <c r="O714">
         <v>0</v>
       </c>
-    </row>
-    <row r="715" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P714" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="715" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A715" s="1" t="s">
         <v>733</v>
       </c>
@@ -39007,8 +39484,11 @@
       <c r="O715">
         <v>0</v>
       </c>
-    </row>
-    <row r="716" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P715" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="716" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A716" s="1" t="s">
         <v>734</v>
       </c>
@@ -39054,8 +39534,11 @@
       <c r="O716">
         <v>0</v>
       </c>
-    </row>
-    <row r="717" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P716" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="717" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A717" s="1" t="s">
         <v>735</v>
       </c>
@@ -39101,8 +39584,11 @@
       <c r="O717">
         <v>0</v>
       </c>
-    </row>
-    <row r="718" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P717" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="718" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A718" s="1" t="s">
         <v>736</v>
       </c>
@@ -39148,8 +39634,11 @@
       <c r="O718">
         <v>0</v>
       </c>
-    </row>
-    <row r="719" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P718" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="719" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A719" s="1" t="s">
         <v>737</v>
       </c>
@@ -39195,8 +39684,11 @@
       <c r="O719">
         <v>0</v>
       </c>
-    </row>
-    <row r="720" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P719" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="720" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A720" s="1" t="s">
         <v>738</v>
       </c>
@@ -39242,8 +39734,11 @@
       <c r="O720">
         <v>0</v>
       </c>
-    </row>
-    <row r="721" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P720" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="721" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A721" s="1" t="s">
         <v>739</v>
       </c>
@@ -39289,8 +39784,11 @@
       <c r="O721">
         <v>0</v>
       </c>
-    </row>
-    <row r="722" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P721" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="722" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A722" s="1" t="s">
         <v>740</v>
       </c>
@@ -39336,8 +39834,11 @@
       <c r="O722">
         <v>0</v>
       </c>
-    </row>
-    <row r="723" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P722" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="723" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A723" s="1" t="s">
         <v>741</v>
       </c>
@@ -39383,8 +39884,11 @@
       <c r="O723">
         <v>0</v>
       </c>
-    </row>
-    <row r="724" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P723" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="724" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A724" s="1" t="s">
         <v>742</v>
       </c>
@@ -39430,8 +39934,11 @@
       <c r="O724">
         <v>0</v>
       </c>
-    </row>
-    <row r="725" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P724" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="725" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A725" s="1" t="s">
         <v>743</v>
       </c>
@@ -39477,8 +39984,11 @@
       <c r="O725">
         <v>0</v>
       </c>
-    </row>
-    <row r="726" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P725" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="726" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A726" s="1" t="s">
         <v>744</v>
       </c>
@@ -39524,8 +40034,11 @@
       <c r="O726">
         <v>0</v>
       </c>
-    </row>
-    <row r="727" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P726" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="727" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A727" s="1" t="s">
         <v>745</v>
       </c>
@@ -39571,8 +40084,11 @@
       <c r="O727">
         <v>0</v>
       </c>
-    </row>
-    <row r="728" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P727" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="728" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A728" s="1" t="s">
         <v>746</v>
       </c>
@@ -39618,8 +40134,11 @@
       <c r="O728">
         <v>0</v>
       </c>
-    </row>
-    <row r="729" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P728" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="729" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A729" s="1" t="s">
         <v>747</v>
       </c>
@@ -39665,8 +40184,11 @@
       <c r="O729">
         <v>0</v>
       </c>
-    </row>
-    <row r="730" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P729" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="730" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A730" s="1" t="s">
         <v>748</v>
       </c>
@@ -39712,8 +40234,11 @@
       <c r="O730">
         <v>0</v>
       </c>
-    </row>
-    <row r="731" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P730" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="731" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A731" s="1" t="s">
         <v>749</v>
       </c>
@@ -39759,8 +40284,11 @@
       <c r="O731">
         <v>0</v>
       </c>
-    </row>
-    <row r="732" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P731" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="732" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A732" s="1" t="s">
         <v>750</v>
       </c>
@@ -39806,8 +40334,11 @@
       <c r="O732">
         <v>0</v>
       </c>
-    </row>
-    <row r="733" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P732" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="733" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A733" s="1" t="s">
         <v>751</v>
       </c>
@@ -39853,8 +40384,11 @@
       <c r="O733">
         <v>0</v>
       </c>
-    </row>
-    <row r="734" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P733" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="734" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A734" s="1" t="s">
         <v>752</v>
       </c>
@@ -39900,8 +40434,11 @@
       <c r="O734">
         <v>0</v>
       </c>
-    </row>
-    <row r="735" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P734" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="735" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A735" s="1" t="s">
         <v>753</v>
       </c>
@@ -39947,8 +40484,11 @@
       <c r="O735">
         <v>0</v>
       </c>
-    </row>
-    <row r="736" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P735" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="736" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A736" s="1" t="s">
         <v>67</v>
       </c>
@@ -39994,8 +40534,11 @@
       <c r="O736">
         <v>0</v>
       </c>
-    </row>
-    <row r="737" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P736" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="737" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A737" s="1" t="s">
         <v>754</v>
       </c>
@@ -40041,8 +40584,11 @@
       <c r="O737">
         <v>0</v>
       </c>
-    </row>
-    <row r="738" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P737" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="738" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A738" s="1" t="s">
         <v>755</v>
       </c>
@@ -40088,8 +40634,11 @@
       <c r="O738">
         <v>0</v>
       </c>
-    </row>
-    <row r="739" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P738" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="739" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A739" s="1" t="s">
         <v>756</v>
       </c>
@@ -40135,8 +40684,11 @@
       <c r="O739">
         <v>0</v>
       </c>
-    </row>
-    <row r="740" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P739" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="740" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A740" s="1" t="s">
         <v>757</v>
       </c>
@@ -40182,8 +40734,11 @@
       <c r="O740">
         <v>0</v>
       </c>
-    </row>
-    <row r="741" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P740" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="741" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A741" s="1" t="s">
         <v>758</v>
       </c>
@@ -40229,8 +40784,11 @@
       <c r="O741">
         <v>0</v>
       </c>
-    </row>
-    <row r="742" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P741" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="742" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A742" s="1" t="s">
         <v>759</v>
       </c>
@@ -40276,8 +40834,11 @@
       <c r="O742">
         <v>0</v>
       </c>
-    </row>
-    <row r="743" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P742" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="743" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A743" s="1" t="s">
         <v>760</v>
       </c>
@@ -40323,8 +40884,11 @@
       <c r="O743">
         <v>0</v>
       </c>
-    </row>
-    <row r="744" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P743" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="744" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A744" s="1" t="s">
         <v>761</v>
       </c>
@@ -40370,8 +40934,11 @@
       <c r="O744">
         <v>0</v>
       </c>
-    </row>
-    <row r="745" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P744" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="745" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A745" s="1" t="s">
         <v>762</v>
       </c>
@@ -40417,8 +40984,11 @@
       <c r="O745">
         <v>0</v>
       </c>
-    </row>
-    <row r="746" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P745" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="746" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A746" s="1" t="s">
         <v>763</v>
       </c>
@@ -40464,8 +41034,11 @@
       <c r="O746">
         <v>0</v>
       </c>
-    </row>
-    <row r="747" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P746" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="747" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A747" s="1" t="s">
         <v>601</v>
       </c>
@@ -40511,8 +41084,11 @@
       <c r="O747">
         <v>0</v>
       </c>
-    </row>
-    <row r="748" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P747" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="748" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A748" s="1" t="s">
         <v>602</v>
       </c>
@@ -40558,8 +41134,11 @@
       <c r="O748">
         <v>0</v>
       </c>
-    </row>
-    <row r="749" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P748" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="749" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A749" s="1" t="s">
         <v>764</v>
       </c>
@@ -40605,8 +41184,11 @@
       <c r="O749">
         <v>0</v>
       </c>
-    </row>
-    <row r="750" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P749" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="750" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A750" s="1" t="s">
         <v>765</v>
       </c>
@@ -40652,8 +41234,11 @@
       <c r="O750">
         <v>0</v>
       </c>
-    </row>
-    <row r="751" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P750" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="751" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A751" s="1" t="s">
         <v>766</v>
       </c>
@@ -40699,8 +41284,11 @@
       <c r="O751">
         <v>0</v>
       </c>
-    </row>
-    <row r="752" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P751" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="752" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A752" s="1" t="s">
         <v>767</v>
       </c>
@@ -40746,8 +41334,11 @@
       <c r="O752">
         <v>0</v>
       </c>
-    </row>
-    <row r="753" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P752" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="753" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A753" s="1" t="s">
         <v>768</v>
       </c>
@@ -40793,8 +41384,11 @@
       <c r="O753">
         <v>0</v>
       </c>
-    </row>
-    <row r="754" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P753" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="754" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A754" s="1" t="s">
         <v>769</v>
       </c>
@@ -40840,8 +41434,11 @@
       <c r="O754">
         <v>0</v>
       </c>
-    </row>
-    <row r="755" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P754" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="755" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A755" s="1" t="s">
         <v>770</v>
       </c>
@@ -40887,8 +41484,11 @@
       <c r="O755">
         <v>0</v>
       </c>
-    </row>
-    <row r="756" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P755" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="756" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A756" s="1" t="s">
         <v>771</v>
       </c>
@@ -40934,8 +41534,11 @@
       <c r="O756">
         <v>0</v>
       </c>
-    </row>
-    <row r="757" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P756" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="757" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A757" s="1" t="s">
         <v>772</v>
       </c>
@@ -40981,8 +41584,11 @@
       <c r="O757">
         <v>0</v>
       </c>
-    </row>
-    <row r="758" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P757" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="758" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A758" s="1" t="s">
         <v>773</v>
       </c>
@@ -41028,8 +41634,11 @@
       <c r="O758">
         <v>0</v>
       </c>
-    </row>
-    <row r="759" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P758" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="759" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A759" s="1" t="s">
         <v>774</v>
       </c>
@@ -41075,8 +41684,11 @@
       <c r="O759">
         <v>0</v>
       </c>
-    </row>
-    <row r="760" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P759" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="760" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A760" s="1" t="s">
         <v>775</v>
       </c>
@@ -41122,8 +41734,11 @@
       <c r="O760">
         <v>0</v>
       </c>
-    </row>
-    <row r="761" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P760" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="761" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A761" s="1" t="s">
         <v>776</v>
       </c>
@@ -41169,8 +41784,11 @@
       <c r="O761">
         <v>0</v>
       </c>
-    </row>
-    <row r="762" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P761" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="762" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A762" s="1" t="s">
         <v>777</v>
       </c>
@@ -41216,8 +41834,11 @@
       <c r="O762">
         <v>0</v>
       </c>
-    </row>
-    <row r="763" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P762" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="763" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A763" s="1" t="s">
         <v>778</v>
       </c>
@@ -41263,8 +41884,11 @@
       <c r="O763">
         <v>0</v>
       </c>
-    </row>
-    <row r="764" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P763" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="764" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A764" s="1" t="s">
         <v>779</v>
       </c>
@@ -41310,8 +41934,11 @@
       <c r="O764">
         <v>0</v>
       </c>
-    </row>
-    <row r="765" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P764" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="765" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A765" s="1" t="s">
         <v>780</v>
       </c>
@@ -41357,8 +41984,11 @@
       <c r="O765">
         <v>0</v>
       </c>
-    </row>
-    <row r="766" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P765" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="766" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A766" s="1" t="s">
         <v>781</v>
       </c>
@@ -41404,8 +42034,11 @@
       <c r="O766">
         <v>0</v>
       </c>
-    </row>
-    <row r="767" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P766" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="767" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A767" s="1" t="s">
         <v>782</v>
       </c>
@@ -41451,8 +42084,11 @@
       <c r="O767">
         <v>0</v>
       </c>
-    </row>
-    <row r="768" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P767" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="768" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A768" s="1" t="s">
         <v>783</v>
       </c>
@@ -41498,8 +42134,11 @@
       <c r="O768">
         <v>0</v>
       </c>
-    </row>
-    <row r="769" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P768" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="769" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A769" s="1" t="s">
         <v>784</v>
       </c>
@@ -41545,8 +42184,11 @@
       <c r="O769">
         <v>0</v>
       </c>
-    </row>
-    <row r="770" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P769" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="770" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A770" s="1" t="s">
         <v>785</v>
       </c>
@@ -41592,8 +42234,11 @@
       <c r="O770">
         <v>0</v>
       </c>
-    </row>
-    <row r="771" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P770" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="771" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A771" s="1" t="s">
         <v>786</v>
       </c>
@@ -41639,8 +42284,11 @@
       <c r="O771">
         <v>0</v>
       </c>
-    </row>
-    <row r="772" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P771" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="772" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A772" s="1" t="s">
         <v>787</v>
       </c>
@@ -41686,8 +42334,11 @@
       <c r="O772">
         <v>0</v>
       </c>
-    </row>
-    <row r="773" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P772" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="773" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A773" s="1" t="s">
         <v>788</v>
       </c>
@@ -41733,8 +42384,11 @@
       <c r="O773">
         <v>0</v>
       </c>
-    </row>
-    <row r="774" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P773" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="774" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A774" s="1" t="s">
         <v>789</v>
       </c>
@@ -41780,8 +42434,11 @@
       <c r="O774">
         <v>0</v>
       </c>
-    </row>
-    <row r="775" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P774" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="775" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A775" s="1" t="s">
         <v>790</v>
       </c>
@@ -41827,8 +42484,11 @@
       <c r="O775">
         <v>0</v>
       </c>
-    </row>
-    <row r="776" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P775" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="776" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A776" s="1" t="s">
         <v>791</v>
       </c>
@@ -41874,8 +42534,11 @@
       <c r="O776">
         <v>0</v>
       </c>
-    </row>
-    <row r="777" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P776" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="777" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A777" s="1" t="s">
         <v>792</v>
       </c>
@@ -41921,8 +42584,11 @@
       <c r="O777">
         <v>0</v>
       </c>
-    </row>
-    <row r="778" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P777" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="778" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A778" s="1" t="s">
         <v>793</v>
       </c>
@@ -41968,8 +42634,11 @@
       <c r="O778">
         <v>0</v>
       </c>
-    </row>
-    <row r="779" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P778" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="779" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A779" s="1" t="s">
         <v>794</v>
       </c>
@@ -42015,8 +42684,11 @@
       <c r="O779">
         <v>0</v>
       </c>
-    </row>
-    <row r="780" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P779" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="780" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A780" s="1" t="s">
         <v>795</v>
       </c>
@@ -42062,8 +42734,11 @@
       <c r="O780">
         <v>0</v>
       </c>
-    </row>
-    <row r="781" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P780" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="781" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A781" s="1" t="s">
         <v>796</v>
       </c>
@@ -42109,8 +42784,11 @@
       <c r="O781">
         <v>0</v>
       </c>
-    </row>
-    <row r="782" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P781" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="782" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A782" s="1" t="s">
         <v>797</v>
       </c>
@@ -42156,8 +42834,11 @@
       <c r="O782">
         <v>0</v>
       </c>
-    </row>
-    <row r="783" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P782" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="783" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A783" s="1" t="s">
         <v>798</v>
       </c>
@@ -42203,8 +42884,11 @@
       <c r="O783">
         <v>0</v>
       </c>
-    </row>
-    <row r="784" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P783" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="784" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A784" s="1" t="s">
         <v>799</v>
       </c>
@@ -42250,8 +42934,11 @@
       <c r="O784">
         <v>0</v>
       </c>
-    </row>
-    <row r="785" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P784" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="785" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A785" s="1" t="s">
         <v>800</v>
       </c>
@@ -42297,8 +42984,11 @@
       <c r="O785">
         <v>0</v>
       </c>
-    </row>
-    <row r="786" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P785" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="786" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A786" s="1" t="s">
         <v>801</v>
       </c>
@@ -42344,8 +43034,11 @@
       <c r="O786">
         <v>0</v>
       </c>
-    </row>
-    <row r="787" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P786" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="787" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A787" s="1" t="s">
         <v>802</v>
       </c>
@@ -42391,8 +43084,11 @@
       <c r="O787">
         <v>0</v>
       </c>
-    </row>
-    <row r="788" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P787" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="788" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A788" s="1" t="s">
         <v>803</v>
       </c>
@@ -42438,8 +43134,11 @@
       <c r="O788">
         <v>0</v>
       </c>
-    </row>
-    <row r="789" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P788" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="789" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A789" s="1" t="s">
         <v>804</v>
       </c>
@@ -42485,8 +43184,11 @@
       <c r="O789">
         <v>0</v>
       </c>
-    </row>
-    <row r="790" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P789" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="790" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A790" s="1" t="s">
         <v>805</v>
       </c>
@@ -42532,8 +43234,11 @@
       <c r="O790">
         <v>0</v>
       </c>
-    </row>
-    <row r="791" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P790" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="791" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A791" s="1" t="s">
         <v>806</v>
       </c>
@@ -42579,8 +43284,11 @@
       <c r="O791">
         <v>0</v>
       </c>
-    </row>
-    <row r="792" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P791" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="792" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A792" s="1" t="s">
         <v>807</v>
       </c>
@@ -42626,8 +43334,11 @@
       <c r="O792">
         <v>0</v>
       </c>
-    </row>
-    <row r="793" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P792" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="793" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A793" s="1" t="s">
         <v>808</v>
       </c>
@@ -42673,8 +43384,11 @@
       <c r="O793">
         <v>0</v>
       </c>
-    </row>
-    <row r="794" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P793" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="794" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A794" s="1" t="s">
         <v>809</v>
       </c>
@@ -42720,8 +43434,11 @@
       <c r="O794">
         <v>0</v>
       </c>
-    </row>
-    <row r="795" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P794" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="795" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A795" s="1" t="s">
         <v>810</v>
       </c>
@@ -42767,8 +43484,11 @@
       <c r="O795">
         <v>0</v>
       </c>
-    </row>
-    <row r="796" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P795" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="796" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A796" s="1" t="s">
         <v>811</v>
       </c>
@@ -42814,8 +43534,11 @@
       <c r="O796">
         <v>0</v>
       </c>
-    </row>
-    <row r="797" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P796" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="797" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A797" s="1" t="s">
         <v>812</v>
       </c>
@@ -42861,8 +43584,11 @@
       <c r="O797">
         <v>0</v>
       </c>
-    </row>
-    <row r="798" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P797" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="798" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A798" s="1" t="s">
         <v>813</v>
       </c>
@@ -42908,8 +43634,11 @@
       <c r="O798">
         <v>0</v>
       </c>
-    </row>
-    <row r="799" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P798" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="799" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A799" s="1" t="s">
         <v>814</v>
       </c>
@@ -42955,8 +43684,11 @@
       <c r="O799">
         <v>0</v>
       </c>
-    </row>
-    <row r="800" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P799" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="800" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A800" s="1" t="s">
         <v>815</v>
       </c>
@@ -43002,8 +43734,11 @@
       <c r="O800">
         <v>0</v>
       </c>
-    </row>
-    <row r="801" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P800" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="801" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A801" s="1" t="s">
         <v>816</v>
       </c>
@@ -43049,8 +43784,11 @@
       <c r="O801">
         <v>0</v>
       </c>
-    </row>
-    <row r="802" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P801" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="802" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A802" s="1" t="s">
         <v>817</v>
       </c>
@@ -43096,8 +43834,11 @@
       <c r="O802">
         <v>0</v>
       </c>
-    </row>
-    <row r="803" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P802" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="803" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A803" s="1" t="s">
         <v>818</v>
       </c>
@@ -43143,8 +43884,11 @@
       <c r="O803">
         <v>0</v>
       </c>
-    </row>
-    <row r="804" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P803" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="804" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A804" s="1" t="s">
         <v>819</v>
       </c>
@@ -43190,8 +43934,11 @@
       <c r="O804">
         <v>0</v>
       </c>
-    </row>
-    <row r="805" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P804" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="805" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A805" s="1" t="s">
         <v>820</v>
       </c>
@@ -43237,8 +43984,11 @@
       <c r="O805">
         <v>0</v>
       </c>
-    </row>
-    <row r="806" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P805" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="806" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A806" s="1" t="s">
         <v>821</v>
       </c>
@@ -43284,8 +44034,11 @@
       <c r="O806">
         <v>0</v>
       </c>
-    </row>
-    <row r="807" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P806" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="807" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A807" s="1" t="s">
         <v>822</v>
       </c>
@@ -43331,8 +44084,11 @@
       <c r="O807">
         <v>0</v>
       </c>
-    </row>
-    <row r="808" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P807" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="808" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A808" s="1" t="s">
         <v>823</v>
       </c>
@@ -43378,8 +44134,11 @@
       <c r="O808">
         <v>0</v>
       </c>
-    </row>
-    <row r="809" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P808" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="809" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A809" s="1" t="s">
         <v>824</v>
       </c>
@@ -43425,8 +44184,11 @@
       <c r="O809">
         <v>0</v>
       </c>
-    </row>
-    <row r="810" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P809" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="810" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A810" s="1" t="s">
         <v>825</v>
       </c>
@@ -43472,8 +44234,11 @@
       <c r="O810">
         <v>0</v>
       </c>
-    </row>
-    <row r="811" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P810" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="811" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A811" s="1" t="s">
         <v>826</v>
       </c>
@@ -43519,8 +44284,11 @@
       <c r="O811">
         <v>0</v>
       </c>
-    </row>
-    <row r="812" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P811" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="812" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A812" s="1" t="s">
         <v>827</v>
       </c>
@@ -43566,8 +44334,11 @@
       <c r="O812">
         <v>0</v>
       </c>
-    </row>
-    <row r="813" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P812" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="813" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A813" s="1" t="s">
         <v>828</v>
       </c>
@@ -43613,8 +44384,11 @@
       <c r="O813">
         <v>0</v>
       </c>
-    </row>
-    <row r="814" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P813" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="814" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A814" s="1" t="s">
         <v>829</v>
       </c>
@@ -43660,8 +44434,11 @@
       <c r="O814">
         <v>0</v>
       </c>
-    </row>
-    <row r="815" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P814" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="815" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A815" s="1" t="s">
         <v>393</v>
       </c>
@@ -43707,8 +44484,11 @@
       <c r="O815">
         <v>0</v>
       </c>
-    </row>
-    <row r="816" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P815" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="816" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A816" s="1" t="s">
         <v>830</v>
       </c>
@@ -43754,8 +44534,11 @@
       <c r="O816">
         <v>0</v>
       </c>
-    </row>
-    <row r="817" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P816" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="817" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A817" s="1" t="s">
         <v>831</v>
       </c>
@@ -43801,8 +44584,11 @@
       <c r="O817">
         <v>0</v>
       </c>
-    </row>
-    <row r="818" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P817" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="818" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A818" s="1" t="s">
         <v>832</v>
       </c>
@@ -43848,8 +44634,11 @@
       <c r="O818">
         <v>0</v>
       </c>
-    </row>
-    <row r="819" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P818" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="819" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A819" s="1" t="s">
         <v>833</v>
       </c>
@@ -43895,8 +44684,11 @@
       <c r="O819">
         <v>0</v>
       </c>
-    </row>
-    <row r="820" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P819" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="820" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A820" s="1" t="s">
         <v>834</v>
       </c>
@@ -43942,8 +44734,11 @@
       <c r="O820">
         <v>0</v>
       </c>
-    </row>
-    <row r="821" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P820" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="821" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A821" s="1" t="s">
         <v>835</v>
       </c>
@@ -43989,8 +44784,11 @@
       <c r="O821">
         <v>0</v>
       </c>
-    </row>
-    <row r="822" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P821" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="822" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A822" s="1" t="s">
         <v>836</v>
       </c>
@@ -44036,8 +44834,11 @@
       <c r="O822">
         <v>0</v>
       </c>
-    </row>
-    <row r="823" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P822" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="823" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A823" s="1" t="s">
         <v>837</v>
       </c>
@@ -44083,8 +44884,11 @@
       <c r="O823">
         <v>0</v>
       </c>
-    </row>
-    <row r="824" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P823" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="824" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A824" s="1" t="s">
         <v>838</v>
       </c>
@@ -44130,8 +44934,11 @@
       <c r="O824">
         <v>0</v>
       </c>
-    </row>
-    <row r="825" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P824" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="825" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A825" s="1" t="s">
         <v>46</v>
       </c>
@@ -44177,8 +44984,11 @@
       <c r="O825">
         <v>0</v>
       </c>
-    </row>
-    <row r="826" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P825" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="826" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A826" s="1" t="s">
         <v>839</v>
       </c>
@@ -44224,8 +45034,11 @@
       <c r="O826">
         <v>0</v>
       </c>
-    </row>
-    <row r="827" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P826" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="827" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A827" s="1" t="s">
         <v>39</v>
       </c>
@@ -44271,8 +45084,11 @@
       <c r="O827">
         <v>0</v>
       </c>
-    </row>
-    <row r="828" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P827" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="828" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A828" s="1" t="s">
         <v>391</v>
       </c>
@@ -44318,8 +45134,11 @@
       <c r="O828">
         <v>0</v>
       </c>
-    </row>
-    <row r="829" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P828" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="829" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A829" s="1" t="s">
         <v>392</v>
       </c>
@@ -44365,8 +45184,11 @@
       <c r="O829">
         <v>0</v>
       </c>
-    </row>
-    <row r="830" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P829" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="830" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A830" t="s">
         <v>1002</v>
       </c>
@@ -44412,10 +45234,13 @@
       <c r="O830">
         <v>0</v>
       </c>
-    </row>
-    <row r="831" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P830" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="831" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A831" t="s">
-        <v>1003</v>
+        <v>115</v>
       </c>
       <c r="B831" t="s">
         <v>841</v>
@@ -44459,10 +45284,13 @@
       <c r="O831">
         <v>0</v>
       </c>
-    </row>
-    <row r="832" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P831" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="832" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A832" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B832" t="s">
         <v>841</v>
@@ -44506,10 +45334,13 @@
       <c r="O832">
         <v>0</v>
       </c>
-    </row>
-    <row r="833" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P832" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="833" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A833" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B833" t="s">
         <v>841</v>
@@ -44553,10 +45384,13 @@
       <c r="O833">
         <v>0</v>
       </c>
-    </row>
-    <row r="834" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P833" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="834" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A834" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B834" t="s">
         <v>841</v>
@@ -44600,10 +45434,13 @@
       <c r="O834">
         <v>0</v>
       </c>
-    </row>
-    <row r="835" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P834" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="835" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A835" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B835" t="s">
         <v>841</v>
@@ -44647,10 +45484,13 @@
       <c r="O835">
         <v>0</v>
       </c>
-    </row>
-    <row r="836" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P835" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="836" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A836" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B836" t="s">
         <v>841</v>
@@ -44694,10 +45534,13 @@
       <c r="O836">
         <v>0</v>
       </c>
-    </row>
-    <row r="837" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P836" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="837" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A837" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B837" t="s">
         <v>841</v>
@@ -44741,10 +45584,13 @@
       <c r="O837">
         <v>0</v>
       </c>
-    </row>
-    <row r="838" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P837" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="838" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A838" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B838" t="s">
         <v>841</v>
@@ -44788,10 +45634,13 @@
       <c r="O838">
         <v>0</v>
       </c>
-    </row>
-    <row r="839" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P838" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="839" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A839" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B839" t="s">
         <v>841</v>
@@ -44835,10 +45684,13 @@
       <c r="O839">
         <v>0</v>
       </c>
-    </row>
-    <row r="840" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P839" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="840" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A840" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B840" t="s">
         <v>841</v>
@@ -44882,10 +45734,13 @@
       <c r="O840">
         <v>0</v>
       </c>
-    </row>
-    <row r="841" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P840" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="841" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A841" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B841" t="s">
         <v>841</v>
@@ -44929,10 +45784,13 @@
       <c r="O841">
         <v>0</v>
       </c>
-    </row>
-    <row r="842" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P841" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="842" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A842" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B842" t="s">
         <v>841</v>
@@ -44976,10 +45834,13 @@
       <c r="O842">
         <v>0</v>
       </c>
-    </row>
-    <row r="843" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P842" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="843" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A843" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B843" t="s">
         <v>841</v>
@@ -45023,10 +45884,13 @@
       <c r="O843">
         <v>0</v>
       </c>
-    </row>
-    <row r="844" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P843" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="844" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A844" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B844" t="s">
         <v>841</v>
@@ -45070,10 +45934,13 @@
       <c r="O844">
         <v>0</v>
       </c>
-    </row>
-    <row r="845" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P844" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="845" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A845" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B845" t="s">
         <v>841</v>
@@ -45117,10 +45984,13 @@
       <c r="O845">
         <v>0</v>
       </c>
-    </row>
-    <row r="846" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P845" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="846" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A846" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B846" t="s">
         <v>841</v>
@@ -45164,10 +46034,13 @@
       <c r="O846">
         <v>0</v>
       </c>
-    </row>
-    <row r="847" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P846" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="847" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A847" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B847" t="s">
         <v>841</v>
@@ -45211,10 +46084,13 @@
       <c r="O847">
         <v>0</v>
       </c>
-    </row>
-    <row r="848" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P847" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="848" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A848" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B848" t="s">
         <v>841</v>
@@ -45258,10 +46134,13 @@
       <c r="O848">
         <v>0</v>
       </c>
-    </row>
-    <row r="849" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P848" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="849" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A849" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B849" t="s">
         <v>841</v>
@@ -45305,10 +46184,13 @@
       <c r="O849">
         <v>0</v>
       </c>
-    </row>
-    <row r="850" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P849" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="850" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A850" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B850" t="s">
         <v>841</v>
@@ -45352,10 +46234,13 @@
       <c r="O850">
         <v>0</v>
       </c>
-    </row>
-    <row r="851" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P850" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="851" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A851" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B851" t="s">
         <v>841</v>
@@ -45399,10 +46284,13 @@
       <c r="O851">
         <v>0</v>
       </c>
-    </row>
-    <row r="852" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P851" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="852" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A852" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B852" t="s">
         <v>841</v>
@@ -45446,10 +46334,13 @@
       <c r="O852">
         <v>0</v>
       </c>
-    </row>
-    <row r="853" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P852" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="853" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A853" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B853" t="s">
         <v>841</v>
@@ -45493,10 +46384,13 @@
       <c r="O853">
         <v>0</v>
       </c>
-    </row>
-    <row r="854" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P853" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="854" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A854" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B854" t="s">
         <v>841</v>
@@ -45540,10 +46434,13 @@
       <c r="O854">
         <v>0</v>
       </c>
-    </row>
-    <row r="855" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P854" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="855" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A855" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B855" t="s">
         <v>841</v>
@@ -45587,10 +46484,13 @@
       <c r="O855">
         <v>0</v>
       </c>
-    </row>
-    <row r="856" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P855" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="856" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A856" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B856" t="s">
         <v>841</v>
@@ -45634,10 +46534,13 @@
       <c r="O856">
         <v>0</v>
       </c>
-    </row>
-    <row r="857" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P856" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="857" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A857" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B857" t="s">
         <v>841</v>
@@ -45681,10 +46584,13 @@
       <c r="O857">
         <v>0</v>
       </c>
-    </row>
-    <row r="858" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P857" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="858" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A858" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B858" t="s">
         <v>841</v>
@@ -45728,10 +46634,13 @@
       <c r="O858">
         <v>0</v>
       </c>
-    </row>
-    <row r="859" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P858" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="859" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A859" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B859" t="s">
         <v>841</v>
@@ -45775,10 +46684,13 @@
       <c r="O859">
         <v>0</v>
       </c>
-    </row>
-    <row r="860" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P859" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="860" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A860" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B860" t="s">
         <v>841</v>
@@ -45822,10 +46734,13 @@
       <c r="O860">
         <v>0</v>
       </c>
-    </row>
-    <row r="861" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P860" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="861" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A861" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B861" t="s">
         <v>841</v>
@@ -45869,10 +46784,13 @@
       <c r="O861">
         <v>0</v>
       </c>
-    </row>
-    <row r="862" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P861" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="862" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A862" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B862" t="s">
         <v>841</v>
@@ -45916,10 +46834,13 @@
       <c r="O862">
         <v>0</v>
       </c>
-    </row>
-    <row r="863" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P862" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="863" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A863" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B863" t="s">
         <v>841</v>
@@ -45963,10 +46884,13 @@
       <c r="O863">
         <v>0</v>
       </c>
-    </row>
-    <row r="864" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P863" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="864" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A864" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B864" t="s">
         <v>841</v>
@@ -46010,10 +46934,13 @@
       <c r="O864">
         <v>0</v>
       </c>
+      <c r="P864" t="s">
+        <v>1045</v>
+      </c>
     </row>
     <row r="865" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A865" s="1" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B865" t="s">
         <v>841</v>
@@ -46058,12 +46985,12 @@
         <v>0</v>
       </c>
       <c r="P865" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="866" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A866" s="1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B866" t="s">
         <v>841</v>
@@ -46108,12 +47035,12 @@
         <v>0</v>
       </c>
       <c r="P866" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="867" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A867" s="1" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B867" t="s">
         <v>841</v>
@@ -46158,7 +47085,7 @@
         <v>0</v>
       </c>
       <c r="P867" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
   </sheetData>

--- a/file/players_updated.xlsx
+++ b/file/players_updated.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.abraga\Downloads\personal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.abraga\Downloads\ck-tools-main\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D925DF6E-2F43-49CD-856E-CC63959C5A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810B1009-2415-4C80-8A3F-0E06B8BAEEB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3480" uniqueCount="1103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3481" uniqueCount="1104">
   <si>
     <t>PlayerName</t>
   </si>
@@ -3329,6 +3329,9 @@
   </si>
   <si>
     <t>POland</t>
+  </si>
+  <si>
+    <t>Major Winner</t>
   </si>
 </sst>
 </file>
@@ -3723,22 +3726,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P867"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:Q867"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="4.75" customWidth="1"/>
     <col min="8" max="8" width="3.75" customWidth="1"/>
     <col min="9" max="9" width="3.25" customWidth="1"/>
-    <col min="10" max="10" width="4.83203125" customWidth="1"/>
-    <col min="11" max="11" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.9140625" customWidth="1"/>
+    <col min="10" max="10" width="4.875" customWidth="1"/>
+    <col min="11" max="11" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.875" customWidth="1"/>
     <col min="15" max="15" width="11.5" customWidth="1"/>
     <col min="16" max="16" width="20.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3787,8 +3790,11 @@
       <c r="P1" t="s">
         <v>1039</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q1" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>79</v>
       </c>
@@ -3838,7 +3844,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>80</v>
       </c>
@@ -3888,7 +3894,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>81</v>
       </c>
@@ -3938,7 +3944,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>82</v>
       </c>
@@ -3988,7 +3994,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>83</v>
       </c>
@@ -4038,7 +4044,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>84</v>
       </c>
@@ -4088,7 +4094,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>85</v>
       </c>
@@ -4138,7 +4144,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>72</v>
       </c>
@@ -4188,7 +4194,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>73</v>
       </c>
@@ -4238,7 +4244,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>74</v>
       </c>
@@ -4288,7 +4294,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>59</v>
       </c>
@@ -4338,7 +4344,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>61</v>
       </c>
@@ -4388,7 +4394,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>62</v>
       </c>
@@ -4438,7 +4444,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>63</v>
       </c>
@@ -4488,7 +4494,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>64</v>
       </c>
@@ -4538,7 +4544,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>86</v>
       </c>
@@ -4588,7 +4594,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>87</v>
       </c>
@@ -4638,7 +4644,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>88</v>
       </c>
@@ -4688,7 +4694,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>89</v>
       </c>
@@ -4738,7 +4744,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>90</v>
       </c>
@@ -4788,7 +4794,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>91</v>
       </c>
@@ -4838,7 +4844,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>92</v>
       </c>
@@ -4888,7 +4894,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>93</v>
       </c>
@@ -4938,7 +4944,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>94</v>
       </c>
@@ -4988,7 +4994,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>95</v>
       </c>
@@ -5038,7 +5044,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>21</v>
       </c>
@@ -5088,7 +5094,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>23</v>
       </c>
@@ -5138,7 +5144,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>24</v>
       </c>
@@ -5188,7 +5194,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>25</v>
       </c>
@@ -5238,7 +5244,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>26</v>
       </c>
@@ -5288,7 +5294,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>33</v>
       </c>
@@ -5338,7 +5344,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>35</v>
       </c>
@@ -5388,7 +5394,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>36</v>
       </c>
@@ -5438,7 +5444,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>37</v>
       </c>
@@ -5488,7 +5494,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>38</v>
       </c>
@@ -5538,7 +5544,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>96</v>
       </c>
@@ -5588,7 +5594,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>97</v>
       </c>
@@ -5638,7 +5644,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>98</v>
       </c>
@@ -5688,7 +5694,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>99</v>
       </c>
@@ -5738,7 +5744,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>100</v>
       </c>
@@ -5788,7 +5794,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>101</v>
       </c>
@@ -5838,7 +5844,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>102</v>
       </c>
@@ -5888,7 +5894,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>103</v>
       </c>
@@ -5938,7 +5944,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>104</v>
       </c>
@@ -5988,7 +5994,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>105</v>
       </c>
@@ -6038,7 +6044,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>106</v>
       </c>
@@ -6088,7 +6094,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>107</v>
       </c>
@@ -6138,7 +6144,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>108</v>
       </c>
@@ -6188,7 +6194,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>109</v>
       </c>
@@ -6238,7 +6244,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>110</v>
       </c>
@@ -6288,7 +6294,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>111</v>
       </c>
@@ -6338,7 +6344,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>112</v>
       </c>
@@ -6388,7 +6394,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>113</v>
       </c>
@@ -6438,7 +6444,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>114</v>
       </c>
@@ -6488,7 +6494,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>115</v>
       </c>
@@ -6538,7 +6544,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>116</v>
       </c>
@@ -6588,7 +6594,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>117</v>
       </c>
@@ -6638,7 +6644,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>118</v>
       </c>
@@ -6688,7 +6694,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>119</v>
       </c>
@@ -6738,7 +6744,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>120</v>
       </c>
@@ -6788,7 +6794,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>53</v>
       </c>
@@ -6838,7 +6844,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6888,7 +6894,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>56</v>
       </c>
@@ -6938,7 +6944,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6988,7 +6994,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>58</v>
       </c>
@@ -7038,7 +7044,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>121</v>
       </c>
@@ -7088,7 +7094,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>122</v>
       </c>
@@ -7138,7 +7144,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>123</v>
       </c>
@@ -7188,7 +7194,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>124</v>
       </c>
@@ -7238,7 +7244,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>125</v>
       </c>
@@ -7288,7 +7294,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>126</v>
       </c>
@@ -7338,7 +7344,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>127</v>
       </c>
@@ -7388,7 +7394,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>128</v>
       </c>
@@ -7438,7 +7444,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>129</v>
       </c>
@@ -7488,7 +7494,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>130</v>
       </c>
@@ -7538,7 +7544,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>131</v>
       </c>
@@ -7588,7 +7594,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>132</v>
       </c>
@@ -7638,7 +7644,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>133</v>
       </c>
@@ -7688,7 +7694,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>134</v>
       </c>
@@ -7738,7 +7744,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>135</v>
       </c>
@@ -7788,7 +7794,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>136</v>
       </c>
@@ -7838,7 +7844,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>137</v>
       </c>
@@ -7888,7 +7894,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>138</v>
       </c>
@@ -7938,7 +7944,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>139</v>
       </c>
@@ -7988,7 +7994,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>140</v>
       </c>
@@ -8038,7 +8044,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>141</v>
       </c>
@@ -8088,7 +8094,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>142</v>
       </c>
@@ -8138,7 +8144,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>143</v>
       </c>
@@ -8188,7 +8194,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>144</v>
       </c>
@@ -8238,7 +8244,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>145</v>
       </c>
@@ -8288,7 +8294,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>146</v>
       </c>
@@ -8338,7 +8344,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>147</v>
       </c>
@@ -8388,7 +8394,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>148</v>
       </c>
@@ -8438,7 +8444,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>149</v>
       </c>
@@ -8488,7 +8494,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>150</v>
       </c>
@@ -8538,7 +8544,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>151</v>
       </c>
@@ -8588,7 +8594,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>152</v>
       </c>
@@ -8638,7 +8644,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>153</v>
       </c>
@@ -8688,7 +8694,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>154</v>
       </c>
@@ -8738,7 +8744,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>155</v>
       </c>
@@ -8788,7 +8794,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>156</v>
       </c>
@@ -8838,7 +8844,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>157</v>
       </c>
@@ -8888,7 +8894,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>158</v>
       </c>
@@ -8938,7 +8944,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>159</v>
       </c>
@@ -8988,7 +8994,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>160</v>
       </c>
@@ -9038,7 +9044,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>161</v>
       </c>
@@ -9088,7 +9094,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>162</v>
       </c>
@@ -9138,7 +9144,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>163</v>
       </c>
@@ -9188,7 +9194,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>164</v>
       </c>
@@ -9238,7 +9244,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>165</v>
       </c>
@@ -9288,7 +9294,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>166</v>
       </c>
@@ -9338,7 +9344,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>167</v>
       </c>
@@ -9388,7 +9394,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>168</v>
       </c>
@@ -9438,7 +9444,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>169</v>
       </c>
@@ -9488,7 +9494,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>170</v>
       </c>
@@ -9538,7 +9544,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>4</v>
       </c>
@@ -9588,7 +9594,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>6</v>
       </c>
@@ -9638,7 +9644,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>7</v>
       </c>
@@ -9688,7 +9694,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>8</v>
       </c>
@@ -9738,7 +9744,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>9</v>
       </c>
@@ -9788,7 +9794,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>171</v>
       </c>
@@ -9838,7 +9844,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>172</v>
       </c>
@@ -9888,7 +9894,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>173</v>
       </c>
@@ -9938,7 +9944,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>174</v>
       </c>
@@ -9988,7 +9994,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>175</v>
       </c>
@@ -10038,7 +10044,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>176</v>
       </c>
@@ -10088,7 +10094,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>177</v>
       </c>
@@ -10138,7 +10144,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>178</v>
       </c>
@@ -10188,7 +10194,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>179</v>
       </c>
@@ -10238,7 +10244,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>180</v>
       </c>
@@ -10288,7 +10294,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>181</v>
       </c>
@@ -10338,7 +10344,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>182</v>
       </c>
@@ -10388,7 +10394,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>183</v>
       </c>
@@ -10438,7 +10444,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>184</v>
       </c>
@@ -10488,7 +10494,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>185</v>
       </c>
@@ -10538,7 +10544,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>186</v>
       </c>
@@ -10588,7 +10594,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>187</v>
       </c>
@@ -10638,7 +10644,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>188</v>
       </c>
@@ -10688,7 +10694,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>189</v>
       </c>
@@ -10738,7 +10744,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>190</v>
       </c>
@@ -10788,7 +10794,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>191</v>
       </c>
@@ -10838,7 +10844,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>192</v>
       </c>
@@ -10888,7 +10894,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>193</v>
       </c>
@@ -10938,7 +10944,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>194</v>
       </c>
@@ -10988,7 +10994,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>195</v>
       </c>
@@ -11038,7 +11044,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>196</v>
       </c>
@@ -11088,7 +11094,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>197</v>
       </c>
@@ -11138,7 +11144,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>198</v>
       </c>
@@ -11188,7 +11194,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>199</v>
       </c>
@@ -11238,7 +11244,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>200</v>
       </c>
@@ -11288,7 +11294,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>201</v>
       </c>
@@ -11338,7 +11344,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>202</v>
       </c>
@@ -11388,7 +11394,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>203</v>
       </c>
@@ -11438,7 +11444,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>204</v>
       </c>
@@ -11488,7 +11494,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>205</v>
       </c>
@@ -11538,7 +11544,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>206</v>
       </c>
@@ -11588,7 +11594,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>207</v>
       </c>
@@ -11638,7 +11644,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>208</v>
       </c>
@@ -11688,7 +11694,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>209</v>
       </c>
@@ -11738,7 +11744,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>210</v>
       </c>
@@ -11788,7 +11794,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>211</v>
       </c>
@@ -11838,7 +11844,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>212</v>
       </c>
@@ -11888,7 +11894,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>213</v>
       </c>
@@ -11938,7 +11944,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>214</v>
       </c>
@@ -11988,7 +11994,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>215</v>
       </c>
@@ -12038,7 +12044,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>216</v>
       </c>
@@ -12088,7 +12094,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>217</v>
       </c>
@@ -12138,7 +12144,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>218</v>
       </c>
@@ -12188,7 +12194,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>219</v>
       </c>
@@ -12238,7 +12244,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>220</v>
       </c>
@@ -12288,7 +12294,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>221</v>
       </c>
@@ -12338,7 +12344,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>222</v>
       </c>
@@ -12388,7 +12394,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>223</v>
       </c>
@@ -12438,7 +12444,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>224</v>
       </c>
@@ -12488,7 +12494,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>225</v>
       </c>
@@ -12538,7 +12544,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>47</v>
       </c>
@@ -12588,7 +12594,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>49</v>
       </c>
@@ -12638,7 +12644,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>50</v>
       </c>
@@ -12688,7 +12694,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>51</v>
       </c>
@@ -12738,7 +12744,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>52</v>
       </c>
@@ -12788,7 +12794,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>226</v>
       </c>
@@ -12838,7 +12844,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>227</v>
       </c>
@@ -12888,7 +12894,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>228</v>
       </c>
@@ -12938,7 +12944,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>229</v>
       </c>
@@ -12988,7 +12994,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>230</v>
       </c>
@@ -13038,7 +13044,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>231</v>
       </c>
@@ -13088,7 +13094,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>232</v>
       </c>
@@ -13138,7 +13144,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>233</v>
       </c>
@@ -13188,7 +13194,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>234</v>
       </c>
@@ -13238,7 +13244,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>235</v>
       </c>
@@ -13288,7 +13294,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>236</v>
       </c>
@@ -13338,7 +13344,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>237</v>
       </c>
@@ -13388,7 +13394,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>238</v>
       </c>
@@ -13438,7 +13444,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>239</v>
       </c>
@@ -13488,7 +13494,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>240</v>
       </c>
@@ -13538,7 +13544,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>241</v>
       </c>
@@ -13588,7 +13594,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>242</v>
       </c>
@@ -13638,7 +13644,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>243</v>
       </c>
@@ -13688,7 +13694,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>244</v>
       </c>
@@ -13738,7 +13744,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>245</v>
       </c>
@@ -13788,7 +13794,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>246</v>
       </c>
@@ -13838,7 +13844,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>247</v>
       </c>
@@ -13888,7 +13894,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>248</v>
       </c>
@@ -13938,7 +13944,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>249</v>
       </c>
@@ -13988,7 +13994,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>250</v>
       </c>
@@ -14038,7 +14044,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>251</v>
       </c>
@@ -14088,7 +14094,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>252</v>
       </c>
@@ -14138,7 +14144,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>253</v>
       </c>
@@ -14188,7 +14194,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>254</v>
       </c>
@@ -14238,7 +14244,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>255</v>
       </c>
@@ -14288,7 +14294,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>256</v>
       </c>
@@ -14338,7 +14344,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>257</v>
       </c>
@@ -14388,7 +14394,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>258</v>
       </c>
@@ -14438,7 +14444,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>259</v>
       </c>
@@ -14488,7 +14494,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>260</v>
       </c>
@@ -14538,7 +14544,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>261</v>
       </c>
@@ -14588,7 +14594,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>262</v>
       </c>
@@ -14638,7 +14644,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>263</v>
       </c>
@@ -14688,7 +14694,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>264</v>
       </c>
@@ -14738,7 +14744,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>265</v>
       </c>
@@ -14788,7 +14794,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>266</v>
       </c>
@@ -14838,7 +14844,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>267</v>
       </c>
@@ -14888,7 +14894,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>268</v>
       </c>
@@ -14938,7 +14944,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>269</v>
       </c>
@@ -14988,7 +14994,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>270</v>
       </c>
@@ -15038,7 +15044,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>271</v>
       </c>
@@ -15088,7 +15094,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>272</v>
       </c>
@@ -15138,7 +15144,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>273</v>
       </c>
@@ -15188,7 +15194,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>274</v>
       </c>
@@ -15238,7 +15244,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>275</v>
       </c>
@@ -15288,7 +15294,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>276</v>
       </c>
@@ -15338,7 +15344,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>277</v>
       </c>
@@ -15388,7 +15394,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>278</v>
       </c>
@@ -15438,7 +15444,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>279</v>
       </c>
@@ -15488,7 +15494,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>280</v>
       </c>
@@ -15538,7 +15544,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>281</v>
       </c>
@@ -15588,7 +15594,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>282</v>
       </c>
@@ -15638,7 +15644,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>283</v>
       </c>
@@ -15688,7 +15694,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>284</v>
       </c>
@@ -15738,7 +15744,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>285</v>
       </c>
@@ -15788,7 +15794,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>286</v>
       </c>
@@ -15838,7 +15844,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>287</v>
       </c>
@@ -15888,7 +15894,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>288</v>
       </c>
@@ -15938,7 +15944,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>289</v>
       </c>
@@ -15988,7 +15994,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>290</v>
       </c>
@@ -16038,7 +16044,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>291</v>
       </c>
@@ -16088,7 +16094,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>292</v>
       </c>
@@ -16138,7 +16144,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>293</v>
       </c>
@@ -16188,7 +16194,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>294</v>
       </c>
@@ -16238,7 +16244,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>295</v>
       </c>
@@ -16288,7 +16294,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>296</v>
       </c>
@@ -16338,7 +16344,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>297</v>
       </c>
@@ -16388,7 +16394,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>298</v>
       </c>
@@ -16438,7 +16444,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>299</v>
       </c>
@@ -16488,7 +16494,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>300</v>
       </c>
@@ -16538,7 +16544,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="257" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>301</v>
       </c>
@@ -16588,7 +16594,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>302</v>
       </c>
@@ -16638,7 +16644,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>303</v>
       </c>
@@ -16688,7 +16694,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="260" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>304</v>
       </c>
@@ -16738,7 +16744,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>305</v>
       </c>
@@ -16788,7 +16794,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>306</v>
       </c>
@@ -16838,7 +16844,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>307</v>
       </c>
@@ -16888,7 +16894,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>308</v>
       </c>
@@ -16938,7 +16944,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>309</v>
       </c>
@@ -16988,7 +16994,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>310</v>
       </c>
@@ -17038,7 +17044,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>311</v>
       </c>
@@ -17088,7 +17094,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>312</v>
       </c>
@@ -17138,7 +17144,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>313</v>
       </c>
@@ -17188,7 +17194,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>314</v>
       </c>
@@ -17238,7 +17244,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>315</v>
       </c>
@@ -17288,7 +17294,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>316</v>
       </c>
@@ -17338,7 +17344,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>317</v>
       </c>
@@ -17388,7 +17394,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>318</v>
       </c>
@@ -17438,7 +17444,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>319</v>
       </c>
@@ -17488,7 +17494,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>320</v>
       </c>
@@ -17538,7 +17544,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>321</v>
       </c>
@@ -17588,7 +17594,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>322</v>
       </c>
@@ -17638,7 +17644,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>323</v>
       </c>
@@ -17688,7 +17694,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>324</v>
       </c>
@@ -17738,7 +17744,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>325</v>
       </c>
@@ -17788,7 +17794,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>326</v>
       </c>
@@ -17838,7 +17844,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>327</v>
       </c>
@@ -17888,7 +17894,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>328</v>
       </c>
@@ -17938,7 +17944,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>329</v>
       </c>
@@ -17988,7 +17994,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="286" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>330</v>
       </c>
@@ -18038,7 +18044,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>331</v>
       </c>
@@ -18088,7 +18094,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>332</v>
       </c>
@@ -18138,7 +18144,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>333</v>
       </c>
@@ -18188,7 +18194,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>334</v>
       </c>
@@ -18238,7 +18244,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>335</v>
       </c>
@@ -18288,7 +18294,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>336</v>
       </c>
@@ -18338,7 +18344,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="293" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>337</v>
       </c>
@@ -18388,7 +18394,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="294" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>338</v>
       </c>
@@ -18438,7 +18444,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="295" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>339</v>
       </c>
@@ -18488,7 +18494,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="296" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>340</v>
       </c>
@@ -18538,7 +18544,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>341</v>
       </c>
@@ -18588,7 +18594,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>342</v>
       </c>
@@ -18638,7 +18644,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="299" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>343</v>
       </c>
@@ -18688,7 +18694,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="300" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>344</v>
       </c>
@@ -18738,7 +18744,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>345</v>
       </c>
@@ -18788,7 +18794,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="302" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>346</v>
       </c>
@@ -18838,7 +18844,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="303" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>347</v>
       </c>
@@ -18888,7 +18894,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="304" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>348</v>
       </c>
@@ -18938,7 +18944,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="305" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>349</v>
       </c>
@@ -18988,7 +18994,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="306" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>350</v>
       </c>
@@ -19038,7 +19044,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>351</v>
       </c>
@@ -19088,7 +19094,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="308" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>352</v>
       </c>
@@ -19138,7 +19144,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="309" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>353</v>
       </c>
@@ -19188,7 +19194,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="310" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>354</v>
       </c>
@@ -19238,7 +19244,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="311" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>355</v>
       </c>
@@ -19288,7 +19294,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="312" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>356</v>
       </c>
@@ -19338,7 +19344,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="313" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>357</v>
       </c>
@@ -19388,7 +19394,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>222</v>
       </c>
@@ -19438,7 +19444,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="315" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>358</v>
       </c>
@@ -19488,7 +19494,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="316" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>359</v>
       </c>
@@ -19538,7 +19544,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="317" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>360</v>
       </c>
@@ -19588,7 +19594,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="318" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>361</v>
       </c>
@@ -19638,7 +19644,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="319" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>362</v>
       </c>
@@ -19688,7 +19694,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="320" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>363</v>
       </c>
@@ -19738,7 +19744,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="321" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>364</v>
       </c>
@@ -19788,7 +19794,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="322" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>15</v>
       </c>
@@ -19838,7 +19844,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="323" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>17</v>
       </c>
@@ -19888,7 +19894,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="324" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>18</v>
       </c>
@@ -19938,7 +19944,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="325" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>19</v>
       </c>
@@ -19988,7 +19994,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="326" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>20</v>
       </c>
@@ -20038,7 +20044,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="327" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>365</v>
       </c>
@@ -20088,7 +20094,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="328" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>366</v>
       </c>
@@ -20138,7 +20144,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="329" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>367</v>
       </c>
@@ -20188,7 +20194,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="330" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>368</v>
       </c>
@@ -20238,7 +20244,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="331" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>369</v>
       </c>
@@ -20288,7 +20294,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="332" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>370</v>
       </c>
@@ -20338,7 +20344,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="333" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>371</v>
       </c>
@@ -20388,7 +20394,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="334" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>372</v>
       </c>
@@ -20438,7 +20444,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="335" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>373</v>
       </c>
@@ -20488,7 +20494,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="336" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>374</v>
       </c>
@@ -20538,7 +20544,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="337" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>375</v>
       </c>
@@ -20588,7 +20594,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="338" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>376</v>
       </c>
@@ -20638,7 +20644,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="339" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>377</v>
       </c>
@@ -20688,7 +20694,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="340" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>378</v>
       </c>
@@ -20738,7 +20744,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="341" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>379</v>
       </c>
@@ -20788,7 +20794,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="342" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>380</v>
       </c>
@@ -20838,7 +20844,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="343" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>381</v>
       </c>
@@ -20888,7 +20894,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="344" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>382</v>
       </c>
@@ -20938,7 +20944,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="345" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>383</v>
       </c>
@@ -20988,7 +20994,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="346" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>384</v>
       </c>
@@ -21038,7 +21044,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="347" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>385</v>
       </c>
@@ -21088,7 +21094,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="348" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>386</v>
       </c>
@@ -21138,7 +21144,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="349" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>387</v>
       </c>
@@ -21188,7 +21194,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="350" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>388</v>
       </c>
@@ -21238,7 +21244,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="351" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>389</v>
       </c>
@@ -21288,7 +21294,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="352" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>390</v>
       </c>
@@ -21338,7 +21344,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="353" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>391</v>
       </c>
@@ -21388,7 +21394,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="354" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>392</v>
       </c>
@@ -21438,7 +21444,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="355" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>393</v>
       </c>
@@ -21488,7 +21494,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="356" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>394</v>
       </c>
@@ -21538,7 +21544,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="357" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>395</v>
       </c>
@@ -21588,7 +21594,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="358" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>396</v>
       </c>
@@ -21638,7 +21644,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="359" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>397</v>
       </c>
@@ -21688,7 +21694,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="360" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>398</v>
       </c>
@@ -21738,7 +21744,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="361" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>399</v>
       </c>
@@ -21788,7 +21794,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="362" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>40</v>
       </c>
@@ -21838,7 +21844,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="363" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>42</v>
       </c>
@@ -21888,7 +21894,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="364" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>43</v>
       </c>
@@ -21938,7 +21944,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="365" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>44</v>
       </c>
@@ -21988,7 +21994,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="366" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>45</v>
       </c>
@@ -22038,7 +22044,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="367" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>400</v>
       </c>
@@ -22088,7 +22094,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="368" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>401</v>
       </c>
@@ -22138,7 +22144,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="369" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>402</v>
       </c>
@@ -22188,7 +22194,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="370" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>403</v>
       </c>
@@ -22238,7 +22244,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="371" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>404</v>
       </c>
@@ -22288,7 +22294,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="372" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>405</v>
       </c>
@@ -22338,7 +22344,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="373" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>406</v>
       </c>
@@ -22388,7 +22394,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="374" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>407</v>
       </c>
@@ -22438,7 +22444,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="375" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>408</v>
       </c>
@@ -22488,7 +22494,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="376" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>409</v>
       </c>
@@ -22538,7 +22544,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="377" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>410</v>
       </c>
@@ -22588,7 +22594,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="378" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>411</v>
       </c>
@@ -22638,7 +22644,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="379" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>412</v>
       </c>
@@ -22688,7 +22694,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="380" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>413</v>
       </c>
@@ -22738,7 +22744,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="381" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>414</v>
       </c>
@@ -22788,7 +22794,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="382" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>415</v>
       </c>
@@ -22838,7 +22844,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="383" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>416</v>
       </c>
@@ -22888,7 +22894,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="384" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>417</v>
       </c>
@@ -22938,7 +22944,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="385" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>418</v>
       </c>
@@ -22988,7 +22994,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="386" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>419</v>
       </c>
@@ -23038,7 +23044,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="387" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>420</v>
       </c>
@@ -23088,7 +23094,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="388" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>421</v>
       </c>
@@ -23138,7 +23144,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="389" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>422</v>
       </c>
@@ -23188,7 +23194,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="390" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>423</v>
       </c>
@@ -23238,7 +23244,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="391" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>424</v>
       </c>
@@ -23288,7 +23294,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="392" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>425</v>
       </c>
@@ -23338,7 +23344,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="393" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>426</v>
       </c>
@@ -23388,7 +23394,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="394" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>427</v>
       </c>
@@ -23438,7 +23444,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="395" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>428</v>
       </c>
@@ -23488,7 +23494,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="396" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>429</v>
       </c>
@@ -23538,7 +23544,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="397" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>430</v>
       </c>
@@ -23588,7 +23594,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="398" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>431</v>
       </c>
@@ -23638,7 +23644,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="399" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>432</v>
       </c>
@@ -23688,7 +23694,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="400" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>433</v>
       </c>
@@ -23738,7 +23744,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="401" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>434</v>
       </c>
@@ -23788,7 +23794,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="402" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>435</v>
       </c>
@@ -23838,7 +23844,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="403" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>436</v>
       </c>
@@ -23888,7 +23894,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="404" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>437</v>
       </c>
@@ -23938,7 +23944,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="405" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>438</v>
       </c>
@@ -23988,7 +23994,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="406" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>439</v>
       </c>
@@ -24038,7 +24044,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="407" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>440</v>
       </c>
@@ -24088,7 +24094,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="408" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>441</v>
       </c>
@@ -24138,7 +24144,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="409" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>442</v>
       </c>
@@ -24188,7 +24194,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="410" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>443</v>
       </c>
@@ -24238,7 +24244,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="411" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>444</v>
       </c>
@@ -24288,7 +24294,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="412" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>445</v>
       </c>
@@ -24338,7 +24344,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="413" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>446</v>
       </c>
@@ -24388,7 +24394,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="414" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>447</v>
       </c>
@@ -24438,7 +24444,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="415" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>448</v>
       </c>
@@ -24488,7 +24494,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="416" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>449</v>
       </c>
@@ -24538,7 +24544,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="417" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>450</v>
       </c>
@@ -24588,7 +24594,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="418" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>451</v>
       </c>
@@ -24638,7 +24644,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="419" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>452</v>
       </c>
@@ -24688,7 +24694,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="420" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>453</v>
       </c>
@@ -24738,7 +24744,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="421" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>454</v>
       </c>
@@ -24788,7 +24794,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="422" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>455</v>
       </c>
@@ -24838,7 +24844,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="423" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>456</v>
       </c>
@@ -24888,7 +24894,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="424" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>457</v>
       </c>
@@ -24938,7 +24944,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="425" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>458</v>
       </c>
@@ -24988,7 +24994,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="426" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>459</v>
       </c>
@@ -25038,7 +25044,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="427" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>460</v>
       </c>
@@ -25088,7 +25094,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="428" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>461</v>
       </c>
@@ -25138,7 +25144,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="429" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>462</v>
       </c>
@@ -25188,7 +25194,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="430" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>463</v>
       </c>
@@ -25238,7 +25244,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="431" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>464</v>
       </c>
@@ -25288,7 +25294,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="432" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>465</v>
       </c>
@@ -25338,7 +25344,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="433" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>466</v>
       </c>
@@ -25388,7 +25394,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="434" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>467</v>
       </c>
@@ -25438,7 +25444,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="435" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>468</v>
       </c>
@@ -25488,7 +25494,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="436" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>469</v>
       </c>
@@ -25538,7 +25544,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="437" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
         <v>470</v>
       </c>
@@ -25588,7 +25594,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="438" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>471</v>
       </c>
@@ -25638,7 +25644,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="439" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>472</v>
       </c>
@@ -25688,7 +25694,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="440" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>473</v>
       </c>
@@ -25738,7 +25744,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="441" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>474</v>
       </c>
@@ -25788,7 +25794,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="442" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>475</v>
       </c>
@@ -25838,7 +25844,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="443" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>476</v>
       </c>
@@ -25888,7 +25894,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="444" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>477</v>
       </c>
@@ -25938,7 +25944,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="445" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>478</v>
       </c>
@@ -25988,7 +25994,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="446" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
         <v>479</v>
       </c>
@@ -26038,7 +26044,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="447" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
         <v>480</v>
       </c>
@@ -26088,7 +26094,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="448" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
         <v>481</v>
       </c>
@@ -26138,7 +26144,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="449" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
         <v>482</v>
       </c>
@@ -26188,7 +26194,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="450" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
         <v>483</v>
       </c>
@@ -26238,7 +26244,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="451" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
         <v>484</v>
       </c>
@@ -26288,7 +26294,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="452" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
         <v>485</v>
       </c>
@@ -26338,7 +26344,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="453" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
         <v>486</v>
       </c>
@@ -26388,7 +26394,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="454" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
         <v>487</v>
       </c>
@@ -26438,7 +26444,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="455" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
         <v>488</v>
       </c>
@@ -26488,7 +26494,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="456" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
         <v>489</v>
       </c>
@@ -26538,7 +26544,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="457" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>490</v>
       </c>
@@ -26588,7 +26594,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="458" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
         <v>491</v>
       </c>
@@ -26638,7 +26644,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="459" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>492</v>
       </c>
@@ -26688,7 +26694,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="460" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>493</v>
       </c>
@@ -26738,7 +26744,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="461" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>494</v>
       </c>
@@ -26788,7 +26794,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="462" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>495</v>
       </c>
@@ -26838,7 +26844,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="463" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
         <v>496</v>
       </c>
@@ -26888,7 +26894,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="464" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>497</v>
       </c>
@@ -26938,7 +26944,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="465" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
         <v>498</v>
       </c>
@@ -26988,7 +26994,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="466" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
         <v>499</v>
       </c>
@@ -27038,7 +27044,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="467" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
         <v>500</v>
       </c>
@@ -27088,7 +27094,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="468" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
         <v>501</v>
       </c>
@@ -27138,7 +27144,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="469" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
         <v>502</v>
       </c>
@@ -27188,7 +27194,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="470" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
         <v>503</v>
       </c>
@@ -27238,7 +27244,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="471" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
         <v>504</v>
       </c>
@@ -27288,7 +27294,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="472" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>27</v>
       </c>
@@ -27338,7 +27344,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="473" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
         <v>29</v>
       </c>
@@ -27388,7 +27394,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="474" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
         <v>30</v>
       </c>
@@ -27438,7 +27444,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="475" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
         <v>31</v>
       </c>
@@ -27488,7 +27494,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="476" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
         <v>32</v>
       </c>
@@ -27538,7 +27544,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="477" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
         <v>505</v>
       </c>
@@ -27588,7 +27594,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="478" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
         <v>506</v>
       </c>
@@ -27638,7 +27644,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="479" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
         <v>507</v>
       </c>
@@ -27688,7 +27694,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="480" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
         <v>508</v>
       </c>
@@ -27738,7 +27744,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="481" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
         <v>509</v>
       </c>
@@ -27788,7 +27794,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="482" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
         <v>510</v>
       </c>
@@ -27838,7 +27844,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="483" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
         <v>511</v>
       </c>
@@ -27888,7 +27894,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="484" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
         <v>512</v>
       </c>
@@ -27938,7 +27944,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="485" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
         <v>513</v>
       </c>
@@ -27988,7 +27994,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="486" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
         <v>514</v>
       </c>
@@ -28038,7 +28044,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="487" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
         <v>515</v>
       </c>
@@ -28088,7 +28094,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="488" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
         <v>516</v>
       </c>
@@ -28138,7 +28144,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="489" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
         <v>517</v>
       </c>
@@ -28188,7 +28194,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="490" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
         <v>518</v>
       </c>
@@ -28238,7 +28244,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="491" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
         <v>519</v>
       </c>
@@ -28288,7 +28294,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="492" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
         <v>520</v>
       </c>
@@ -28338,7 +28344,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="493" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
         <v>521</v>
       </c>
@@ -28388,7 +28394,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="494" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
         <v>522</v>
       </c>
@@ -28438,7 +28444,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="495" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
         <v>523</v>
       </c>
@@ -28488,7 +28494,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="496" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
         <v>524</v>
       </c>
@@ -28538,7 +28544,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="497" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
         <v>525</v>
       </c>
@@ -28588,7 +28594,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="498" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
         <v>526</v>
       </c>
@@ -28638,7 +28644,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="499" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
         <v>527</v>
       </c>
@@ -28688,7 +28694,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="500" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
         <v>528</v>
       </c>
@@ -28738,7 +28744,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="501" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
         <v>529</v>
       </c>
@@ -28788,7 +28794,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="502" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
         <v>530</v>
       </c>
@@ -28838,7 +28844,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="503" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
         <v>531</v>
       </c>
@@ -28888,7 +28894,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="504" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
         <v>532</v>
       </c>
@@ -28938,7 +28944,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="505" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
         <v>533</v>
       </c>
@@ -28988,7 +28994,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="506" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
         <v>534</v>
       </c>
@@ -29038,7 +29044,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="507" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
         <v>535</v>
       </c>
@@ -29088,7 +29094,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="508" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
         <v>536</v>
       </c>
@@ -29138,7 +29144,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="509" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
         <v>537</v>
       </c>
@@ -29188,7 +29194,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="510" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
         <v>538</v>
       </c>
@@ -29238,7 +29244,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="511" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
         <v>539</v>
       </c>
@@ -29288,7 +29294,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="512" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
         <v>540</v>
       </c>
@@ -29338,7 +29344,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="513" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
         <v>541</v>
       </c>
@@ -29388,7 +29394,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="514" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
         <v>542</v>
       </c>
@@ -29438,7 +29444,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="515" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
         <v>543</v>
       </c>
@@ -29488,7 +29494,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="516" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
         <v>544</v>
       </c>
@@ -29538,7 +29544,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="517" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
         <v>545</v>
       </c>
@@ -29588,7 +29594,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="518" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>546</v>
       </c>
@@ -29638,7 +29644,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="519" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>547</v>
       </c>
@@ -29688,7 +29694,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="520" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
         <v>548</v>
       </c>
@@ -29738,7 +29744,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="521" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
         <v>549</v>
       </c>
@@ -29788,7 +29794,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="522" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
         <v>65</v>
       </c>
@@ -29838,7 +29844,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="523" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
         <v>67</v>
       </c>
@@ -29888,7 +29894,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="524" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
         <v>68</v>
       </c>
@@ -29938,7 +29944,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="525" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
         <v>69</v>
       </c>
@@ -29988,7 +29994,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="526" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
         <v>70</v>
       </c>
@@ -30038,7 +30044,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="527" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
         <v>550</v>
       </c>
@@ -30088,7 +30094,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="528" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
         <v>551</v>
       </c>
@@ -30138,7 +30144,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="529" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
         <v>552</v>
       </c>
@@ -30188,7 +30194,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="530" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
         <v>553</v>
       </c>
@@ -30238,7 +30244,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="531" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
         <v>554</v>
       </c>
@@ -30288,7 +30294,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="532" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
         <v>555</v>
       </c>
@@ -30338,7 +30344,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="533" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
         <v>556</v>
       </c>
@@ -30388,7 +30394,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="534" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
         <v>557</v>
       </c>
@@ -30438,7 +30444,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="535" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
         <v>558</v>
       </c>
@@ -30488,7 +30494,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="536" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
         <v>559</v>
       </c>
@@ -30538,7 +30544,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="537" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
         <v>560</v>
       </c>
@@ -30588,7 +30594,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="538" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
         <v>561</v>
       </c>
@@ -30638,7 +30644,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="539" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
         <v>562</v>
       </c>
@@ -30688,7 +30694,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="540" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
         <v>563</v>
       </c>
@@ -30738,7 +30744,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="541" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
         <v>564</v>
       </c>
@@ -30788,7 +30794,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="542" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
         <v>565</v>
       </c>
@@ -30838,7 +30844,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="543" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
         <v>566</v>
       </c>
@@ -30888,7 +30894,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="544" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
         <v>567</v>
       </c>
@@ -30938,7 +30944,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="545" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
         <v>568</v>
       </c>
@@ -30988,7 +30994,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="546" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
         <v>569</v>
       </c>
@@ -31038,7 +31044,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="547" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
         <v>10</v>
       </c>
@@ -31088,7 +31094,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="548" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
         <v>12</v>
       </c>
@@ -31138,7 +31144,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="549" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
         <v>13</v>
       </c>
@@ -31188,7 +31194,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="550" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
         <v>14</v>
       </c>
@@ -31238,7 +31244,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="551" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
         <v>570</v>
       </c>
@@ -31288,7 +31294,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="552" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
         <v>571</v>
       </c>
@@ -31338,7 +31344,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="553" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
         <v>572</v>
       </c>
@@ -31388,7 +31394,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="554" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
         <v>573</v>
       </c>
@@ -31438,7 +31444,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="555" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
         <v>574</v>
       </c>
@@ -31488,7 +31494,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="556" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
         <v>575</v>
       </c>
@@ -31538,7 +31544,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="557" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
         <v>576</v>
       </c>
@@ -31588,7 +31594,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="558" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
         <v>577</v>
       </c>
@@ -31638,7 +31644,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="559" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
         <v>578</v>
       </c>
@@ -31688,7 +31694,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="560" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
         <v>579</v>
       </c>
@@ -31738,7 +31744,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="561" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
         <v>580</v>
       </c>
@@ -31788,7 +31794,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="562" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
         <v>581</v>
       </c>
@@ -31838,7 +31844,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="563" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
         <v>582</v>
       </c>
@@ -31888,7 +31894,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="564" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
         <v>583</v>
       </c>
@@ -31938,7 +31944,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="565" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
         <v>584</v>
       </c>
@@ -31988,7 +31994,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="566" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
         <v>585</v>
       </c>
@@ -32038,7 +32044,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="567" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
         <v>586</v>
       </c>
@@ -32088,7 +32094,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="568" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
         <v>587</v>
       </c>
@@ -32138,7 +32144,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="569" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
         <v>588</v>
       </c>
@@ -32188,7 +32194,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="570" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
         <v>589</v>
       </c>
@@ -32238,7 +32244,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="571" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
         <v>590</v>
       </c>
@@ -32288,7 +32294,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="572" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
         <v>591</v>
       </c>
@@ -32338,7 +32344,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="573" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
         <v>592</v>
       </c>
@@ -32388,7 +32394,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="574" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
         <v>593</v>
       </c>
@@ -32438,7 +32444,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="575" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
         <v>594</v>
       </c>
@@ -32488,7 +32494,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="576" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
         <v>595</v>
       </c>
@@ -32538,7 +32544,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="577" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
         <v>596</v>
       </c>
@@ -32588,7 +32594,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="578" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
         <v>597</v>
       </c>
@@ -32638,7 +32644,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="579" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
         <v>598</v>
       </c>
@@ -32688,7 +32694,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="580" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
         <v>599</v>
       </c>
@@ -32738,7 +32744,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="581" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
         <v>600</v>
       </c>
@@ -32788,7 +32794,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="582" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
         <v>601</v>
       </c>
@@ -32838,7 +32844,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="583" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
         <v>602</v>
       </c>
@@ -32888,7 +32894,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="584" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
         <v>603</v>
       </c>
@@ -32938,7 +32944,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="585" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
         <v>604</v>
       </c>
@@ -32988,7 +32994,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="586" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
         <v>605</v>
       </c>
@@ -33038,7 +33044,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="587" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
         <v>606</v>
       </c>
@@ -33088,7 +33094,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="588" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
         <v>607</v>
       </c>
@@ -33138,7 +33144,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="589" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
         <v>608</v>
       </c>
@@ -33188,7 +33194,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="590" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
         <v>609</v>
       </c>
@@ -33238,7 +33244,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="591" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
         <v>610</v>
       </c>
@@ -33288,7 +33294,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="592" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
         <v>611</v>
       </c>
@@ -33338,7 +33344,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="593" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
         <v>612</v>
       </c>
@@ -33388,7 +33394,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="594" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
         <v>613</v>
       </c>
@@ -33438,7 +33444,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="595" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
         <v>614</v>
       </c>
@@ -33488,7 +33494,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="596" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
         <v>615</v>
       </c>
@@ -33538,7 +33544,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="597" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
         <v>616</v>
       </c>
@@ -33588,7 +33594,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="598" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
         <v>617</v>
       </c>
@@ -33638,7 +33644,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="599" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
         <v>618</v>
       </c>
@@ -33688,7 +33694,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="600" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
         <v>619</v>
       </c>
@@ -33738,7 +33744,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="601" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
         <v>620</v>
       </c>
@@ -33788,7 +33794,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="602" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
         <v>621</v>
       </c>
@@ -33838,7 +33844,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="603" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
         <v>622</v>
       </c>
@@ -33888,7 +33894,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="604" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
         <v>623</v>
       </c>
@@ -33938,7 +33944,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="605" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
         <v>624</v>
       </c>
@@ -33988,7 +33994,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="606" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
         <v>625</v>
       </c>
@@ -34038,7 +34044,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="607" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
         <v>626</v>
       </c>
@@ -34088,7 +34094,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="608" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
         <v>627</v>
       </c>
@@ -34138,7 +34144,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="609" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
         <v>628</v>
       </c>
@@ -34188,7 +34194,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="610" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
         <v>629</v>
       </c>
@@ -34238,7 +34244,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="611" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
         <v>630</v>
       </c>
@@ -34288,7 +34294,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="612" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
         <v>631</v>
       </c>
@@ -34338,7 +34344,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="613" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
         <v>632</v>
       </c>
@@ -34388,7 +34394,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="614" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
         <v>633</v>
       </c>
@@ -34438,7 +34444,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="615" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
         <v>634</v>
       </c>
@@ -34488,7 +34494,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="616" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
         <v>635</v>
       </c>
@@ -34538,7 +34544,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="617" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
         <v>636</v>
       </c>
@@ -34588,7 +34594,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="618" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
         <v>637</v>
       </c>
@@ -34638,7 +34644,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="619" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
         <v>638</v>
       </c>
@@ -34688,7 +34694,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="620" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
         <v>639</v>
       </c>
@@ -34738,7 +34744,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="621" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
         <v>640</v>
       </c>
@@ -34788,7 +34794,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="622" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
         <v>641</v>
       </c>
@@ -34838,7 +34844,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="623" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
         <v>642</v>
       </c>
@@ -34888,7 +34894,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="624" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
         <v>643</v>
       </c>
@@ -34938,7 +34944,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="625" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
         <v>644</v>
       </c>
@@ -34988,7 +34994,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="626" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
         <v>645</v>
       </c>
@@ -35038,7 +35044,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="627" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
         <v>646</v>
       </c>
@@ -35088,7 +35094,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="628" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
         <v>647</v>
       </c>
@@ -35138,7 +35144,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="629" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
         <v>648</v>
       </c>
@@ -35188,7 +35194,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="630" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
         <v>649</v>
       </c>
@@ -35238,7 +35244,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="631" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
         <v>650</v>
       </c>
@@ -35288,7 +35294,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="632" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
         <v>651</v>
       </c>
@@ -35338,7 +35344,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="633" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
         <v>652</v>
       </c>
@@ -35388,7 +35394,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="634" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
         <v>653</v>
       </c>
@@ -35438,7 +35444,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="635" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
         <v>654</v>
       </c>
@@ -35488,7 +35494,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="636" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
         <v>655</v>
       </c>
@@ -35538,7 +35544,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="637" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
         <v>656</v>
       </c>
@@ -35588,7 +35594,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="638" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
         <v>657</v>
       </c>
@@ -35638,7 +35644,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="639" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
         <v>658</v>
       </c>
@@ -35688,7 +35694,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="640" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
         <v>659</v>
       </c>
@@ -35738,7 +35744,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="641" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
         <v>660</v>
       </c>
@@ -35788,7 +35794,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="642" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
         <v>661</v>
       </c>
@@ -35838,7 +35844,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="643" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
         <v>662</v>
       </c>
@@ -35888,7 +35894,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="644" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
         <v>663</v>
       </c>
@@ -35938,7 +35944,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="645" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
         <v>664</v>
       </c>
@@ -35988,7 +35994,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="646" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
         <v>665</v>
       </c>
@@ -36038,7 +36044,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="647" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
         <v>666</v>
       </c>
@@ -36088,7 +36094,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="648" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
         <v>563</v>
       </c>
@@ -36138,7 +36144,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="649" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
         <v>667</v>
       </c>
@@ -36188,7 +36194,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="650" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
         <v>668</v>
       </c>
@@ -36238,7 +36244,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="651" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
         <v>669</v>
       </c>
@@ -36288,7 +36294,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="652" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
         <v>670</v>
       </c>
@@ -36338,7 +36344,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="653" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
         <v>671</v>
       </c>
@@ -36388,7 +36394,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="654" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
         <v>672</v>
       </c>
@@ -36438,7 +36444,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="655" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
         <v>673</v>
       </c>
@@ -36488,7 +36494,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="656" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
         <v>674</v>
       </c>
@@ -36538,7 +36544,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="657" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
         <v>675</v>
       </c>
@@ -36588,7 +36594,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="658" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
         <v>676</v>
       </c>
@@ -36638,7 +36644,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="659" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
         <v>677</v>
       </c>
@@ -36688,7 +36694,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="660" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
         <v>678</v>
       </c>
@@ -36738,7 +36744,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="661" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
         <v>679</v>
       </c>
@@ -36788,7 +36794,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="662" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
         <v>680</v>
       </c>
@@ -36838,7 +36844,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="663" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
         <v>681</v>
       </c>
@@ -36888,7 +36894,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="664" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
         <v>682</v>
       </c>
@@ -36938,7 +36944,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="665" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
         <v>683</v>
       </c>
@@ -36988,7 +36994,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="666" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
         <v>684</v>
       </c>
@@ -37038,7 +37044,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="667" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
         <v>685</v>
       </c>
@@ -37088,7 +37094,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="668" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
         <v>686</v>
       </c>
@@ -37138,7 +37144,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="669" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
         <v>687</v>
       </c>
@@ -37188,7 +37194,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="670" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
         <v>688</v>
       </c>
@@ -37238,7 +37244,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="671" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
         <v>689</v>
       </c>
@@ -37288,7 +37294,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="672" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
         <v>690</v>
       </c>
@@ -37338,7 +37344,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="673" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
         <v>691</v>
       </c>
@@ -37388,7 +37394,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="674" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
         <v>692</v>
       </c>
@@ -37438,7 +37444,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="675" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
         <v>693</v>
       </c>
@@ -37488,7 +37494,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="676" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
         <v>694</v>
       </c>
@@ -37538,7 +37544,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="677" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
         <v>695</v>
       </c>
@@ -37588,7 +37594,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="678" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
         <v>696</v>
       </c>
@@ -37638,7 +37644,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="679" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
         <v>697</v>
       </c>
@@ -37688,7 +37694,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="680" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
         <v>698</v>
       </c>
@@ -37738,7 +37744,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="681" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
         <v>699</v>
       </c>
@@ -37788,7 +37794,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="682" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
         <v>700</v>
       </c>
@@ -37838,7 +37844,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="683" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
         <v>701</v>
       </c>
@@ -37888,7 +37894,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="684" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
         <v>702</v>
       </c>
@@ -37938,7 +37944,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="685" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
         <v>703</v>
       </c>
@@ -37988,7 +37994,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="686" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
         <v>704</v>
       </c>
@@ -38038,7 +38044,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="687" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
         <v>705</v>
       </c>
@@ -38088,7 +38094,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="688" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
         <v>706</v>
       </c>
@@ -38138,7 +38144,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="689" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
         <v>707</v>
       </c>
@@ -38188,7 +38194,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="690" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
         <v>708</v>
       </c>
@@ -38238,7 +38244,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="691" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
         <v>709</v>
       </c>
@@ -38288,7 +38294,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="692" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
         <v>710</v>
       </c>
@@ -38338,7 +38344,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="693" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
         <v>711</v>
       </c>
@@ -38388,7 +38394,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="694" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
         <v>712</v>
       </c>
@@ -38438,7 +38444,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="695" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
         <v>713</v>
       </c>
@@ -38488,7 +38494,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="696" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
         <v>714</v>
       </c>
@@ -38538,7 +38544,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="697" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
         <v>715</v>
       </c>
@@ -38588,7 +38594,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="698" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
         <v>716</v>
       </c>
@@ -38638,7 +38644,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="699" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
         <v>717</v>
       </c>
@@ -38688,7 +38694,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="700" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
         <v>718</v>
       </c>
@@ -38738,7 +38744,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="701" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
         <v>719</v>
       </c>
@@ -38788,7 +38794,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="702" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
         <v>720</v>
       </c>
@@ -38838,7 +38844,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="703" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A703" s="1" t="s">
         <v>721</v>
       </c>
@@ -38888,7 +38894,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="704" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A704" s="1" t="s">
         <v>722</v>
       </c>
@@ -38938,7 +38944,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="705" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A705" s="1" t="s">
         <v>723</v>
       </c>
@@ -38988,7 +38994,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="706" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A706" s="1" t="s">
         <v>724</v>
       </c>
@@ -39038,7 +39044,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="707" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="s">
         <v>725</v>
       </c>
@@ -39088,7 +39094,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="708" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A708" s="1" t="s">
         <v>726</v>
       </c>
@@ -39138,7 +39144,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="709" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A709" s="1" t="s">
         <v>727</v>
       </c>
@@ -39188,7 +39194,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="710" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A710" s="1" t="s">
         <v>728</v>
       </c>
@@ -39238,7 +39244,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="711" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A711" s="1" t="s">
         <v>729</v>
       </c>
@@ -39288,7 +39294,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="712" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A712" s="1" t="s">
         <v>730</v>
       </c>
@@ -39338,7 +39344,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="713" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A713" s="1" t="s">
         <v>731</v>
       </c>
@@ -39388,7 +39394,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="714" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A714" s="1" t="s">
         <v>732</v>
       </c>
@@ -39438,7 +39444,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="715" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A715" s="1" t="s">
         <v>733</v>
       </c>
@@ -39488,7 +39494,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="716" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A716" s="1" t="s">
         <v>734</v>
       </c>
@@ -39538,7 +39544,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="717" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A717" s="1" t="s">
         <v>735</v>
       </c>
@@ -39588,7 +39594,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="718" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A718" s="1" t="s">
         <v>736</v>
       </c>
@@ -39638,7 +39644,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="719" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A719" s="1" t="s">
         <v>737</v>
       </c>
@@ -39688,7 +39694,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="720" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A720" s="1" t="s">
         <v>738</v>
       </c>
@@ -39738,7 +39744,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="721" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A721" s="1" t="s">
         <v>739</v>
       </c>
@@ -39788,7 +39794,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="722" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A722" s="1" t="s">
         <v>740</v>
       </c>
@@ -39838,7 +39844,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="723" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A723" s="1" t="s">
         <v>741</v>
       </c>
@@ -39888,7 +39894,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="724" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A724" s="1" t="s">
         <v>742</v>
       </c>
@@ -39938,7 +39944,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="725" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A725" s="1" t="s">
         <v>743</v>
       </c>
@@ -39988,7 +39994,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="726" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A726" s="1" t="s">
         <v>744</v>
       </c>
@@ -40038,7 +40044,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="727" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A727" s="1" t="s">
         <v>745</v>
       </c>
@@ -40088,7 +40094,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="728" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A728" s="1" t="s">
         <v>746</v>
       </c>
@@ -40138,7 +40144,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="729" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A729" s="1" t="s">
         <v>747</v>
       </c>
@@ -40188,7 +40194,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="730" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A730" s="1" t="s">
         <v>748</v>
       </c>
@@ -40238,7 +40244,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="731" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A731" s="1" t="s">
         <v>749</v>
       </c>
@@ -40288,7 +40294,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="732" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A732" s="1" t="s">
         <v>750</v>
       </c>
@@ -40338,7 +40344,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="733" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A733" s="1" t="s">
         <v>751</v>
       </c>
@@ -40388,7 +40394,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="734" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A734" s="1" t="s">
         <v>752</v>
       </c>
@@ -40438,7 +40444,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="735" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A735" s="1" t="s">
         <v>753</v>
       </c>
@@ -40488,7 +40494,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="736" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A736" s="1" t="s">
         <v>67</v>
       </c>
@@ -40538,7 +40544,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="737" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A737" s="1" t="s">
         <v>754</v>
       </c>
@@ -40588,7 +40594,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="738" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A738" s="1" t="s">
         <v>755</v>
       </c>
@@ -40638,7 +40644,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="739" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A739" s="1" t="s">
         <v>756</v>
       </c>
@@ -40688,7 +40694,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="740" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A740" s="1" t="s">
         <v>757</v>
       </c>
@@ -40738,7 +40744,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="741" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A741" s="1" t="s">
         <v>758</v>
       </c>
@@ -40788,7 +40794,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="742" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A742" s="1" t="s">
         <v>759</v>
       </c>
@@ -40838,7 +40844,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="743" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A743" s="1" t="s">
         <v>760</v>
       </c>
@@ -40888,7 +40894,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="744" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A744" s="1" t="s">
         <v>761</v>
       </c>
@@ -40938,7 +40944,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="745" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A745" s="1" t="s">
         <v>762</v>
       </c>
@@ -40988,7 +40994,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="746" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A746" s="1" t="s">
         <v>763</v>
       </c>
@@ -41038,7 +41044,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="747" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A747" s="1" t="s">
         <v>601</v>
       </c>
@@ -41088,7 +41094,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="748" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A748" s="1" t="s">
         <v>602</v>
       </c>
@@ -41138,7 +41144,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="749" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A749" s="1" t="s">
         <v>764</v>
       </c>
@@ -41188,7 +41194,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="750" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A750" s="1" t="s">
         <v>765</v>
       </c>
@@ -41238,7 +41244,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="751" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A751" s="1" t="s">
         <v>766</v>
       </c>
@@ -41288,7 +41294,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="752" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A752" s="1" t="s">
         <v>767</v>
       </c>
@@ -41338,7 +41344,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="753" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A753" s="1" t="s">
         <v>768</v>
       </c>
@@ -41388,7 +41394,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="754" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A754" s="1" t="s">
         <v>769</v>
       </c>
@@ -41438,7 +41444,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="755" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A755" s="1" t="s">
         <v>770</v>
       </c>
@@ -41488,7 +41494,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="756" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A756" s="1" t="s">
         <v>771</v>
       </c>
@@ -41538,7 +41544,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="757" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A757" s="1" t="s">
         <v>772</v>
       </c>
@@ -41588,7 +41594,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="758" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A758" s="1" t="s">
         <v>773</v>
       </c>
@@ -41638,7 +41644,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="759" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A759" s="1" t="s">
         <v>774</v>
       </c>
@@ -41688,7 +41694,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="760" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A760" s="1" t="s">
         <v>775</v>
       </c>
@@ -41738,7 +41744,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="761" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A761" s="1" t="s">
         <v>776</v>
       </c>
@@ -41788,7 +41794,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="762" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A762" s="1" t="s">
         <v>777</v>
       </c>
@@ -41838,7 +41844,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="763" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A763" s="1" t="s">
         <v>778</v>
       </c>
@@ -41888,7 +41894,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="764" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A764" s="1" t="s">
         <v>779</v>
       </c>
@@ -41938,7 +41944,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="765" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A765" s="1" t="s">
         <v>780</v>
       </c>
@@ -41988,7 +41994,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="766" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A766" s="1" t="s">
         <v>781</v>
       </c>
@@ -42038,7 +42044,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="767" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A767" s="1" t="s">
         <v>782</v>
       </c>
@@ -42088,7 +42094,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="768" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A768" s="1" t="s">
         <v>783</v>
       </c>
@@ -42138,7 +42144,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="769" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A769" s="1" t="s">
         <v>784</v>
       </c>
@@ -42188,7 +42194,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="770" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A770" s="1" t="s">
         <v>785</v>
       </c>
@@ -42238,7 +42244,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="771" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A771" s="1" t="s">
         <v>786</v>
       </c>
@@ -42288,7 +42294,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="772" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A772" s="1" t="s">
         <v>787</v>
       </c>
@@ -42338,7 +42344,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="773" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A773" s="1" t="s">
         <v>788</v>
       </c>
@@ -42388,7 +42394,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="774" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A774" s="1" t="s">
         <v>789</v>
       </c>
@@ -42438,7 +42444,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="775" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A775" s="1" t="s">
         <v>790</v>
       </c>
@@ -42488,7 +42494,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="776" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A776" s="1" t="s">
         <v>791</v>
       </c>
@@ -42538,7 +42544,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="777" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A777" s="1" t="s">
         <v>792</v>
       </c>
@@ -42588,7 +42594,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="778" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A778" s="1" t="s">
         <v>793</v>
       </c>
@@ -42638,7 +42644,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="779" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A779" s="1" t="s">
         <v>794</v>
       </c>
@@ -42688,7 +42694,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="780" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A780" s="1" t="s">
         <v>795</v>
       </c>
@@ -42738,7 +42744,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="781" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A781" s="1" t="s">
         <v>796</v>
       </c>
@@ -42788,7 +42794,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="782" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A782" s="1" t="s">
         <v>797</v>
       </c>
@@ -42838,7 +42844,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="783" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A783" s="1" t="s">
         <v>798</v>
       </c>
@@ -42888,7 +42894,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="784" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A784" s="1" t="s">
         <v>799</v>
       </c>
@@ -42938,7 +42944,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="785" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A785" s="1" t="s">
         <v>800</v>
       </c>
@@ -42988,7 +42994,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="786" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A786" s="1" t="s">
         <v>801</v>
       </c>
@@ -43038,7 +43044,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="787" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A787" s="1" t="s">
         <v>802</v>
       </c>
@@ -43088,7 +43094,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="788" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A788" s="1" t="s">
         <v>803</v>
       </c>
@@ -43138,7 +43144,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="789" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A789" s="1" t="s">
         <v>804</v>
       </c>
@@ -43188,7 +43194,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="790" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A790" s="1" t="s">
         <v>805</v>
       </c>
@@ -43238,7 +43244,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="791" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A791" s="1" t="s">
         <v>806</v>
       </c>
@@ -43288,7 +43294,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="792" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A792" s="1" t="s">
         <v>807</v>
       </c>
@@ -43338,7 +43344,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="793" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A793" s="1" t="s">
         <v>808</v>
       </c>
@@ -43388,7 +43394,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="794" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A794" s="1" t="s">
         <v>809</v>
       </c>
@@ -43438,7 +43444,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="795" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A795" s="1" t="s">
         <v>810</v>
       </c>
@@ -43488,7 +43494,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="796" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A796" s="1" t="s">
         <v>811</v>
       </c>
@@ -43538,7 +43544,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="797" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A797" s="1" t="s">
         <v>812</v>
       </c>
@@ -43588,7 +43594,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="798" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A798" s="1" t="s">
         <v>813</v>
       </c>
@@ -43638,7 +43644,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="799" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A799" s="1" t="s">
         <v>814</v>
       </c>
@@ -43688,7 +43694,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="800" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A800" s="1" t="s">
         <v>815</v>
       </c>
@@ -43738,7 +43744,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="801" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A801" s="1" t="s">
         <v>816</v>
       </c>
@@ -43788,7 +43794,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="802" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A802" s="1" t="s">
         <v>817</v>
       </c>
@@ -43838,7 +43844,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="803" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A803" s="1" t="s">
         <v>818</v>
       </c>
@@ -43888,7 +43894,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="804" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A804" s="1" t="s">
         <v>819</v>
       </c>
@@ -43938,7 +43944,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="805" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A805" s="1" t="s">
         <v>820</v>
       </c>
@@ -43988,7 +43994,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="806" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A806" s="1" t="s">
         <v>821</v>
       </c>
@@ -44038,7 +44044,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="807" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A807" s="1" t="s">
         <v>822</v>
       </c>
@@ -44088,7 +44094,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="808" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A808" s="1" t="s">
         <v>823</v>
       </c>
@@ -44138,7 +44144,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="809" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A809" s="1" t="s">
         <v>824</v>
       </c>
@@ -44188,7 +44194,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="810" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A810" s="1" t="s">
         <v>825</v>
       </c>
@@ -44238,7 +44244,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="811" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A811" s="1" t="s">
         <v>826</v>
       </c>
@@ -44288,7 +44294,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="812" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A812" s="1" t="s">
         <v>827</v>
       </c>
@@ -44338,7 +44344,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="813" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A813" s="1" t="s">
         <v>828</v>
       </c>
@@ -44388,7 +44394,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="814" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A814" s="1" t="s">
         <v>829</v>
       </c>
@@ -44438,7 +44444,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="815" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A815" s="1" t="s">
         <v>393</v>
       </c>
@@ -44488,7 +44494,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="816" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A816" s="1" t="s">
         <v>830</v>
       </c>
@@ -44538,7 +44544,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="817" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A817" s="1" t="s">
         <v>831</v>
       </c>
@@ -44588,7 +44594,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="818" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A818" s="1" t="s">
         <v>832</v>
       </c>
@@ -44638,7 +44644,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="819" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A819" s="1" t="s">
         <v>833</v>
       </c>
@@ -44688,7 +44694,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="820" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A820" s="1" t="s">
         <v>834</v>
       </c>
@@ -44738,7 +44744,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="821" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A821" s="1" t="s">
         <v>835</v>
       </c>
@@ -44788,7 +44794,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="822" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A822" s="1" t="s">
         <v>836</v>
       </c>
@@ -44838,7 +44844,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="823" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A823" s="1" t="s">
         <v>837</v>
       </c>
@@ -44888,7 +44894,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="824" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A824" s="1" t="s">
         <v>838</v>
       </c>
@@ -44938,7 +44944,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="825" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A825" s="1" t="s">
         <v>46</v>
       </c>
@@ -44988,7 +44994,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="826" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A826" s="1" t="s">
         <v>839</v>
       </c>
@@ -45038,7 +45044,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="827" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A827" s="1" t="s">
         <v>39</v>
       </c>
@@ -45088,7 +45094,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="828" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A828" s="1" t="s">
         <v>391</v>
       </c>
@@ -45138,7 +45144,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="829" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A829" s="1" t="s">
         <v>392</v>
       </c>
@@ -45188,7 +45194,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="830" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>1002</v>
       </c>
@@ -45238,7 +45244,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="831" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>115</v>
       </c>
@@ -45288,7 +45294,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="832" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>1003</v>
       </c>
@@ -45338,7 +45344,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="833" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>1004</v>
       </c>
@@ -45388,7 +45394,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="834" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>1005</v>
       </c>
@@ -45438,7 +45444,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="835" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>1006</v>
       </c>
@@ -45488,7 +45494,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="836" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>1007</v>
       </c>
@@ -45538,7 +45544,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="837" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>1008</v>
       </c>
@@ -45588,7 +45594,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="838" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>1009</v>
       </c>
@@ -45638,7 +45644,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="839" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>1010</v>
       </c>
@@ -45688,7 +45694,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="840" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>1011</v>
       </c>
@@ -45738,7 +45744,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="841" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>1012</v>
       </c>
@@ -45788,7 +45794,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="842" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>1013</v>
       </c>
@@ -45838,7 +45844,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="843" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>1014</v>
       </c>
@@ -45888,7 +45894,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="844" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>1015</v>
       </c>
@@ -45938,7 +45944,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="845" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>1016</v>
       </c>
@@ -45988,7 +45994,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="846" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>1017</v>
       </c>
@@ -46038,7 +46044,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="847" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>1018</v>
       </c>
@@ -46088,7 +46094,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="848" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>1019</v>
       </c>
@@ -46138,7 +46144,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="849" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="849" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>1020</v>
       </c>
@@ -46188,7 +46194,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="850" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="850" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>1021</v>
       </c>
@@ -46238,7 +46244,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="851" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="851" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>1022</v>
       </c>
@@ -46288,7 +46294,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="852" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="852" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>1023</v>
       </c>
@@ -46338,7 +46344,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="853" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="853" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>1024</v>
       </c>
@@ -46388,7 +46394,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="854" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="854" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>1025</v>
       </c>
@@ -46438,7 +46444,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="855" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="855" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>1026</v>
       </c>
@@ -46488,7 +46494,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="856" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="856" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>1027</v>
       </c>
@@ -46538,7 +46544,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="857" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="857" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>1028</v>
       </c>
@@ -46588,7 +46594,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="858" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="858" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>1029</v>
       </c>
@@ -46638,7 +46644,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="859" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>1030</v>
       </c>
@@ -46688,7 +46694,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="860" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="860" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>1031</v>
       </c>
@@ -46738,7 +46744,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="861" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="861" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>1032</v>
       </c>
@@ -46788,7 +46794,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="862" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="862" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>1033</v>
       </c>
@@ -46838,7 +46844,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="863" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="863" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>1034</v>
       </c>
@@ -46888,7 +46894,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="864" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="864" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>1035</v>
       </c>
@@ -46938,7 +46944,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="865" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="865" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A865" s="1" t="s">
         <v>1036</v>
       </c>
@@ -46988,7 +46994,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="866" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="866" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A866" s="1" t="s">
         <v>1037</v>
       </c>
@@ -47038,7 +47044,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="867" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="867" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A867" s="1" t="s">
         <v>1038</v>
       </c>

--- a/file/players_updated.xlsx
+++ b/file/players_updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.abraga\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5601089-5C80-4AAE-A451-E54469D33832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFE33DA-D3EC-4284-B13A-E9E7AF2D1989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4348" uniqueCount="1106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4348" uniqueCount="1118">
   <si>
     <t>PlayerName</t>
   </si>
@@ -3338,6 +3338,42 @@
   </si>
   <si>
     <t>maxilus</t>
+  </si>
+  <si>
+    <t>awper</t>
+  </si>
+  <si>
+    <t>awper|entry fragger</t>
+  </si>
+  <si>
+    <t>igl|awper</t>
+  </si>
+  <si>
+    <t>entry fragger|star player</t>
+  </si>
+  <si>
+    <t>rifler|trader</t>
+  </si>
+  <si>
+    <t>awper|closer</t>
+  </si>
+  <si>
+    <t>awper|igl</t>
+  </si>
+  <si>
+    <t>anchor</t>
+  </si>
+  <si>
+    <t>star player|closer</t>
+  </si>
+  <si>
+    <t>igl|anchor</t>
+  </si>
+  <si>
+    <t>entry fragger</t>
+  </si>
+  <si>
+    <t>dynamic</t>
   </si>
 </sst>
 </file>
@@ -3730,9 +3766,9 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="3" max="3" width="28.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.75" customWidth="1"/>
+    <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="3.75" customWidth="1"/>
     <col min="9" max="9" width="3.25" customWidth="1"/>
     <col min="10" max="10" width="4.875" customWidth="1"/>
@@ -3806,7 +3842,7 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>1109</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -3862,7 +3898,7 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>1110</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -3918,7 +3954,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>1117</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -3974,7 +4010,7 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>1108</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -4030,7 +4066,7 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>1117</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -4086,7 +4122,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>1106</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -4142,7 +4178,7 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>1117</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -4198,7 +4234,7 @@
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>1116</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -4254,7 +4290,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>1117</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -4310,7 +4346,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>1117</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -4366,7 +4402,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>1109</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -4422,7 +4458,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>1113</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -4478,7 +4514,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>1117</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -4534,7 +4570,7 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>1113</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -4590,7 +4626,7 @@
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>1106</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -5486,7 +5522,7 @@
         <v>19</v>
       </c>
       <c r="C32" t="s">
-        <v>20</v>
+        <v>1109</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -5542,7 +5578,7 @@
         <v>19</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>1111</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -5598,7 +5634,7 @@
         <v>19</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>1115</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -5654,7 +5690,7 @@
         <v>19</v>
       </c>
       <c r="C35" t="s">
-        <v>20</v>
+        <v>1113</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -5710,7 +5746,7 @@
         <v>19</v>
       </c>
       <c r="C36" t="s">
-        <v>20</v>
+        <v>1116</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -10246,7 +10282,7 @@
         <v>19</v>
       </c>
       <c r="C117" t="s">
-        <v>20</v>
+        <v>1112</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -10302,7 +10338,7 @@
         <v>19</v>
       </c>
       <c r="C118" t="s">
-        <v>20</v>
+        <v>1113</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -10358,7 +10394,7 @@
         <v>19</v>
       </c>
       <c r="C119" t="s">
-        <v>20</v>
+        <v>1109</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -10414,7 +10450,7 @@
         <v>19</v>
       </c>
       <c r="C120" t="s">
-        <v>20</v>
+        <v>1114</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -10470,7 +10506,7 @@
         <v>19</v>
       </c>
       <c r="C121" t="s">
-        <v>20</v>
+        <v>1107</v>
       </c>
       <c r="D121">
         <v>0</v>

--- a/file/players_updated.xlsx
+++ b/file/players_updated.xlsx
@@ -484,10 +484,10 @@
         <v>entry fragger|star player</v>
       </c>
       <c r="D2">
-        <v>56666.66666666666</v>
+        <v>56666.666666666664</v>
       </c>
       <c r="E2">
-        <v>56666.66666666666</v>
+        <v>56666.666666666664</v>
       </c>
       <c r="F2">
         <v>12</v>
@@ -529,7 +529,7 @@
         <v>1</v>
       </c>
       <c r="S2">
-        <v>5667</v>
+        <v>5600</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -609,13 +609,13 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V3">
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="str">
         <v/>
@@ -683,13 +683,13 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V4">
         <v>0</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="str">
         <v/>
@@ -706,10 +706,10 @@
         <v>igl|awper</v>
       </c>
       <c r="D5">
-        <v>47142.85714285714</v>
+        <v>47142.857142857145</v>
       </c>
       <c r="E5">
-        <v>47142.85714285714</v>
+        <v>47142.857142857145</v>
       </c>
       <c r="F5">
         <v>12</v>
@@ -751,7 +751,7 @@
         <v>1</v>
       </c>
       <c r="S5">
-        <v>4714</v>
+        <v>4243</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -831,13 +831,13 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V6">
         <v>0</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="str">
         <v/>
@@ -2334,10 +2334,10 @@
         <v>awper</v>
       </c>
       <c r="D27">
-        <v>25504.7619047619</v>
+        <v>25504.761904761905</v>
       </c>
       <c r="E27">
-        <v>25504.7619047619</v>
+        <v>25504.761904761905</v>
       </c>
       <c r="F27">
         <v>6</v>
@@ -3814,10 +3814,10 @@
         <v>awper</v>
       </c>
       <c r="D47">
-        <v>15142.85714285714</v>
+        <v>15142.857142857141</v>
       </c>
       <c r="E47">
-        <v>15142.85714285714</v>
+        <v>15142.857142857141</v>
       </c>
       <c r="F47">
         <v>6</v>
@@ -7571,7 +7571,7 @@
         <v>0</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X97" t="str">
         <v/>
@@ -7645,7 +7645,7 @@
         <v>0</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X98" t="str">
         <v/>
@@ -7668,7 +7668,7 @@
         <v>0</v>
       </c>
       <c r="F99">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G99" t="str">
         <v>Iluminar</v>
@@ -7793,7 +7793,7 @@
         <v>0</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X100" t="str">
         <v/>
@@ -7867,7 +7867,7 @@
         <v>0</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X101" t="str">
         <v/>
@@ -8260,7 +8260,7 @@
         <v>0</v>
       </c>
       <c r="F107">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G107" t="str">
         <v>Iluminar</v>
@@ -8385,7 +8385,7 @@
         <v>0</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X108" t="str">
         <v/>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X109" t="str">
         <v/>
@@ -8533,7 +8533,7 @@
         <v>0</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X110" t="str">
         <v/>
@@ -8607,7 +8607,7 @@
         <v>0</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X111" t="str">
         <v/>
@@ -9213,7 +9213,7 @@
         <v>Starter</v>
       </c>
       <c r="C120" t="str">
-        <v>star player</v>
+        <v>star player|star player</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -62798,7 +62798,7 @@
         <v>0</v>
       </c>
       <c r="F844">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G844" t="str">
         <v>Kappa Bar</v>
@@ -63242,7 +63242,7 @@
         <v>0</v>
       </c>
       <c r="F850">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G850" t="str">
         <v>Mythic</v>
@@ -64352,7 +64352,7 @@
         <v>0</v>
       </c>
       <c r="F865">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G865" t="str">
         <v>Lux Tenebris</v>
@@ -64406,7 +64406,7 @@
         <v>0</v>
       </c>
       <c r="X865" t="str">
-        <v/>
+        <v>user</v>
       </c>
     </row>
     <row r="866">
@@ -64648,7 +64648,7 @@
         <v>0</v>
       </c>
       <c r="F869">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G869" t="str">
         <v>Lux Tenebris</v>
@@ -64722,7 +64722,7 @@
         <v>0</v>
       </c>
       <c r="F870">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G870" t="str">
         <v>Lux Tenebris</v>

--- a/file/players_updated.xlsx
+++ b/file/players_updated.xlsx
@@ -64710,7 +64710,7 @@
         <v>fer</v>
       </c>
       <c r="B870" t="str">
-        <v>Starter</v>
+        <v>Bench</v>
       </c>
       <c r="C870" t="str">
         <v>dynamic</v>
@@ -64784,7 +64784,7 @@
         <v>boltz</v>
       </c>
       <c r="B871" t="str">
-        <v>no team</v>
+        <v>Starter</v>
       </c>
       <c r="C871" t="str">
         <v>dynamic</v>
@@ -64796,10 +64796,10 @@
         <v>0</v>
       </c>
       <c r="F871">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G871" t="str">
-        <v>none</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="H871">
         <v>0</v>

--- a/file/players_updated.xlsx
+++ b/file/players_updated.xlsx
@@ -21944,10 +21944,10 @@
         <v>anchor</v>
       </c>
       <c r="D292">
-        <v>0</v>
+        <v>3811.428571428571</v>
       </c>
       <c r="E292">
-        <v>0</v>
+        <v>3811.428571428571</v>
       </c>
       <c r="F292">
         <v>5</v>
@@ -21959,13 +21959,13 @@
         <v>0</v>
       </c>
       <c r="I292">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J292">
         <v>0</v>
       </c>
       <c r="K292">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L292">
         <v>0</v>
@@ -22018,10 +22018,10 @@
         <v>star player</v>
       </c>
       <c r="D293">
-        <v>0</v>
+        <v>5240</v>
       </c>
       <c r="E293">
-        <v>0</v>
+        <v>5240</v>
       </c>
       <c r="F293">
         <v>5</v>
@@ -22030,7 +22030,7 @@
         <v>Fnatic</v>
       </c>
       <c r="H293">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I293">
         <v>0</v>
@@ -22039,7 +22039,7 @@
         <v>0</v>
       </c>
       <c r="K293">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L293">
         <v>0</v>
@@ -22092,10 +22092,10 @@
         <v>igl</v>
       </c>
       <c r="D294">
-        <v>0</v>
+        <v>2382.8571428571427</v>
       </c>
       <c r="E294">
-        <v>0</v>
+        <v>2382.8571428571427</v>
       </c>
       <c r="F294">
         <v>5</v>
@@ -22110,10 +22110,10 @@
         <v>0</v>
       </c>
       <c r="J294">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K294">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L294">
         <v>0</v>
@@ -22166,10 +22166,10 @@
         <v>star player</v>
       </c>
       <c r="D295">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="E295">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="F295">
         <v>5</v>
@@ -22187,7 +22187,7 @@
         <v>0</v>
       </c>
       <c r="K295">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L295">
         <v>0</v>
@@ -22240,10 +22240,10 @@
         <v>awper</v>
       </c>
       <c r="D296">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="E296">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="F296">
         <v>5</v>
@@ -22261,7 +22261,7 @@
         <v>0</v>
       </c>
       <c r="K296">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L296">
         <v>0</v>
@@ -41924,10 +41924,10 @@
         <v>dynamic</v>
       </c>
       <c r="D562">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E562">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F562">
         <v>5</v>
@@ -41998,10 +41998,10 @@
         <v>dynamic</v>
       </c>
       <c r="D563">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E563">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F563">
         <v>5</v>
@@ -42072,10 +42072,10 @@
         <v>dynamic</v>
       </c>
       <c r="D564">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E564">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F564">
         <v>5</v>
@@ -42146,10 +42146,10 @@
         <v>dynamic</v>
       </c>
       <c r="D565">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E565">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F565">
         <v>5</v>
@@ -42220,10 +42220,10 @@
         <v>dynamic</v>
       </c>
       <c r="D566">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E566">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F566">
         <v>5</v>
@@ -42294,10 +42294,10 @@
         <v>dynamic</v>
       </c>
       <c r="D567">
-        <v>0</v>
+        <v>2262.8571428571427</v>
       </c>
       <c r="E567">
-        <v>0</v>
+        <v>2262.8571428571427</v>
       </c>
       <c r="F567">
         <v>5</v>
@@ -42312,7 +42312,7 @@
         <v>0</v>
       </c>
       <c r="J567">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K567">
         <v>0</v>
@@ -42368,10 +42368,10 @@
         <v>dynamic</v>
       </c>
       <c r="D568">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E568">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F568">
         <v>5</v>
@@ -42442,10 +42442,10 @@
         <v>dynamic</v>
       </c>
       <c r="D569">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E569">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F569">
         <v>5</v>
@@ -42516,10 +42516,10 @@
         <v>dynamic</v>
       </c>
       <c r="D570">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E570">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F570">
         <v>5</v>
@@ -42590,10 +42590,10 @@
         <v>dynamic</v>
       </c>
       <c r="D571">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E571">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F571">
         <v>5</v>
@@ -43404,10 +43404,10 @@
         <v>dynamic</v>
       </c>
       <c r="D582">
-        <v>0</v>
+        <v>2302.8571428571427</v>
       </c>
       <c r="E582">
-        <v>0</v>
+        <v>2302.8571428571427</v>
       </c>
       <c r="F582">
         <v>5</v>
@@ -43422,7 +43422,7 @@
         <v>0</v>
       </c>
       <c r="J582">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K582">
         <v>0</v>
@@ -43478,10 +43478,10 @@
         <v>dynamic</v>
       </c>
       <c r="D583">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="E583">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F583">
         <v>5</v>
@@ -43552,10 +43552,10 @@
         <v>dynamic</v>
       </c>
       <c r="D584">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="E584">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F584">
         <v>5</v>
@@ -43626,10 +43626,10 @@
         <v>dynamic</v>
       </c>
       <c r="D585">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="E585">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F585">
         <v>5</v>
@@ -43700,10 +43700,10 @@
         <v>dynamic</v>
       </c>
       <c r="D586">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="E586">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F586">
         <v>5</v>
@@ -53394,10 +53394,10 @@
         <v>dynamic</v>
       </c>
       <c r="D717">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E717">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F717">
         <v>5</v>
@@ -53468,10 +53468,10 @@
         <v>dynamic</v>
       </c>
       <c r="D718">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E718">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F718">
         <v>5</v>
@@ -53542,10 +53542,10 @@
         <v>dynamic</v>
       </c>
       <c r="D719">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E719">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F719">
         <v>5</v>
@@ -53616,10 +53616,10 @@
         <v>dynamic</v>
       </c>
       <c r="D720">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E720">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F720">
         <v>5</v>
@@ -53690,10 +53690,10 @@
         <v>dynamic</v>
       </c>
       <c r="D721">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E721">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F721">
         <v>5</v>
@@ -53764,10 +53764,10 @@
         <v>dynamic</v>
       </c>
       <c r="D722">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E722">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F722">
         <v>5</v>
@@ -53838,10 +53838,10 @@
         <v>dynamic</v>
       </c>
       <c r="D723">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E723">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F723">
         <v>5</v>
@@ -53912,10 +53912,10 @@
         <v>dynamic</v>
       </c>
       <c r="D724">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E724">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F724">
         <v>5</v>
@@ -53986,10 +53986,10 @@
         <v>dynamic</v>
       </c>
       <c r="D725">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E725">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F725">
         <v>5</v>
@@ -54060,10 +54060,10 @@
         <v>dynamic</v>
       </c>
       <c r="D726">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E726">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F726">
         <v>5</v>
@@ -54504,10 +54504,10 @@
         <v>dynamic</v>
       </c>
       <c r="D732">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E732">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F732">
         <v>5</v>
@@ -54578,10 +54578,10 @@
         <v>dynamic</v>
       </c>
       <c r="D733">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E733">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F733">
         <v>5</v>
@@ -54652,10 +54652,10 @@
         <v>dynamic</v>
       </c>
       <c r="D734">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E734">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F734">
         <v>5</v>
@@ -54726,10 +54726,10 @@
         <v>dynamic</v>
       </c>
       <c r="D735">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E735">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F735">
         <v>5</v>
@@ -54800,10 +54800,10 @@
         <v>dynamic</v>
       </c>
       <c r="D736">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E736">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F736">
         <v>5</v>
@@ -55244,10 +55244,10 @@
         <v>dynamic</v>
       </c>
       <c r="D742">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E742">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F742">
         <v>5</v>
@@ -55318,10 +55318,10 @@
         <v>dynamic</v>
       </c>
       <c r="D743">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E743">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F743">
         <v>5</v>
@@ -55392,10 +55392,10 @@
         <v>dynamic</v>
       </c>
       <c r="D744">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E744">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F744">
         <v>5</v>
@@ -55466,10 +55466,10 @@
         <v>dynamic</v>
       </c>
       <c r="D745">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E745">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F745">
         <v>5</v>
@@ -55540,10 +55540,10 @@
         <v>dynamic</v>
       </c>
       <c r="D746">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E746">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F746">
         <v>5</v>

--- a/file/players_updated.xlsx
+++ b/file/players_updated.xlsx
@@ -64710,7 +64710,7 @@
         <v>fer</v>
       </c>
       <c r="B870" t="str">
-        <v>Bench</v>
+        <v/>
       </c>
       <c r="C870" t="str">
         <v>dynamic</v>
@@ -64722,10 +64722,10 @@
         <v>0</v>
       </c>
       <c r="F870">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G870" t="str">
-        <v>Lux Tenebris</v>
+        <v>none</v>
       </c>
       <c r="H870">
         <v>0</v>
@@ -64773,7 +64773,7 @@
         <v>0</v>
       </c>
       <c r="W870">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X870" t="str">
         <v/>
